--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账重量汇总</t>
+          <t>第 1 题：第1题：统计某客户订单金额</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,77 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家物流公司的文员，现有一份到货台账，需要按货物类型汇总重量。请用 SUMIF 函数统计「电子产品」的总重量。</t>
+          <t>要求：你在一家小公司做订单台账，需要按客户名称快速汇总订单金额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，计算「电子产品」的总重量。</t>
+          <t>任务：在 D2 单元格输入公式，计算客户“张三”的订单金额合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>货物类型</t>
+          <t>客户名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>60</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -573,412 +573,488 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港台账计数与最大重量</t>
+          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责港口到港记录，需要统计「已到港」的批次数，并找出所有货物中的最大重量。</t>
+          <t>要求：仓库台账中记录了不同供应商、不同品类的到货重量，需要先汇总某供应商某品类的总重量，再判断是否达到 1000 公斤。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C5，请在 E2 单元格统计「已到港」的批次数，在 E3 单元格找出最大重量。</t>
+          <t>任务：在 F2 单元格输入公式：如果“A公司”的“钢材”到货总重量大于等于 1000，则显示“达标”，否则显示“未达标”。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>批次号</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>品类</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>到货重量</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>A公司</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
+          <t>钢材</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>未到港</t>
+          <t>钢材</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>A公司</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
+          <t>铝材</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>760</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>A公司</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
+          <t>钢材</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>B公司</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>铝材</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份仓库入库明细，需要统计「华东仓」且「食品」的总重量，并将结果四舍五入保留 1 位小数。</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C6，请在 E2 单元格统计「华东仓」且「食品」的总重量，并四舍五入保留 1 位小数。</t>
+          <t>要求：物流跟单表中记录了到港日期，同时需要统计某司机迟到次数，并计算从发车到到港经过了多少天。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 单元格输入公式，统计司机“赵六”状态为“迟到”的次数；在 G3 单元格输入公式，计算第 2 行从发车日期到到港日期的天数。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>125.36</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>司机</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>发车日期</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>华北仓</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>200.1</v>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>80.25</v>
+          <t>准时</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>99.87</v>
+          <t>准时</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>华南仓</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>150.4</v>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：入职天数与错误处理</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一名人事实习生，需要根据员工入职日期计算截至今天的在职天数；如果日期缺失或错误，则显示「日期有误」。</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:B5，请在 C2:C5 单元格输入公式，计算每位员工截至今天的入职天数，日期缺失时显示「日期有误」。</t>
+          <t>要求：销售开单时需要根据商品编号从价格表中查单价；如果编号不存在，不希望显示错误值，而是显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 单元格输入公式，根据 F2 中的商品编号“P1003”查找对应单价；如果找不到，则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2022-03-15</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>P1001</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
-        </is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr"/>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>P1003</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>8.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>P1004</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：运单查询与双向匹配</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责运单查询，需要根据运单号自动带出目的地和运费。先用 XLOOKUP 查目的地，再用 INDEX+MATCH 查运费。</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C5，请在 E2 输入运单号「YD003」；在 F2 用 XLOOKUP 查目的地，在 G2 用 INDEX+MATCH 查运费。</t>
+          <t>要求：商品价格表已更新，需要根据商品名称反向查找单价，同时从商品编号中提取后三位作为短码，并对单价四舍五入保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>运费(元)</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 单元格输入公式，根据 F2 中的商品名称“鼠标”查找对应单价；在 G3 单元格输入公式，提取 A3 商品编号的后三位短码；在 G4 单元格输入公式，将 G2 查到的单价四舍五入保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>35</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>AB2024001</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>42</v>
+        <v>89.456</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>AB2024002</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>鼠标</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>50</v>
+        <v>45.678</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>AB2024003</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>48</v>
+        <v>799.123</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>AB2024004</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>摄像头</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>129.987</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1005,7 +1081,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账重量汇总</t>
+          <t>第 1 题：第1题：统计某客户订单金额</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1092,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"电子产品",B2:B6)</f>
+        <f>SUMIF(A2:A6,"张三",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1106,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港台账计数与最大重量</t>
+          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1117,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B5,"已到港")，=MAX(C2:C5)</f>
+        <f>IF(SUMIFS(C2:C6,A2:A6,"A公司",B2:B6,"钢材")&gt;=1000,"达标","未达标")</f>
         <v/>
       </c>
     </row>
@@ -1055,7 +1131,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
+          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1065,9 +1141,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>ROUND(SUMIFS(C2:C6,A2:A6,"华东仓",B2:B6,"食品"),1)</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>G2：=COUNTIFS(A2:A6,"赵六",B2:B6,"迟到")；G3：=DATEDIF(C2,D2,"d")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1080,7 +1157,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：入职天数与错误处理</t>
+          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1168,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"D"),"日期有误")</f>
+        <f>IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1182,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：运单查询与双向匹配</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
         </is>
       </c>
     </row>
@@ -1115,9 +1192,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>XLOOKUP(E2,A2:A5,B2:B5)，=INDEX(C2:C5,MATCH(E2,A2:A5,0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>G2：=INDEX(C2:C5,MATCH(F2,B2:B5,0))；G3：=RIGHT(A3,3)；G4：=ROUND(G2,1)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1226,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账重量汇总</t>
+          <t>第 1 题：第1题：统计某客户订单金额</t>
         </is>
       </c>
     </row>
@@ -1160,14 +1238,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法：=SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是货物类型，条件是「电子产品」，B2:B6 是重量。结果应为 120+95+70=285。</t>
+          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域,条件,求和区域)。这里 A2:A6 是客户名称，条件是“张三”，B2:B6 是对应订单金额。结果为 1200+300+500=2000。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港台账计数与最大重量</t>
+          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1257,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 语法：=COUNTIF(区域, 条件)，统计满足条件的单元格个数，E2 结果为 3。MAX 语法：=MAX(数值区域)，返回最大值，E3 结果为 760。</t>
+          <t>SUMIFS 支持多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。这里先算出 A公司钢材总重量 600+500=1100，再用 IF 判断 1100&gt;=1000，返回“达标”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
+          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1198,14 +1276,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法：=SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。这里求 C2:C6，条件为 A 列「华东仓」且 B 列「食品」。ROUND 语法：=ROUND(数值, 小数位数)，将 225.23 四舍五入为 225.2。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1,条件1,条件区域2,条件2)。DATEDIF 用于计算两个日期差值，语法为 DATEDIF(开始日期,结束日期,单位)，"d" 表示天数。赵六迟到 2 次；2024-05-01 到 2024-05-06 为 5 天。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：入职天数与错误处理</t>
+          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
         </is>
       </c>
     </row>
@@ -1217,14 +1295,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 语法：=DATEDIF(开始日期, 结束日期, "D")，返回两个日期之间的天数。TODAY() 返回当天日期。IFERROR 语法：=IFERROR(值, 错误时显示内容)，当 B 列为空时 DATEDIF 出错，显示「日期有误」。</t>
+          <t>VLOOKUP 按首列查找并返回指定列数据，语法为 VLOOKUP(查找值,查找区域,返回列号,精确/近似)。这里查找 F2，在 A2:C5 中匹配，返回第 3 列单价，FALSE 表示精确匹配。IFERROR 用于捕获错误，查不到时显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：运单查询与双向匹配</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1314,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法：=XLOOKUP(查找值, 查找区域, 返回区域)，F2 返回「广州」。INDEX 语法：=INDEX(返回区域, 行号)，MATCH 语法：=MATCH(查找值, 查找区域, 0) 返回精确位置；G2 先定位 YD003 在第 3 行，再取 C2:C5 第 3 个值，结果为 50。</t>
+          <t>INDEX 返回区域中指定位置的值，MATCH 返回查找值在区域中的相对位置，语法分别为 INDEX(区域,行号) 和 MATCH(查找值,区域,0)，二者组合可实现反向查找。RIGHT(文本,字符数) 可从右侧提取字符。ROUND(数值,小数位数) 可四舍五入，这里保留 1 位小数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户订单金额</t>
+          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,107 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家小公司做订单台账，需要按客户名称快速汇总订单金额。</t>
+          <t>要求：你在一家电商仓库做台账，需要统计「上海仓」所有出库单的总重量。请按仓库名称汇总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算客户“张三”的订单金额合计。</t>
+          <t>任务：在空白单元格 F2 中，计算「上海仓」的重量合计，请写出公式。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>出库单号</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CK001</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>800</v>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CK002</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>300</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CK003</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1500</v>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CK004</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>15.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>500</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CK005</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
@@ -573,488 +603,420 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
+          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：仓库台账中记录了不同供应商、不同品类的到货重量，需要先汇总某供应商某品类的总重量，再判断是否达到 1000 公斤。</t>
+          <t>要求：你负责跟踪进口货柜到港情况，需要根据「到港日期」计算截至今天已经到港多少天。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格输入公式：如果“A公司”的“钢材”到货总重量大于等于 1000，则显示“达标”，否则显示“未达标”。</t>
+          <t>任务：在 C2 单元格中，计算 GZ001 从到港日期到今天的天数，并向下填充到 C5。请写出 C2 的公式。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>货柜号</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>到货重量</t>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
+          <t>GZ001</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>600</v>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>B公司</t>
+          <t>GZ002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>700</v>
+          <t>2024-05-10</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
+          <t>GZ003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>铝材</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>450</v>
+          <t>2024-06-01</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
+          <t>GZ004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>500</v>
+          <t>2024-06-15</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>B公司</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>铝材</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：销售提成判断（IF）</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>练习函数：IF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>要求：物流跟单表中记录了到港日期，同时需要统计某司机迟到次数，并计算从发车到到港经过了多少天。</t>
+          <t>要求：公司规定：销售额大于等于 10000 元，提成按 5% 计算；否则按 2% 计算。请根据销售额自动计算提成金额。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在 G2 单元格输入公式，统计司机“赵六”状态为“迟到”的次数；在 G3 单元格输入公式，计算第 2 行从发车日期到到港日期的天数。</t>
+          <t>任务：在 C2 单元格中计算张三的提成金额，并向下填充到 C5。请写出 C2 的公式。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>司机</t>
+          <t>员工</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>发车日期</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>准时</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>准时</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你需要统计「华东区」且「订单金额大于等于 1000」的订单数量，以及这些订单的金额合计。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>要求：销售开单时需要根据商品编号从价格表中查单价；如果编号不存在，不希望显示错误值，而是显示“未找到”。</t>
+          <t>任务：在 F2 单元格中统计符合条件的订单数量，在 F3 单元格中统计符合条件的订单金额合计。请分别写出 F2 和 F3 的公式。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 单元格输入公式，根据 F2 中的商品编号“P1003”查找对应单价；如果找不到，则显示“未找到”。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>DD001</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>P1001</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
+          <t>DD002</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>12.5</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>P1002</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>签字笔</t>
+          <t>DD003</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>3.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>P1003</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
+          <t>DD004</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>8.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>P1004</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>订书机</t>
+          <t>DD005</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>25</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>DD006</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品价格表已更新，需要根据商品名称反向查找单价，同时从商品编号中提取后三位作为短码，并对单价四舍五入保留 1 位小数。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 单元格输入公式，根据 F2 中的商品名称“鼠标”查找对应单价；在 G3 单元格输入公式，提取 A3 商品编号的后三位短码；在 G4 单元格输入公式，将 G2 查到的单价四舍五入保留 1 位小数。</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张产品价格表，需要根据订单中的「产品编号」自动查找对应单价。请使用 XLOOKUP 完成查表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 A7 单元格输入要查询的产品编号，例如 P003；在 B7 单元格中根据 A7 查找对应单价。请写出 B7 的公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>AB2024001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>89.456</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>AB2024002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>45.678</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>AB2024003</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
+          <t>鼠标</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>799.123</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>AB2024004</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>摄像头</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>129.987</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>U盘</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1081,7 +1043,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户订单金额</t>
+          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1054,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"张三",B2:B6)</f>
+        <f>SUMIF(A2:A6,"上海仓",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1106,7 +1068,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
+          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1079,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IF(SUMIFS(C2:C6,A2:A6,"A公司",B2:B6,"钢材")&gt;=1000,"达标","未达标")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1131,7 +1093,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
+          <t>第 3 题：第3题：销售提成判断（IF）</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1103,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>G2：=COUNTIFS(A2:A6,"赵六",B2:B6,"迟到")；G3：=DATEDIF(C2,D2,"d")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>IF(B2&gt;=10000,B2*5%,B2*2%)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1157,7 +1118,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
+          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1167,9 +1128,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>F2：=COUNTIFS(A2:A7,"华东区",C2:C7,"&gt;=1000")；F3：=SUMIFS(C2:C7,A2:A7,"华东区",C2:C7,"&gt;=1000")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1182,7 +1144,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
+          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1192,10 +1154,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2：=INDEX(C2:C5,MATCH(F2,B2:B5,0))；G3：=RIGHT(A3,3)；G4：=ROUND(G2,1)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>XLOOKUP(A7,A2:A5,C2:C5)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1226,7 +1187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户订单金额</t>
+          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1238,14 +1199,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域,条件,求和区域)。这里 A2:A6 是客户名称，条件是“张三”，B2:B6 是对应订单金额。结果为 1200+300+500=2000。</t>
+          <t>SUMIF 用于按一个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是仓库列，条件是“上海仓”，C2:C6 是重量列，表示把所有上海仓对应的重量相加。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货重量及判断是否达标</t>
+          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1218,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 支持多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。这里先算出 A公司钢材总重量 600+500=1100，再用 IF 判断 1100&gt;=1000，返回“达标”。</t>
+          <t>TODAY() 返回当天日期；DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。这里以 B2 为开始日期，TODAY() 为结束日期，参数 "d" 表示按天计算。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：统计迟到次数并计算到港天数</t>
+          <t>第 3 题：第3题：销售提成判断（IF）</t>
         </is>
       </c>
     </row>
@@ -1276,14 +1237,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1,条件1,条件区域2,条件2)。DATEDIF 用于计算两个日期差值，语法为 DATEDIF(开始日期,结束日期,单位)，"d" 表示天数。赵六迟到 2 次；2024-05-01 到 2024-05-06 为 5 天。</t>
+          <t>IF 用于条件判断，语法为 IF(条件, 条件成立时返回的值, 条件不成立时返回的值)。这里判断 B2 是否大于等于 10000，成立则返回 B2*5%，否则返回 B2*2%。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查找单价并处理错误</t>
+          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1295,14 +1256,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 按首列查找并返回指定列数据，语法为 VLOOKUP(查找值,查找区域,返回列号,精确/近似)。这里查找 F2，在 A2:C5 中匹配，返回第 3 列单价，FALSE 表示精确匹配。IFERROR 用于捕获错误，查不到时显示“未找到”。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里同时判断区域为“华东区”且订单金额大于等于 1000。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查价格并提取商品编码后三位</t>
+          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1275,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX 返回区域中指定位置的值，MATCH 返回查找值在区域中的相对位置，语法分别为 INDEX(区域,行号) 和 MATCH(查找值,区域,0)，二者组合可实现反向查找。RIGHT(文本,字符数) 可从右侧提取字符。ROUND(数值,小数位数) 可四舍五入，这里保留 1 位小数。</t>
+          <t>XLOOKUP 用于查找匹配，语法为 XLOOKUP(查找值, 查找区域, 返回区域)。这里 A7 是要查找的产品编号，A2:A5 是产品编号列，C2:C5 是单价列，返回对应单价。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,121 +476,151 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家电商仓库做台账，需要统计「上海仓」所有出库单的总重量。请按仓库名称汇总重量。</t>
+          <t>要求：你是仓库文员，需要统计每个仓库的入库总重量。请根据下面的入库台账，计算「上海仓」的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 F2 中，计算「上海仓」的重量合计，请写出公式。</t>
+          <t>任务：在空白单元格输入公式，计算仓库为「上海仓」的重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>仓库</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>出库单号</t>
-        </is>
-      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量kg</t>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CK001</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>12.5</v>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>纸巾</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>北京仓</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CK002</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8</v>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CK003</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>20</v>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>矿泉水</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>广州仓</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>CK004</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>15.5</v>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>纸巾</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CK005</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>6.5</v>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -603,31 +633,36 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：统计到港天数并处理异常</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责跟踪进口货柜到港情况，需要根据「到港日期」计算截至今天已经到港多少天。</t>
+          <t>要求：物流跟单员需要计算货物从发运到到港的天数。如果还没到港，日期为空，公式不要显示错误，而显示「未到港」。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格中，计算 GZ001 从到港日期到今天的天数，并向下填充到 C5。请写出 C2 的公式。</t>
+          <t>任务：在 E2 单元格输入公式，计算 A001 的到港天数；然后向下填充到 E5，未到港的显示「未到港」。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>货柜号</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>到港日期</t>
         </is>
@@ -636,22 +671,32 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GZ001</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>GZ002</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
@@ -660,24 +705,30 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>GZ003</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>GZ004</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
         </is>
       </c>
     </row>
@@ -691,81 +742,81 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售提成判断（IF）</t>
+          <t>第 3 题：第3题：按商品名称查价格</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>练习函数：IF</t>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>要求：公司规定：销售额大于等于 10000 元，提成按 5% 计算；否则按 2% 计算。请根据销售额自动计算提成金额。</t>
+          <t>要求：客服需要根据商品名称快速查出单价。请使用 XLOOKUP 在商品价目表中查找「矿泉水」的价格。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格中计算张三的提成金额，并向下填充到 C5。请写出 C2 的公式。</t>
+          <t>任务：在空白单元格输入公式，查找商品「矿泉水」对应的单价。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>员工</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>纸巾</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>12000</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>洗衣液</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>8000</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>矿泉水</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>15000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>方便面</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>6000</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32">
@@ -778,245 +829,231 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
+          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：你需要统计「华东区」且「订单金额大于等于 1000」的订单数量，以及这些订单的金额合计。</t>
+          <t>要求：HR 需要根据员工姓名查部门。请用 INDEX 和 MATCH 组合，查找员工「李娜」所在的部门。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格中统计符合条件的订单数量，在 F3 单元格中统计符合条件的订单金额合计。请分别写出 F2 和 F3 的公式。</t>
+          <t>任务：在空白单元格输入公式，查找「李娜」对应的部门。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>工号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>王强</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>DD001</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1200</v>
+          <t>仓储部</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>李娜</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DD002</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>900</v>
+          <t>客服部</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>赵敏</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>DD003</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>800</v>
+          <t>财务部</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>陈杰</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DD004</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
+          <t>物流部</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售助理需要统计金额大于等于 1000 的订单数量，并计算所有订单的平均金额（保留 2 位小数）。请分两步完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：第1步：在空白单元格输入公式，统计金额大于等于 1000 的订单数量。第2步：在另一个空白单元格输入公式，计算所有订单的平均金额并保留 2 位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>甲公司</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>乙公司</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>甲公司</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
         <v>1500</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>DD005</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>DD006</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张产品价格表，需要根据订单中的「产品编号」自动查找对应单价。请使用 XLOOKUP 完成查表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 A7 单元格输入要查询的产品编号，例如 P003；在 B7 单元格中根据 A7 查找对应单价。请写出 B7 的公式。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
+          <t>丙公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>59</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
+          <t>乙公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>129</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>U盘</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1043,7 +1080,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1091,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"上海仓",C2:C6)</f>
+        <f>SUMIFS(D2:D6,B2:B6,"上海仓")</f>
         <v/>
       </c>
     </row>
@@ -1068,7 +1105,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：统计到港天数并处理异常</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1116,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"未到港")</f>
         <v/>
       </c>
     </row>
@@ -1093,7 +1130,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售提成判断（IF）</t>
+          <t>第 3 题：第3题：按商品名称查价格</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1141,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IF(B2&gt;=10000,B2*5%,B2*2%)</f>
+        <f>XLOOKUP("矿泉水",A2:A5,B2:B5)</f>
         <v/>
       </c>
     </row>
@@ -1118,7 +1155,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
+          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
         </is>
       </c>
     </row>
@@ -1128,10 +1165,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>F2：=COUNTIFS(A2:A7,"华东区",C2:C7,"&gt;=1000")；F3：=SUMIFS(C2:C7,A2:A7,"华东区",C2:C7,"&gt;=1000")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>INDEX(B2:B5,MATCH("李娜",A2:A5,0))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1144,7 +1180,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
+          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1191,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>XLOOKUP(A7,A2:A5,C2:C5)</f>
+        <f>COUNTIFS(C2:C6,"&gt;=1000")；=ROUND(SUMIF(C2:C6,"&gt;0")/COUNTIF(C2:C6,"&gt;0"),2)</f>
         <v/>
       </c>
     </row>
@@ -1187,7 +1223,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
@@ -1199,14 +1235,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按一个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是仓库列，条件是“上海仓”，C2:C6 是重量列，表示把所有上海仓对应的重量相加。</t>
+          <t>SUMIFS 用于按多个条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题只用一个条件：重量列 D2:D6 是求和区域，仓库列 B2:B6 中等于「上海仓」的行参与求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计物流到港天数（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：统计到港天数并处理异常</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1254,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回当天日期；DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。这里以 B2 为开始日期，TODAY() 为结束日期，参数 "d" 表示按天计算。</t>
+          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数，单位 d 表示天。当到港日期为空时，DATEDIF 会报错，因此外面套 IFERROR，把错误结果显示为「未到港」。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售提成判断（IF）</t>
+          <t>第 3 题：第3题：按商品名称查价格</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1273,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IF 用于条件判断，语法为 IF(条件, 条件成立时返回的值, 条件不成立时返回的值)。这里判断 B2 是否大于等于 10000，成立则返回 B2*5%，否则返回 B2*2%。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)。本题在 A2:A5 中查找「矿泉水」，找到后返回 B2:B5 中同一行的单价。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单数量区间统计（COUNTIFS、SUMIFS）</t>
+          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1292,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里同时判断区域为“华东区”且订单金额大于等于 1000。</t>
+          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置；INDEX(返回区域, 位置) 根据位置取出对应内容。本题先用 MATCH 找到「李娜」在第 2 行，再用 INDEX 返回部门列第 2 个值「客服部」。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品单价查表匹配（XLOOKUP）</t>
+          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1311,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 用于查找匹配，语法为 XLOOKUP(查找值, 查找区域, 返回区域)。这里 A7 是要查找的产品编号，A2:A5 是产品编号列，C2:C5 是单价列，返回对应单价。</t>
+          <t>COUNTIFS 可以按条件计数，条件写成 "&gt;=1000" 表示大于等于 1000。平均金额可以用 SUMIF 先求金额总和，再用 COUNTIF 统计金额个数，最后用 ROUND(数值, 2) 保留两位小数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,97 +476,110 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：物流运费的金额汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一名物流公司文员，需要从运单台账中统计“上海仓”发出的“已完成”运单总运费，并把结果四舍五入保留到整数元。请使用 SUMIFS 按多个条件求和，再用 ROUND 处理结果。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要统计每个仓库的入库总重量。请根据下面的入库台账，计算「上海仓」的入库总重量。</t>
+          <t>任务：在任意空白单元格输入公式，计算“上海仓”且“已完成”的运单总运费，并将总金额四舍五入到整数元。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，计算仓库为「上海仓」的重量合计。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>发货仓</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>328.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>纸巾</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>120</v>
+        <v>410.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>洗衣液</t>
+          <t>运输中</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>200</v>
+        <v>288.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -576,17 +589,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>矿泉水</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>350</v>
+        <v>199.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>YD005</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -596,464 +609,447 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>纸巾</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>80</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：到港天数的计算</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计到港天数并处理异常</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责跟踪一批海运货物到港情况，需要根据“到港日期”计算截至今天已经到港多少天。请使用 TODAY 获取当天日期，用 DATEDIF 计算两个日期之间的天数差。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：物流跟单员需要计算货物从发运到到港的天数。如果还没到港，日期为空，公式不要显示错误，而显示「未到港」。</t>
+          <t>任务：在每个订单的右侧新增一列“到港天数”，输入公式计算从“到港日期”到今天的经过天数。假设第一个到港日期在 C2 单元格。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，计算 A001 的到港天数；然后向下填充到 E5，未到港的显示「未到港」。</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SO1001</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>机械配件</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>SO1002</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>塑料粒子</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>SO1003</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>钢材卷板</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-18</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：包裹重量区间统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家快递网点的数据员，需要统计重量在 1 公斤到 5 公斤之间（含 1 和 5）的包裹数量，同时找出当前台账中的最大包裹重量。请使用 COUNTIFS 做多条件计数，用 MAX 找最大值。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按商品名称查价格</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格计算重量大于等于 1 且小于等于 5 的包裹数量；再在另一个空白单元格计算最大包裹重量。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>包裹编号</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>目的城市</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服需要根据商品名称快速查出单价。请使用 XLOOKUP 在商品价目表中查找「矿泉水」的价格。</t>
-        </is>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PK001</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，查找商品「矿泉水」对应的单价。</t>
-        </is>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>PK002</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PK003</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>纸巾</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>5.5</v>
+          <t>PK004</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>39.9</v>
+          <t>PK005</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>矿泉水</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>2</v>
+          <t>PK006</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>方便面</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：员工姓名拆分与工号提取</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：你拿到一份员工信息表，其中“员工代码”格式为“部门-工号-姓名拼音”，例如“FIN-2024-zhangsan”。你需要提取部门代码、工号后四位和姓名拼音首字母大写前的部分。请使用 RIGHT 和 MID 完成提取。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：HR 需要根据员工姓名查部门。请用 INDEX 和 MATCH 组合，查找员工「李娜」所在的部门。</t>
+          <t>任务：在 B2 单元格输入公式提取“员工代码”中的工号后四位；在 C2 单元格输入公式提取姓名拼音部分（从第 10 个字符开始到结尾）。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，查找「李娜」对应的部门。</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>员工代码</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>工号</t>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FIN-2024-zhangsan</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>王强</t>
+          <t>HR-2023-lisi</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>仓储部</t>
+          <t>人事部</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
+          <t>李四</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>OPS-2025-wangwu</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>客服部</t>
+          <t>运营部</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>王五</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>陈杰</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>物流部</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>E004</t>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：产品单价查表匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责电商订单核价，需要根据订单表中的“产品编号”，从产品价格表中查出对应单价。如果查不到，就显示“未找到”。请分别用 XLOOKUP 和 INDEX+MATCH 两种方式完成。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格输入公式，根据指定的产品编号“P1003”查询单价；若找不到则返回“未找到”。可用 XLOOKUP，也可用 IFERROR+INDEX+MATCH。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售助理需要统计金额大于等于 1000 的订单数量，并计算所有订单的平均金额（保留 2 位小数）。请分两步完成。</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：第1步：在空白单元格输入公式，统计金额大于等于 1000 的订单数量。第2步：在另一个空白单元格输入公式，计算所有订单的平均金额并保留 2 位小数。</t>
-        </is>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>无线鼠标</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>机械键盘</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>P1003</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>甲公司</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1200</v>
+        <v>899</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>P1004</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>乙公司</t>
+          <t>摄像头</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>丙公司</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>乙公司</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1080,7 +1076,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：物流运费的金额汇总</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1087,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(D2:D6,B2:B6,"上海仓")</f>
+        <f>ROUND(SUMIFS(D2:D6,B2:B6,"上海仓",C2:C6,"已完成"),0)</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1101,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并处理异常</t>
+          <t>第 2 题：到港天数的计算</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1112,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"未到港")</f>
+        <f>DATEDIF(C2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1130,7 +1126,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按商品名称查价格</t>
+          <t>第 3 题：包裹重量区间统计</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1137,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>XLOOKUP("矿泉水",A2:A5,B2:B5)</f>
+        <f>COUNTIFS(C2:C7,"&gt;=1",C2:C7,"&lt;=5")；=MAX(C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1155,7 +1151,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
+          <t>第 4 题：员工姓名拆分与工号提取</t>
         </is>
       </c>
     </row>
@@ -1165,9 +1161,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>INDEX(B2:B5,MATCH("李娜",A2:A5,0))</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>B2：=RIGHT(A2,4)；C2：=MID(A2,10,100)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1180,7 +1177,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
+          <t>第 5 题：产品单价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1188,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(C2:C6,"&gt;=1000")；=ROUND(SUMIF(C2:C6,"&gt;0")/COUNTIF(C2:C6,"&gt;0"),2)</f>
+        <f>XLOOKUP("P1003",A2:A5,C2:C5,"未找到")；=IFERROR(INDEX(C2:C5,MATCH("P1003",A2:A5,0)),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1223,7 +1220,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：物流运费的金额汇总</t>
         </is>
       </c>
     </row>
@@ -1235,14 +1232,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于按多个条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题只用一个条件：重量列 D2:D6 是求和区域，仓库列 B2:B6 中等于「上海仓」的行参与求和。</t>
+          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。这里对 D2:D6 的运费求和，同时要求 B 列为“上海仓”、C 列为“已完成”。ROUND(数值,0) 表示四舍五入到整数位。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并处理异常</t>
+          <t>第 2 题：到港天数的计算</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1251,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数，单位 d 表示天。当到港日期为空时，DATEDIF 会报错，因此外面套 IFERROR，把错误结果显示为「未到港」。</t>
+          <t>TODAY() 会返回今天的日期，并且会随日期自动更新。DATEDIF(开始日期,结束日期,单位) 可以计算两个日期之间的间隔，单位 "d" 表示天数。因此 DATEDIF(C2,TODAY(),"d") 表示从到港日期到今天的天数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按商品名称查价格</t>
+          <t>第 3 题：包裹重量区间统计</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1270,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)。本题在 A2:A5 中查找「矿泉水」，找到后返回 B2:B5 中同一行的单价。</t>
+          <t>COUNTIFS 可以按多个条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2)。这里用同一个重量区域 C2:C7 分别限制 &gt;=1 和 &lt;=5。MAX(C2:C7) 返回该区域中的最大值。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 查员工部门</t>
+          <t>第 4 题：员工姓名拆分与工号提取</t>
         </is>
       </c>
     </row>
@@ -1292,14 +1289,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置；INDEX(返回区域, 位置) 根据位置取出对应内容。本题先用 MATCH 找到「李娜」在第 2 行，再用 INDEX 返回部门列第 2 个值「客服部」。</t>
+          <t>RIGHT(文本,字符数) 从文本右侧提取指定数量字符，A2 右侧 4 位就是工号后四位。MID(文本,开始位置,字符数) 从指定位置提取字符；A2 中“FIN-2024-”共 9 个字符，所以从第 10 位开始提取姓名拼音，100 表示取足够长，实际会取到文本结尾。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：统计高价值订单并计算平均金额</t>
+          <t>第 5 题：产品单价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1308,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 可以按条件计数，条件写成 "&gt;=1000" 表示大于等于 1000。平均金额可以用 SUMIF 先求金额总和，再用 COUNTIF 统计金额个数，最后用 ROUND(数值, 2) 保留两位小数。</t>
+          <t>XLOOKUP(查找值,查找区域,返回区域,找不到时的返回值) 可以直接完成查表并处理错误。INDEX(返回区域,行号) 根据位置返回单价，MATCH(查找值,查找区域,0) 找到产品编号所在行号。IFERROR 用来在查不到时显示“未找到”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,580 +476,562 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：物流运费的金额汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单金额</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一名物流公司文员，需要从运单台账中统计“上海仓”发出的“已完成”运单总运费，并把结果四舍五入保留到整数元。请使用 SUMIFS 按多个条件求和，再用 ROUND 处理结果。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格输入公式，计算“上海仓”且“已完成”的运单总运费，并将总金额四舍五入到整数元。</t>
+          <t>要求：你是公司销售助理，需要根据订单台账统计『华东贸易』这一个客户的总订单金额。台账包含客户名称和订单金额。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>发货仓</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 单元格输入公式，计算客户名称为『华东贸易』的订单金额合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>328.5</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>410.2</v>
+          <t>华东贸易</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>12500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>288.8</v>
+          <t>北方物流</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>199.9</v>
+          <t>华东贸易</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>356.4</v>
+          <t>南方供应链</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>15200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>华东贸易</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：到港天数的计算</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责跟踪一批海运货物到港情况，需要根据“到港日期”计算截至今天已经到港多少天。请使用 TODAY 获取当天日期，用 DATEDIF 计算两个日期之间的天数差。</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>任务：在每个订单的右侧新增一列“到港天数”，输入公式计算从“到港日期”到今天的经过天数。假设第一个到港日期在 C2 单元格。</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流公司调度员，需要统计『上海仓』发往『北京』的已完成发货单数量。台账中包含发货仓库、目的地和状态。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SO1001</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>机械配件</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 F2 单元格输入公式，统计发货仓库为『上海仓』、目的地为『北京』且状态为『已完成』的发货单数量。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SO1002</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>塑料粒子</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>发货仓库</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SO1003</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>钢材卷板</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：包裹重量区间统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家快递网点的数据员，需要统计重量在 1 公斤到 5 公斤之间（含 1 和 5）的包裹数量，同时找出当前台账中的最大包裹重量。请使用 COUNTIFS 做多条件计数，用 MAX 找最大值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格计算重量大于等于 1 且小于等于 5 的包裹数量；再在另一个空白单元格计算最大包裹重量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>目的城市</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>重量kg</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>PK001</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>0.8</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>PK002</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1.2</v>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是跨境物流专员，需要根据发运日期和到港日期计算运输天数。如果到港日期为空，则显示『运输中』。TODAY 不是本题重点，DATEDIF 用于计算日期间隔。</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>PK003</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>3.5</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格输入公式，计算每条运单从发运日期到到港日期的天数；若到港日期为空则显示『运输中』，不要显示错误值。</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>PK004</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>苏州</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>5</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PK005</t>
+          <t>YT001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>宁波</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>6.4</v>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PK006</t>
+          <t>YT002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>合肥</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>2.1</v>
-      </c>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YT003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YT004</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：员工姓名拆分与工号提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>要求：你拿到一份员工信息表，其中“员工代码”格式为“部门-工号-姓名拼音”，例如“FIN-2024-zhangsan”。你需要提取部门代码、工号后四位和姓名拼音首字母大写前的部分。请使用 RIGHT 和 MID 完成提取。</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B2 单元格输入公式提取“员工代码”中的工号后四位；在 C2 单元格输入公式提取姓名拼音部分（从第 10 个字符开始到结尾）。</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>员工代码</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是电商运营，需要根据商品编号从商品价格表中查找单价，并计算含税金额，结果保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>FIN-2024-zhangsan</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 F2 单元格输入公式，根据 E2 中的商品编号『A1003』，从左侧表中查找对应单价，并按数量 3 计算金额，结果四舍五入保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>HR-2023-lisi</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>OPS-2025-wangwu</t>
+          <t>A1001</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>运营部</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
+          <t>保温杯</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>59.9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>A1002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>双肩包</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>129.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A1003</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>蓝牙耳机</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>A1004</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>台灯</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：产品单价查表匹配</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责电商订单核价，需要根据订单表中的“产品编号”，从产品价格表中查出对应单价。如果查不到，就显示“未找到”。请分别用 XLOOKUP 和 INDEX+MATCH 两种方式完成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格输入公式，根据指定的产品编号“P1003”查询单价；若找不到则返回“未找到”。可用 XLOOKUP，也可用 IFERROR+INDEX+MATCH。</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>无线鼠标</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>79</v>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是快递公司结算员，需要根据包裹重量判断运费等级：重量大于等于 5kg 为『重货』，否则为『轻货』。然后统计『重货』的运费合计，并用 MAX 找出最高运费。本题重点练习 IF、SUMIFS 和 MAX。</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>P1002</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>机械键盘</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>299</v>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2:D6 输入公式判断每个包裹的运费等级；在 G2 单元格统计『重货』的运费合计；在 G3 单元格用 MAX 找出最高运费。</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>P1003</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>899</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>运费等级</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>P1004</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>摄像头</t>
-        </is>
+          <t>KD001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>3.2</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>159</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>KD002</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>KD003</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>KD004</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>KD005</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1076,7 +1058,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：物流运费的金额汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单金额</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1069,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>ROUND(SUMIFS(D2:D6,B2:B6,"上海仓",C2:C6,"已完成"),0)</f>
+        <f>SUMIF(A2:A6,"华东贸易",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1083,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：到港天数的计算</t>
+          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1094,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(C2,TODAY(),"d")</f>
+        <f>COUNTIFS(A2:A6,"上海仓",B2:B6,"北京",C2:C6,"已完成")</f>
         <v/>
       </c>
     </row>
@@ -1126,7 +1108,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：包裹重量区间统计</t>
+          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1119,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(C2:C7,"&gt;=1",C2:C7,"&lt;=5")；=MAX(C2:C7)</f>
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"运输中")</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1133,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：员工姓名拆分与工号提取</t>
+          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1143,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>B2：=RIGHT(A2,4)；C2：=MID(A2,10,100)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>ROUND(XLOOKUP(E2,A2:A5,C2:C5)*3,2)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1158,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：产品单价查表匹配</t>
+          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
         </is>
       </c>
     </row>
@@ -1187,9 +1168,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>XLOOKUP("P1003",A2:A5,C2:C5,"未找到")；=IFERROR(INDEX(C2:C5,MATCH("P1003",A2:A5,0)),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>D2 输入 =IF(B2&gt;=5,"重货","轻货")；G2 输入 =SUMIFS(C2:C6,D2:D6,"重货")；G3 输入 =MAX(C2:C6)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1202,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：物流运费的金额汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单金额</t>
         </is>
       </c>
     </row>
@@ -1232,14 +1214,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。这里对 D2:D6 的运费求和，同时要求 B 列为“上海仓”、C 列为“已完成”。ROUND(数值,0) 表示四舍五入到整数位。</t>
+          <t>SUMIF 函数用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中 A2:A6 是客户名称列，条件为『华东贸易』，B2:B6 是订单金额列。公式会把所有客户名称为『华东贸易』对应订单金额相加，结果为 12500+4600+3100=20200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：到港天数的计算</t>
+          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1233,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 会返回今天的日期，并且会随日期自动更新。DATEDIF(开始日期,结束日期,单位) 可以计算两个日期之间的间隔，单位 "d" 表示天数。因此 DATEDIF(C2,TODAY(),"d") 表示从到港日期到今天的天数。</t>
+          <t>COUNTIFS 函数用于多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。本题分别用 A、B、C 三列作为条件区域，同时满足『上海仓』『北京』『已完成』的行有第2行和第6行，共 2 条。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：包裹重量区间统计</t>
+          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
         </is>
       </c>
     </row>
@@ -1270,14 +1252,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 可以按多个条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2)。这里用同一个重量区域 C2:C7 分别限制 &gt;=1 和 &lt;=5。MAX(C2:C7) 返回该区域中的最大值。</t>
+          <t>DATEDIF 用于计算两个日期之间的间隔，语法为 DATEDIF(开始日期, 结束日期, 单位)，单位『d』表示天数。当 C2 为空时，DATEDIF 会返回错误。外层用 IFERROR(表达式, 出错时显示内容) 捕获错误，因此空到港日期显示『运输中』。YT001 结果为 7 天，YT003 结果为 9 天。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：员工姓名拆分与工号提取</t>
+          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1289,14 +1271,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT(文本,字符数) 从文本右侧提取指定数量字符，A2 右侧 4 位就是工号后四位。MID(文本,开始位置,字符数) 从指定位置提取字符；A2 中“FIN-2024-”共 9 个字符，所以从第 10 位开始提取姓名拼音，100 表示取足够长，实际会取到文本结尾。</t>
+          <t>XLOOKUP 用于查找匹配，语法为 XLOOKUP(查找值, 查找区域, 返回区域)。本题在 A2:A5 中查找 E2 的值『A1003』，返回 C2:C5 中对应的单价 199。再乘以数量 3，得到 597，最后用 ROUND(数值, 2) 保留两位小数，结果为 597。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：产品单价查表匹配</t>
+          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1290,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找区域,返回区域,找不到时的返回值) 可以直接完成查表并处理错误。INDEX(返回区域,行号) 根据位置返回单价，MATCH(查找值,查找区域,0) 找到产品编号所在行号。IFERROR 用来在查不到时显示“未找到”。</t>
+          <t>IF 函数语法为 IF(条件, 真值, 假值)，B2&gt;=5 成立则显示『重货』，否则显示『轻货』。SUMIFS 用于多条件求和，这里只按一个条件统计运费等级为『重货』的运费合计，结果为 42+55=97。MAX(C2:C6) 会返回运费列最大值 55。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单金额</t>
+          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,107 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是公司销售助理，需要根据订单台账统计『华东贸易』这一个客户的总订单金额。台账包含客户名称和订单金额。</t>
+          <t>要求：你在一家物流公司做对账，需要按办事处汇总运费。数据里只统计“上海办”的运费合计。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 D2 单元格输入公式，计算客户名称为『华东贸易』的订单金额合计。</t>
+          <t>任务：在空白单元格（如G2）输入公式，计算“上海办”的运费合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>办事处</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东贸易</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>12500</v>
+          <t>上海办</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北方物流</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>8300</v>
+          <t>北京办</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>BJ001</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华东贸易</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4600</v>
+          <t>上海办</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SH002</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>南方供应链</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>15200</v>
+          <t>广州办</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>GZ001</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华东贸易</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>3100</v>
+          <t>上海办</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SH003</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -573,131 +603,121 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
+          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你是物流公司调度员，需要统计『上海仓』发往『北京』的已完成发货单数量。台账中包含发货仓库、目的地和状态。</t>
+          <t>要求：仓库需要知道重量大于30公斤的运单有多少票，方便安排叉车或人工搬运。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 F2 单元格输入公式，统计发货仓库为『上海仓』、目的地为『北京』且状态为『已完成』的发货单数量。</t>
+          <t>任务：在空白单元格（如E2）输入公式，统计重量大于30公斤的运单票数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>发货仓库</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>目的地</t>
+          <t>货物名称</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>配件</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -710,45 +730,45 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
+          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：你是跨境物流专员，需要根据发运日期和到港日期计算运输天数。如果到港日期为空，则显示『运输中』。TODAY 不是本题重点，DATEDIF 用于计算日期间隔。</t>
+          <t>要求：海运台账中记录了每票货的到港日期。你需要计算从到港日到今天已经过了多少天，用于提醒客户提货。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 E2 单元格输入公式，计算每条运单从发运日期到到港日期的天数；若到港日期为空则显示『运输中』，不要显示错误值。</t>
+          <t>任务：在D2单元格输入公式，计算BL001从到港日到今天的天数；向下填充到D4。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>提单号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>发运日期</t>
+          <t>到港日期</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>到港日期</t>
+          <t>客户</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>YT001</t>
+          <t>BL001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -758,156 +778,162 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>甲公司</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>YT002</t>
+          <t>BL002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>乙公司</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>YT003</t>
+          <t>BL003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>丙公司</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>YT004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：财务需要统计“甲公司”通过“海运”产生的运费合计，并把结果四舍五入保留到整数，方便开票。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>要求：你是电商运营，需要根据商品编号从商品价格表中查找单价，并计算含税金额，结果保留两位小数。</t>
+          <t>任务：在空白单元格（如F2）输入公式，计算客户为“甲公司”且运输方式为“海运”的运费合计，并四舍五入为整数。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 F2 单元格输入公式，根据 E2 中的商品编号『A1003』，从左侧表中查找对应单价，并按数量 3 计算金额，结果四舍五入保留两位小数。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>运输方式</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>甲公司</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>海运</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1234.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>A1001</t>
+          <t>乙公司</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>保温杯</t>
+          <t>海运</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>59.9</v>
+        <v>800.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A1002</t>
+          <t>甲公司</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>双肩包</t>
+          <t>空运</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>129.5</v>
+        <v>500.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A1003</t>
+          <t>甲公司</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>蓝牙耳机</t>
+          <t>海运</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>199</v>
+        <v>998.4400000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>A1004</t>
+          <t>丙公司</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>台灯</t>
+          <t>陆运</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43">
@@ -920,21 +946,21 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
+          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>要求：你是快递公司结算员，需要根据包裹重量判断运费等级：重量大于等于 5kg 为『重货』，否则为『轻货』。然后统计『重货』的运费合计，并用 MAX 找出最高运费。本题重点练习 IF、SUMIFS 和 MAX。</t>
+          <t>要求：你有一张港口代码对照表，需要根据运单里的港口代码查出港口名称；如果查不到，就显示“代码不存在”。同时结合到港日期计算到港天数。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 D2:D6 输入公式判断每个包裹的运费等级；在 G2 单元格统计『重货』的运费合计；在 G3 单元格用 MAX 找出最高运费。</t>
+          <t>任务：假设港口对照表在E1:F5：E列为代码，F列为港口名称，E1:F5内容为：E1=港口代码、F1=港口名称、E2=SHA、F2=上海港、E3=NGB、F3=宁波港、E4=CAN、F4=广州港、E5=TSN、F5=天津港。请在D2输入公式，根据B2的港口代码查出港口名称，查不到显示“代码不存在”。</t>
         </is>
       </c>
     </row>
@@ -946,92 +972,85 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>重量kg</t>
+          <t>港口代码</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>运费</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>运费等级</t>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>KD001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>YD101</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>SHA</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>KD002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
+          <t>YD102</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>KD003</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>YD103</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>KD004</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D52" s="4" t="inlineStr"/>
+          <t>YD104</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>KD005</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1058,7 +1077,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单金额</t>
+          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1088,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"华东贸易",B2:B6)</f>
+        <f>SUMIF(A2:A6,"上海办",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1102,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
+          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1113,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A6,"上海仓",B2:B6,"北京",C2:C6,"已完成")</f>
+        <f>COUNTIF(C2:C6,"&gt;30")</f>
         <v/>
       </c>
     </row>
@@ -1108,7 +1127,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
+          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1138,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"运输中")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1152,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
+          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1163,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(XLOOKUP(E2,A2:A5,C2:C5)*3,2)</f>
+        <f>ROUND(SUMIFS(C2:C6,A2:A6,"甲公司",B2:B6,"海运"),0)</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1177,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
+          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
         </is>
       </c>
     </row>
@@ -1168,10 +1187,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>D2 输入 =IF(B2&gt;=5,"重货","轻货")；G2 输入 =SUMIFS(C2:C6,D2:D6,"重货")；G3 输入 =MAX(C2:C6)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IFERROR(XLOOKUP(B2,$E$2:$E$5,$F$2:$F$5,"代码不存在"),"代码不存在")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1202,7 +1220,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单金额</t>
+          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
         </is>
       </c>
     </row>
@@ -1214,14 +1232,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中 A2:A6 是客户名称列，条件为『华东贸易』，B2:B6 是订单金额列。公式会把所有客户名称为『华东贸易』对应订单金额相加，结果为 12500+4600+3100=20200。</t>
+          <t>SUMIF 用于单条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是办事处列A2:A6，条件是“上海办”，求和区域是运费列C2:C6。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合多个条件的发货单数量</t>
+          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1251,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 函数用于多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。本题分别用 A、B、C 三列作为条件区域，同时满足『上海仓』『北京』『已完成』的行有第2行和第6行，共 2 条。</t>
+          <t>COUNTIF 用于单条件计数，语法为：COUNTIF(条件区域, 条件)。这里统计重量列C2:C6中大于30的单元格个数，条件写成 "&gt;30"。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算包裹到港天数并屏蔽错误</t>
+          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1270,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的间隔，语法为 DATEDIF(开始日期, 结束日期, 单位)，单位『d』表示天数。当 C2 为空时，DATEDIF 会返回错误。外层用 IFERROR(表达式, 出错时显示内容) 捕获错误，因此空到港日期显示『运输中』。YT001 结果为 7 天，YT003 结果为 9 天。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。这里开始日期是B2，结束日期是TODAY()，"d"表示按天计算。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查找单价并计算金额</t>
+          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
         </is>
       </c>
     </row>
@@ -1271,14 +1289,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 用于查找匹配，语法为 XLOOKUP(查找值, 查找区域, 返回区域)。本题在 A2:A5 中查找 E2 的值『A1003』，返回 C2:C5 中对应的单价 199。再乘以数量 3，得到 597，最后用 ROUND(数值, 2) 保留两位小数，结果为 597。</t>
+          <t>SUMIFS 支持多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。ROUND(数值, 0) 表示四舍五入到整数。组合后先求“甲公司+海运”的运费合计，再取整。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据重量区间自动判断运费等级并汇总</t>
+          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1308,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IF 函数语法为 IF(条件, 真值, 假值)，B2&gt;=5 成立则显示『重货』，否则显示『轻货』。SUMIFS 用于多条件求和，这里只按一个条件统计运费等级为『重货』的运费合计，结果为 42+55=97。MAX(C2:C6) 会返回运费列最大值 55。</t>
+          <t>XLOOKUP(查找值, 查找区域, 返回区域, 未找到时返回值) 可以直接完成查表。IFERROR 用于兜底，避免公式报错。这里若B2的代码在E2:E5中找不到，XLOOKUP返回“代码不存在”，IFERROR再保证即使出现其他错误也显示“代码不存在”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
+          <t>第 1 题：第1题：统计指定线路的运费总额</t>
         </is>
       </c>
     </row>
@@ -490,29 +490,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做对账，需要按办事处汇总运费。数据里只统计“上海办”的运费合计。</t>
+          <t>要求：你是一名物流公司对账员，需要快速统计“上海-北京”线路的运费总额。请根据下面的运费台账完成统计。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如G2）输入公式，计算“上海办”的运费合计。</t>
+          <t>任务：请在 D2 单元格输入公式，统计线路为“上海-北京”的运费总额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>办事处</t>
+          <t>线路</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>运费</t>
         </is>
@@ -521,536 +516,523 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海办</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>SH001</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京办</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>BJ001</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
+          <t>广州-深圳</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海办</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>SH002</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州办</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>GZ001</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
+          <t>杭州-南京</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海办</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>SH003</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>100</v>
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>广州-深圳</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>练习函数：COUNTIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库需要知道重量大于30公斤的运单有多少票，方便安排叉车或人工搬运。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如E2）输入公式，统计重量大于30公斤的运单票数。</t>
+          <t>要求：仓库主管想了解本周有多少票运单重量超过 1000 公斤，以便安排装卸资源。请根据运单重量台账完成统计。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 单元格输入公式，统计重量大于 1000 公斤的运单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>运单号</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>12</v>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>45</v>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>30</v>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>设备</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>68</v>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>YD005</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>YD006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：海运台账中记录了每票货的到港日期。你需要计算从到港日到今天已经过了多少天，用于提醒客户提货。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，计算BL001从到港日到今天的天数；向下填充到D4。</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>提单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责跟踪进口货物到港天数。对于已到港的货物，计算从发运日期到今天已经过了多少天；如果还没有发运日期，则显示“待发运”。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>BL001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算到港天数；若发运日期为空导致无法计算，则显示“待发运”。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>BL002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>乙公司</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>BL003</t>
+          <t>HG001</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>丙公司</t>
+          <t>2024-01-10</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>HG002</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>HG003</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>HG004</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>HG005</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：财务需要统计“甲公司”通过“海运”产生的运费合计，并把结果四舍五入保留到整数，方便开票。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如F2）输入公式，计算客户为“甲公司”且运输方式为“海运”的运费合计，并四舍五入为整数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>运输方式</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>海运</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1234.56</v>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>乙公司</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>海运</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>800.2</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售经理需要同时满足两个条件统计：统计“华东区”且“金额大于等于500”的销售总金额，以及统计满足这两个条件的订单笔数。请根据销售明细完成统计。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>空运</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>500.1</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格输入公式，统计区域为“华东区”且金额大于等于 500 的销售总金额；请在 E3 单元格输入公式，统计满足同样条件的订单笔数。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>海运</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>998.4400000000001</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>丙公司</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>陆运</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张港口代码对照表，需要根据运单里的港口代码查出港口名称；如果查不到，就显示“代码不存在”。同时结合到港日期计算到港天数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设港口对照表在E1:F5：E列为代码，F列为港口名称，E1:F5内容为：E1=港口代码、F1=港口名称、E2=SHA、F2=上海港、E3=NGB、F3=宁波港、E4=CAN、F4=广州港、E5=TSN、F5=天津港。请在D2输入公式，根据B2的港口代码查出港口名称，查不到显示“代码不存在”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>港口代码</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>YD101</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>SHA</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>YD102</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>NGB</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>YD103</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>要求：你收到一批货物编号，需要从货物信息表中查找到港城市，并计算所有货物中的最大重量，同时将最大重量四舍五入到整数。请综合运用查找、匹配、最大值和四舍五入函数完成。</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>YD104</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-12</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格输入公式，根据 D2 单元格中的货物编号“HG003”查找到港城市；请在 E3 单元格输入公式，计算所有货物中的最大重量并四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>到港城市</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>HG001</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>1250.456</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>HG002</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>980.789</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>HG003</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>1560.123</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>HG004</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>760.654</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>HG005</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>1420.987</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1077,7 +1059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
+          <t>第 1 题：第1题：统计指定线路的运费总额</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1070,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"上海办",C2:C6)</f>
+        <f>SUMIF(A2:A7,"上海-北京",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1084,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
+          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1095,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(C2:C6,"&gt;30")</f>
+        <f>COUNTIF(B2:B7,"&gt;1000")</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +1109,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
+          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1120,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待发运")</f>
         <v/>
       </c>
     </row>
@@ -1152,7 +1134,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
+          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
         </is>
       </c>
     </row>
@@ -1162,9 +1144,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>ROUND(SUMIFS(C2:C6,A2:A6,"甲公司",B2:B6,"海运"),0)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>E2: =SUMIFS(C2:C7,A2:A7,"华东区",C2:C7,"&gt;=500")；E3: =COUNTIFS(A2:A7,"华东区",C2:C7,"&gt;=500")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1160,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
+          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
         </is>
       </c>
     </row>
@@ -1187,9 +1170,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP(B2,$E$2:$E$5,$F$2:$F$5,"代码不存在"),"代码不存在")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>E2: =XLOOKUP(D2,A2:A6,B2:B6) 或 =VLOOKUP(D2,A2:B6,2,FALSE) 或 =INDEX(B2:B6,MATCH(D2,A2:A6,0))；E3: =ROUND(MAX(C2:C6),0)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1204,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定办事处的运费总额</t>
+          <t>第 1 题：第1题：统计指定线路的运费总额</t>
         </is>
       </c>
     </row>
@@ -1232,14 +1216,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是办事处列A2:A6，条件是“上海办”，求和区域是运费列C2:C6。</t>
+          <t>SUMIF 用于按单个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7 的线路列，条件是“上海-北京”，求和区域是 B2:B7 的运费列，所以结果为 120+150+130=400。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计重量超过30公斤的运单数量</t>
+          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1235,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于单条件计数，语法为：COUNTIF(条件区域, 条件)。这里统计重量列C2:C6中大于30的单元格个数，条件写成 "&gt;30"。</t>
+          <t>COUNTIF 用于按单个条件计数，语法是 COUNTIF(条件区域, 条件)。条件是“&gt;1000”，需要写成带引号的文本，所以公式为 COUNTIF(B2:B7,"&gt;1000")，结果为 3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按到港日期计算已到港天数</t>
+          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1270,14 +1254,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。这里开始日期是B2，结束日期是TODAY()，"d"表示按天计算。</t>
+          <t>DATEDIF 用于计算两个日期之间的差值，语法是 DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。TODAY() 返回今天日期。IFERROR 用于捕获错误并返回指定值，语法是 IFERROR(值, 错误时返回的内容)。当 B2 为空时 DATEDIF 会出错，因此显示“待发运”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按客户和运输方式汇总应收运费</t>
+          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
         </is>
       </c>
     </row>
@@ -1289,14 +1273,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 支持多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。ROUND(数值, 0) 表示四舍五入到整数。组合后先求“甲公司+海运”的运费合计，再取整。</t>
+          <t>SUMIFS 用于多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。COUNTIFS 用于多条件计数，语法类似。这里两个条件分别是 A 列为“华东区”和 C 列金额“&gt;=500”。满足条件的记录为张三800、赵六1200、孙八500，总金额2500，笔数3。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按港口代码查询港口名称和到港天数</t>
+          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1292,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找区域, 返回区域, 未找到时返回值) 可以直接完成查表。IFERROR 用于兜底，避免公式报错。这里若B2的代码在E2:E5中找不到，XLOOKUP返回“代码不存在”，IFERROR再保证即使出现其他错误也显示“代码不存在”。</t>
+          <t>XLOOKUP 语法是 XLOOKUP(查找值, 查找区域, 返回区域)，可直接返回对应城市；VLOOKUP 语法是 VLOOKUP(查找值, 表格区域, 返回列号, FALSE)，需要查找值在首列；INDEX+MATCH 中 MATCH 定位行号，INDEX 返回对应值。MAX 用于求最大值，ROUND 用于四舍五入，语法是 ROUND(数值, 小数位数)，0 表示保留整数。最大重量为 1560.123，四舍五入后为 1560。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定线路的运费总额</t>
+          <t>第 1 题：第1题：物流费用按城市汇总</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一名物流公司对账员，需要快速统计“上海-北京”线路的运费总额。请根据下面的运费台账完成统计。</t>
+          <t>要求：你是一家快递公司的财务助理，需要根据一张简易运费台账，统计「上海」这一列城市对应的运费总额。数据如下，请把数据粘贴到 A1:B7。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 D2 单元格输入公式，统计线路为“上海-北京”的运费总额。</t>
+          <t>任务：在 D2 单元格输入公式，计算城市为「上海」的运费总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>线路</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,61 +516,73 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>120</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>广州-深圳</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>80</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>150</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>杭州-南京</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>60</v>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>130</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>广州-深圳</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>90</v>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -583,7 +595,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
+          <t>第 2 题：第2题：仓库到货单数统计</t>
         </is>
       </c>
     </row>
@@ -597,442 +609,609 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：仓库主管想了解本周有多少票运单重量超过 1000 公斤，以便安排装卸资源。请根据运单重量台账完成统计。</t>
+          <t>要求：你负责仓库到货登记，需要统计「已到货」状态的订单有多少单。数据如下，请粘贴到 A1:B8。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 D2 单元格输入公式，统计重量大于 1000 公斤的运单数量。</t>
+          <t>任务：在 D2 单元格输入公式，统计状态为「已到货」的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>850</v>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>1200</v>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>未到货</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>980</v>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1500</v>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>1050</v>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>未到货</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>YD006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>760</v>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A007</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>未到货</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责跟踪进口货物到港天数。对于已到港的货物，计算从发运日期到今天已经过了多少天；如果还没有发运日期，则显示“待发运”。</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件统计入库重量</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式，计算到港天数；若发运日期为空导致无法计算，则显示“待发运”。</t>
+          <t>要求：你是物流园区的数据员，需要统计「上海仓」中「生鲜」类商品的入库总重量，并统计符合条件的记录数。数据如下，请粘贴到 A1:D7。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F2 单元格输入公式，统计「上海仓」且「生鲜」的总重量；在 F3 单元格输入公式，统计符合条件的记录条数。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>HG001</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>HG002</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HG003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr"/>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>纸巾</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>HG004</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>牛肉</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>HG005</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>鸡蛋</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售经理需要同时满足两个条件统计：统计“华东区”且“金额大于等于500”的销售总金额，以及统计满足这两个条件的订单笔数。请根据销售明细完成统计。</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 E2 单元格输入公式，统计区域为“华东区”且金额大于等于 500 的销售总金额；请在 E3 单元格输入公式，统计满足同样条件的订单笔数。</t>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算到港天数并防止错误</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责跟踪货物到港情况，需要根据预计到港日期计算距离今天还有多少天。如果日期为空或无效，显示「待确认」。数据如下，请粘贴到 A1:B6。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>800</v>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算预计到港日期距离今天的天数；如果无法计算，则显示「待确认」。公式可向下填充到 C6。</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>600</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>300</v>
+          <t>2026-05-20</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>1200</v>
+          <t>2026-06-01</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>900</v>
-      </c>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>500</v>
+          <t>2026-05-28</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>要求：你收到一批货物编号，需要从货物信息表中查找到港城市，并计算所有货物中的最大重量，同时将最大重量四舍五入到整数。请综合运用查找、匹配、最大值和四舍五入函数完成。</t>
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 E2 单元格输入公式，根据 D2 单元格中的货物编号“HG003”查找到港城市；请在 E3 单元格输入公式，计算所有货物中的最大重量并四舍五入到整数。</t>
+          <t>要求：你是电商运营助理，需要根据商品编号从价目表中匹配单价，并计算订单金额。若金额超过 100 元，标记为「重点订单」，否则标记为「普通订单」；金额保留 2 位小数。数据如下，请粘贴到 A1:D7，价目表放在 F1:G5。</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>到港城市</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，根据 B2 的商品编号从价目表 F2:G5 中匹配单价，用数量 C2 计算金额，并保留 2 位小数；公式可向下填充到 D6。再在 E2 单元格输入公式，若 D2 金额大于 100 显示「重点订单」，否则显示「普通订单」。</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>HG001</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>1250.456</v>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>HG002</t>
+          <t>O001</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>980.789</v>
-      </c>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>HG003</t>
+          <t>O002</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>宁波</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>1560.123</v>
-      </c>
+          <t>P1003</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>HG004</t>
+          <t>O003</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>青岛</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>760.654</v>
-      </c>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>HG005</t>
+          <t>O004</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>1420.987</v>
-      </c>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>O005</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>P1004</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>P1003</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>P1004</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1059,7 +1238,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定线路的运费总额</t>
+          <t>第 1 题：第1题：物流费用按城市汇总</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1249,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"上海-北京",B2:B7)</f>
+        <f>SUMIF(A2:A7,"上海",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1084,7 +1263,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
+          <t>第 2 题：第2题：仓库到货单数统计</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B7,"&gt;1000")</f>
+        <f>COUNTIF(B2:B8,"已到货")</f>
         <v/>
       </c>
     </row>
@@ -1109,7 +1288,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
+          <t>第 3 题：第3题：多条件统计入库重量</t>
         </is>
       </c>
     </row>
@@ -1119,9 +1298,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待发运")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F2：=SUMIFS(D2:D7,A2:A7,"上海仓",B2:B7,"生鲜")；F3：=COUNTIFS(A2:A7,"上海仓",B2:B7,"生鲜")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1134,7 +1314,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
+          <t>第 4 题：第4题：计算到港天数并防止错误</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1324,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>E2: =SUMIFS(C2:C7,A2:A7,"华东区",C2:C7,"&gt;=500")；E3: =COUNTIFS(A2:A7,"华东区",C2:C7,"&gt;=500")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(DATEDIF(TODAY(),B2,"d"),"待确认")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1160,7 +1339,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
+          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1351,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>E2: =XLOOKUP(D2,A2:A6,B2:B6) 或 =VLOOKUP(D2,A2:B6,2,FALSE) 或 =INDEX(B2:B6,MATCH(D2,A2:A6,0))；E3: =ROUND(MAX(C2:C6),0)</t>
+          <t>D2：=ROUND(C2*VLOOKUP(B2,$F$2:$G$5,2,FALSE),2)；E2：=IF(D2&gt;100,"重点订单","普通订单")</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1383,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定线路的运费总额</t>
+          <t>第 1 题：第1题：物流费用按城市汇总</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1395,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7 的线路列，条件是“上海-北京”，求和区域是 B2:B7 的运费列，所以结果为 120+150+130=400。</t>
+          <t>SUMIF 用于按条件求和，语法是 =SUMIF(条件区域,条件,求和区域)。这里条件区域是 A2:A7，条件是「上海」，求和区域是 B2:B7。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计重量超过1000公斤的运单数量</t>
+          <t>第 2 题：第2题：仓库到货单数统计</t>
         </is>
       </c>
     </row>
@@ -1235,14 +1414,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按单个条件计数，语法是 COUNTIF(条件区域, 条件)。条件是“&gt;1000”，需要写成带引号的文本，所以公式为 COUNTIF(B2:B7,"&gt;1000")，结果为 3。</t>
+          <t>COUNTIF 用于按条件计数，语法是 =COUNTIF(条件区域,条件)。这里统计 B2:B8 中等于「已到货」的单元格个数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数并处理错误</t>
+          <t>第 3 题：第3题：多条件统计入库重量</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1433,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的差值，语法是 DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。TODAY() 返回今天日期。IFERROR 用于捕获错误并返回指定值，语法是 IFERROR(值, 错误时返回的内容)。当 B2 为空时 DATEDIF 会出错，因此显示“待发运”。</t>
+          <t>SUMIFS 用于多条件求和，语法是 =SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)。COUNTIFS 用于多条件计数，语法类似。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按部门和金额条件汇总销售金额</t>
+          <t>第 4 题：第4题：计算到港天数并防止错误</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1452,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。COUNTIFS 用于多条件计数，语法类似。这里两个条件分别是 A 列为“华东区”和 C 列金额“&gt;=500”。满足条件的记录为张三800、赵六1200、孙八500，总金额2500，笔数3。</t>
+          <t>TODAY 返回今天日期；DATEDIF 计算两个日期间隔，"d" 表示天数；IFERROR 在公式出错时返回指定内容。思路是：用 TODAY 和到港日期计算天数，日期为空时 DATEDIF 出错，IFERROR 显示「待确认」。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据货物编号查找到港城市并计算最重货物</t>
+          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1471,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法是 XLOOKUP(查找值, 查找区域, 返回区域)，可直接返回对应城市；VLOOKUP 语法是 VLOOKUP(查找值, 表格区域, 返回列号, FALSE)，需要查找值在首列；INDEX+MATCH 中 MATCH 定位行号，INDEX 返回对应值。MAX 用于求最大值，ROUND 用于四舍五入，语法是 ROUND(数值, 小数位数)，0 表示保留整数。最大重量为 1560.123，四舍五入后为 1560。</t>
+          <t>VLOOKUP 用于按列查找，语法是 =VLOOKUP(查找值,查找区域,返回第几列,精确匹配)。这里用 B2 查找商品编号，返回价目表第 2 列单价，再乘以数量并用 ROUND 保留 2 位小数。IF 用于条件判断。也可以用 XLOOKUP：=ROUND(C2*XLOOKUP(B2,$F$2:$F$5,$G$2:$G$5),2)，或用 INDEX+MATCH：=ROUND(C2*INDEX($G$2:$G$5,MATCH(B2,$F$2:$F$5,0)),2)。MAX 可在需要防止负数或取最大金额时配合使用，例如 =MAX(0,D2)。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流费用按城市汇总</t>
+          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
         </is>
       </c>
     </row>
@@ -490,302 +490,347 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家快递公司的财务助理，需要根据一张简易运费台账，统计「上海」这一列城市对应的运费总额。数据如下，请把数据粘贴到 A1:B7。</t>
+          <t>要求：你负责管理一个物流入库台账。现在需要快速计算「上海仓」的总入库重量，方便安排后续车辆。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算城市为「上海」的运费总和。</t>
+          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，计算「上海仓」的入库重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>城市</t>
+          <t>站点</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>运费</t>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>入库重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：仓库到货单数统计</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：进口货物台账里记录了到港日期。公司规定：到港超过 30 天视为超期。需要根据到港日期计算到今天的天数，并判断是否超期。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C5，请在 D2 单元格计算 A001 货物从到港到今天的天数，在 E2 单元格判断是否超期（超过30天显示"超期"，否则显示"正常"）。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责仓库到货登记，需要统计「已到货」状态的订单有多少单。数据如下，请粘贴到 A1:B8。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，统计状态为「已到货」的订单数量。</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>电子元件</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
+          <t>机械配件</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>未到货</t>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>已到货</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>已到货</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>未到货</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>已到货</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>A007</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>未到货</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：出库明细表里记录了不同仓库、不同货物类型的出库数量。现在需要计算「上海仓」且货物类型为「纸箱」的总出库数量。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C7，请在 E2 单元格输入公式，计算「上海仓」且「纸箱」的总出库数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>货物类型</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>出库数量</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件统计入库重量</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流园区的数据员，需要统计「上海仓」中「生鲜」类商品的入库总重量，并统计符合条件的记录数。数据如下，请粘贴到 A1:D7。</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，统计「上海仓」且「生鲜」的总重量；在 F3 单元格输入公式，统计符合条件的记录条数。</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -796,422 +841,240 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>纸巾</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>牛肉</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>鸡蛋</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：订单重量台账中记录了每笔订单的重量。现在需要统计重量大于等于 100 公斤的订单笔数，并找出最重的一笔订单重量。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C6，请在 E2 单元格统计订单重量大于等于 100 的订单笔数，在 E3 单元格找出最大订单重量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>订单重量</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算到港天数并防止错误</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>O001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>甲公司</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责跟踪货物到港情况，需要根据预计到港日期计算距离今天还有多少天。如果日期为空或无效，显示「待确认」。数据如下，请粘贴到 A1:B6。</t>
-        </is>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>O002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>乙公司</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算预计到港日期距离今天的天数；如果无法计算，则显示「待确认」。公式可向下填充到 C6。</t>
-        </is>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>O003</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>丙公司</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
-        </is>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>O004</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>丁公司</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>O005</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
+          <t>戊公司</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>G002</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>G003</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>G004</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>G005</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：货物重量对照表中记录了编号和重量。现在需要根据编号快速查询重量，如果编号不存在，则显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C5，请在 E2 输入要查询的编号 P003，在 F2 单元格用 XLOOKUP 查询对应重量，并用 IFERROR 处理查不到时显示「未找到」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是电商运营助理，需要根据商品编号从价目表中匹配单价，并计算订单金额。若金额超过 100 元，标记为「重点订单」，否则标记为「普通订单」；金额保留 2 位小数。数据如下，请粘贴到 A1:D7，价目表放在 F1:G5。</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，根据 B2 的商品编号从价目表 F2:G5 中匹配单价，用数量 C2 计算金额，并保留 2 位小数；公式可向下填充到 D6。再在 E2 单元格输入公式，若 D2 金额大于 100 显示「重点订单」，否则显示「普通订单」。</t>
-        </is>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>泡沫箱</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>O001</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>O002</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>P1003</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>O003</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>P1002</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>O004</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>O005</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>P1004</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr"/>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>P1002</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>P1003</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>P1004</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr"/>
-      <c r="D65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1238,7 +1101,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流费用按城市汇总</t>
+          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1112,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"上海",B2:B7)</f>
+        <f>SUMIF(A2:A6,"上海仓",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1263,7 +1126,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：仓库到货单数统计</t>
+          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1273,9 +1136,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIF(B2:B8,"已到货")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2：=DATEDIF(C2,TODAY(),"d")；E2：=IF(D2&gt;30,"超期","正常")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1288,7 +1152,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计入库重量</t>
+          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
         </is>
       </c>
     </row>
@@ -1298,10 +1162,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>F2：=SUMIFS(D2:D7,A2:A7,"上海仓",B2:B7,"生鲜")；F3：=COUNTIFS(A2:A7,"上海仓",B2:B7,"生鲜")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"纸箱")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1314,7 +1177,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数并防止错误</t>
+          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
         </is>
       </c>
     </row>
@@ -1324,9 +1187,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(DATEDIF(TODAY(),B2,"d"),"待确认")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>E2：=COUNTIF(C2:C6,"&gt;=100")；E3：=MAX(C2:C6)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1339,7 +1203,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
+          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1213,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>D2：=ROUND(C2*VLOOKUP(B2,$F$2:$G$5,2,FALSE),2)；E2：=IF(D2&gt;100,"重点订单","普通订单")</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IFERROR(XLOOKUP(E2,A2:A5,C2:C5),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1383,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流费用按城市汇总</t>
+          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1258,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按条件求和，语法是 =SUMIF(条件区域,条件,求和区域)。这里条件区域是 A2:A7，条件是「上海」，求和区域是 B2:B7。</t>
+          <t>SUMIF 用于按一个条件求和。语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6 的站点列，条件是 "上海仓"，求和区域是 C2:C6 的入库重量列。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：仓库到货单数统计</t>
+          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1414,14 +1277,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法是 =COUNTIF(条件区域,条件)。这里统计 B2:B8 中等于「已到货」的单元格个数。</t>
+          <t>DATEDIF 计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)，单位 "d" 表示天数；TODAY() 返回当前日期。IF 用于条件判断，语法为 IF(条件, 成立时的值, 不成立时的值)。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计入库重量</t>
+          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
         </is>
       </c>
     </row>
@@ -1433,14 +1296,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法是 =SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)。COUNTIFS 用于多条件计数，语法类似。</t>
+          <t>SUMIFS 用于多条件求和。语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。这里求和区域是 C2:C7，第一个条件是 A 列等于 "上海仓"，第二个条件是 B 列等于 "纸箱"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数并防止错误</t>
+          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
         </is>
       </c>
     </row>
@@ -1452,14 +1315,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY 返回今天日期；DATEDIF 计算两个日期间隔，"d" 表示天数；IFERROR 在公式出错时返回指定内容。思路是：用 TODAY 和到港日期计算天数，日期为空时 DATEDIF 出错，IFERROR 显示「待确认」。</t>
+          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)，条件 "&gt;=100" 表示大于等于 100。MAX 用于返回区域中的最大值，语法为 MAX(区域)。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查表匹配商品单价并计算金额</t>
+          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1334,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 用于按列查找，语法是 =VLOOKUP(查找值,查找区域,返回第几列,精确匹配)。这里用 B2 查找商品编号，返回价目表第 2 列单价，再乘以数量并用 ROUND 保留 2 位小数。IF 用于条件判断。也可以用 XLOOKUP：=ROUND(C2*XLOOKUP(B2,$F$2:$F$5,$G$2:$G$5),2)，或用 INDEX+MATCH：=ROUND(C2*INDEX($G$2:$G$5,MATCH(B2,$F$2:$F$5,0)),2)。MAX 可在需要防止负数或取最大金额时配合使用，例如 =MAX(0,D2)。</t>
+          <t>XLOOKUP 用于查找匹配值，语法为 XLOOKUP(查找值, 查找区域, 返回区域)，这里在 A2:A5 中查找 E2，返回 C2:C5 中对应的重量。IFERROR 用于捕获错误，语法为 IFERROR(表达式, 出错时的值)，当编号不存在时显示「未找到」。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,31 +490,31 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责管理一个物流入库台账。现在需要快速计算「上海仓」的总入库重量，方便安排后续车辆。</t>
+          <t>要求：你是仓库管理员，需要统计「上海仓」发出的总重量。请使用 SUMIF 函数按仓库名称汇总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，计算「上海仓」的入库重量合计。</t>
+          <t>任务：在任意空白单元格（例如 E2）输入公式，计算「上海仓」发出的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>站点</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>入库重量</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
+          <t>A商品</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
+          <t>B商品</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -556,11 +556,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>木箱</t>
+          <t>C商品</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>托盘</t>
+          <t>D商品</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -586,495 +586,493 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>托盘</t>
+          <t>E商品</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>F商品</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：进口货物台账里记录了到港日期。公司规定：到港超过 30 天视为超期。需要根据到港日期计算到今天的天数，并判断是否超期。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单数量条件计数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C5，请在 D2 单元格计算 A001 货物从到港到今天的天数，在 E2 单元格判断是否超期（超过30天显示"超期"，否则显示"正常"）。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是销售助理，需要统计「华东区」且订单金额大于等于 1000 的订单数量。请使用 COUNTIFS 函数完成多条件计数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>电子元件</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格（例如 E2）输入公式，统计区域为「华东区」且金额大于等于 1000 的订单数。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>机械配件</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>A004</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A007</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：出库明细表里记录了不同仓库、不同货物类型的出库数量。现在需要计算「上海仓」且货物类型为「纸箱」的总出库数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C7，请在 E2 单元格输入公式，计算「上海仓」且「纸箱」的总出库数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>货物类型</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>出库数量</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>50</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>30</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流专员，需要根据「发货日期」计算截至今天的在途天数。如果发货日期为空或格式错误，则显示「待确认」。请使用 DATEDIF、TODAY 和 IFERROR 组合完成。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>40</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式并向下填充，计算每张运单从发货日期到今天的在途天数；若出错则显示「待确认」。</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>70</v>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>20</v>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>10</v>
+          <t>2024-05-10</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：订单重量台账中记录了每笔订单的重量。现在需要统计重量大于等于 100 公斤的订单笔数，并找出最重的一笔订单重量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C6，请在 E2 单元格统计订单重量大于等于 100 的订单笔数，在 E3 单元格找出最大订单重量。</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>订单重量</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：产品编号提取与最大重量</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>O001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>80</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是产品数据管理员，需要从产品编号中提取中间 3 位作为批次号，并找出所有产品中的最大重量。请使用 MID、RIGHT 和 MAX 函数。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>O002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>乙公司</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>120</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式提取 B2 对应产品编号的第 6 到第 8 位（即批次号）；在 D2 单元格输入公式计算重量列的最大值。</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>O003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>丙公司</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>95</v>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>O004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>丁公司</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>150</v>
+          <t>P2024A001</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>O005</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>戊公司</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>110</v>
+          <t>P2024B002</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>18.3</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>P2024C003</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>P2024D004</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>P2024E005</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：货物重量对照表中记录了编号和重量。现在需要根据编号快速查询重量，如果编号不存在，则显示「未找到」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C5，请在 E2 输入要查询的编号 P003，在 F2 单元格用 XLOOKUP 查询对应重量，并用 IFERROR 处理查不到时显示「未找到」。</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：员工工资等级查询</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>12</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是人事专员，需要根据员工工号从工资表中查询对应工资，并判断工资是否达到 8000 元，达到显示「高薪」，否则显示「普通」。请使用 VLOOKUP 和 IF 函数。</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>25</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 B8 单元格输入工号「E003」，在 C8 单元格用 VLOOKUP 查询该工号对应工资，在 D8 单元格用 IF 判断工资是否大于等于 8000，若是显示「高薪」，否则显示「普通」。</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>18</v>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>工资</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>E001</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>泡沫箱</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>6</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>E005</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1101,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1110,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"上海仓",C2:C6)</f>
+        <f>SUMIF(A2:A7,"上海仓",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1126,7 +1124,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
+          <t>第 2 题：第2题：订单数量条件计数</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1134,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>D2：=DATEDIF(C2,TODAY(),"d")；E2：=IF(D2&gt;30,"超期","正常")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>COUNTIFS(B2:B8,"华东区",C2:C8,"&gt;=1000")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1152,7 +1149,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1160,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"纸箱")</f>
+        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待确认")</f>
         <v/>
       </c>
     </row>
@@ -1177,7 +1174,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
+          <t>第 4 题：第4题：产品编号提取与最大重量</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1186,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>E2：=COUNTIF(C2:C6,"&gt;=100")；E3：=MAX(C2:C6)</t>
+          <t>C2: =MID(A2,6,3)  D2: =MAX(B2:B6)</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1200,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
+          <t>第 5 题：第5题：员工工资等级查询</t>
         </is>
       </c>
     </row>
@@ -1213,9 +1210,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP(E2,A2:A5,C2:C5),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>C8: =VLOOKUP(B8,A2:C6,3,FALSE)  D8: =IF(C8&gt;=8000,"高薪","普通")</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1246,7 +1244,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某物流站点的入库重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1258,14 +1256,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按一个条件求和。语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6 的站点列，条件是 "上海仓"，求和区域是 C2:C6 的入库重量列。</t>
+          <t>SUMIF 函数语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7（仓库列），条件是「上海仓」，求和区域是 C2:C7（重量列），因此可得到上海仓所有商品重量之和 120+150+60=330 kg。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并判断是否超期</t>
+          <t>第 2 题：第2题：订单数量条件计数</t>
         </is>
       </c>
     </row>
@@ -1277,14 +1275,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)，单位 "d" 表示天数；TODAY() 返回当前日期。IF 用于条件判断，语法为 IF(条件, 成立时的值, 不成立时的值)。</t>
+          <t>COUNTIFS 函数语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。本案例有两个条件：B2:B8 等于「华东区」，C2:C8 大于等于 1000。满足条件的订单为 A001、A003、A006，共 3 单。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库和货物类型汇总出库数量</t>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
         </is>
       </c>
     </row>
@@ -1296,14 +1294,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和。语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。这里求和区域是 C2:C7，第一个条件是 A 列等于 "上海仓"，第二个条件是 B 列等于 "纸箱"。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。IFERROR(值, 错误时显示内容) 用于捕获错误。当 B2 为空或非日期时，DATEDIF 会报错，此时显示「待确认」；否则返回在途天数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计符合条件的订单数量并计算平均重量</t>
+          <t>第 4 题：第4题：产品编号提取与最大重量</t>
         </is>
       </c>
     </row>
@@ -1315,14 +1313,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)，条件 "&gt;=100" 表示大于等于 100。MAX 用于返回区域中的最大值，语法为 MAX(区域)。</t>
+          <t>MID(文本, 起始位置, 截取长度) 从文本中指定位置开始截取字符。这里 A2 的第 6 位开始取 3 个字符，得到如「A00」「B00」等批次号。MAX(区域) 返回区域中的最大值，即重量列最大值 22.1 kg。RIGHT 函数可用于从右侧截取，但本题提取中间字符更适合 MID。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP 按货物编号查询重量并处理查不到的情况</t>
+          <t>第 5 题：第5题：员工工资等级查询</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1332,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 用于查找匹配值，语法为 XLOOKUP(查找值, 查找区域, 返回区域)，这里在 A2:A5 中查找 E2，返回 C2:C5 中对应的重量。IFERROR 用于捕获错误，语法为 IFERROR(表达式, 出错时的值)，当编号不存在时显示「未找到」。</t>
+          <t>VLOOKUP(查找值, 查找区域, 返回列号, 精确匹配) 在区域首列查找 B8 的值，返回第 3 列工资。FALSE 表示精确匹配。IF(条件, 真值, 假值) 判断工资是否 &gt;=8000。E003 对应工资 8800，因此 D8 显示「高薪」。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,76 +476,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIF</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是仓库管理员，需要统计不同仓库中「电子类」商品的重量合计，并把结果保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，需要统计「上海仓」发出的总重量。请使用 SUMIF 函数按仓库名称汇总重量。</t>
+          <t>任务：在数据区域外的单元格中，计算「上海仓」且「商品类别」为「电子类」的重量合计，并四舍五入保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格（例如 E2）输入公式，计算「上海仓」发出的总重量。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>商品类别</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>电子类</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>A商品</t>
+          <t>服装类</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>120</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>B商品</t>
+          <t>服装类</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>80</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8">
@@ -556,11 +564,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>C商品</t>
+          <t>电子类</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>150</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
@@ -571,508 +579,508 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>D商品</t>
+          <t>电子类</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>90</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>E商品</t>
+          <t>电子类</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>60</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>F商品</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单笔数统计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是销售助理，需要统计每个销售员在指定日期范围内完成的订单笔数，并用IFERROR避免错误值显示。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：在数据区域外的单元格中，统计「张三」在2024/5/1至2024/5/5期间、状态为「已完成」的订单笔数。若公式出错则显示0。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是销售助理，需要统计「华东区」且订单金额大于等于 1000 的订单数量。请使用 COUNTIFS 函数完成多条件计数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>订单日期</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>订单状态</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格（例如 E2）输入公式，统计区域为「华东区」且金额大于等于 1000 的订单数。</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/1</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/2</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1200</v>
+          <t>2024/5/3</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>800</v>
+          <t>2024/5/4</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1500</v>
+          <t>2024/5/5</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华北区</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1000</v>
+          <t>2024/5/6</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2000</v>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>A007</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1100</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：到港天数计算</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流跟单员，需要根据货物到港日期计算截至今天已经到港多少天。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在数据区域外的单元格中，计算运单号「YD001」的货物从到港日期到今天已经经过的天数。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流专员，需要根据「发货日期」计算截至今天的在途天数。如果发货日期为空或格式错误，则显示「待确认」。请使用 DATEDIF、TODAY 和 IFERROR 组合完成。</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>轴承</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式并向下填充，计算每张运单从发货日期到今天的在途天数；若出错则显示「待确认」。</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>电机</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/10</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>钢材</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>电缆</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2024/5/25</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按商品编号查价格</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是采购专员，需要根据商品编号从价格表中查出对应单价，如果查不到则显示“无此商品”。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：在数据区域外的单元格中，根据商品编号「A1003」查找对应单价；如果找不到，显示“无此商品”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A1001</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>打印纸</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>A1002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A1003</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>A1004</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：产品编号提取与最大重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是产品数据管理员，需要从产品编号中提取中间 3 位作为批次号，并找出所有产品中的最大重量。请使用 MID、RIGHT 和 MAX 函数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式提取 B2 对应产品编号的第 6 到第 8 位（即批次号）；在 D2 单元格输入公式计算重量列的最大值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>P2024A001</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>P2024B002</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>18.3</v>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>P2024C003</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>9.800000000000001</v>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>P2024D004</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>22.1</v>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是客服人员，需要根据客户姓名从客户台账中查找客户电话。由于姓名列在电话列右边，适合用INDEX+MATCH组合。</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>P2024E005</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>15.6</v>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在数据区域外的单元格中，根据客户姓名「赵强」查找对应客户电话。</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>客户编号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>客户电话</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>王明</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：员工工资等级查询</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>李华</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是人事专员，需要根据员工工号从工资表中查询对应工资，并判断工资是否达到 8000 元，达到显示「高薪」，否则显示「普通」。请使用 VLOOKUP 和 IF 函数。</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>赵强</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B8 单元格输入工号「E003」，在 C8 单元格用 VLOOKUP 查询该工号对应工资，在 D8 单元格用 IF 判断工资是否大于等于 8000，若是显示「高薪」，否则显示「普通」。</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>13600004444</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>孙丽</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>工号</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>工资</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>9500</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>8800</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>E005</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1099,7 +1107,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1118,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"上海仓",C2:C7)</f>
+        <f>ROUND(SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"电子类"),1)</f>
         <v/>
       </c>
     </row>
@@ -1124,7 +1132,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+          <t>第 2 题：第2题：订单笔数统计</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1143,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B8,"华东区",C2:C8,"&gt;=1000")</f>
+        <f>IFERROR(COUNTIFS(A2:A7,"张三",B2:B7,"&gt;=2024/5/1",B2:B7,"&lt;=2024/5/5",C2:C7,"已完成"),0)</f>
         <v/>
       </c>
     </row>
@@ -1149,7 +1157,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+          <t>第 3 题：第3题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1168,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待确认")</f>
+        <f>DATEDIF(C2,TODAY(),"D")</f>
         <v/>
       </c>
     </row>
@@ -1174,7 +1182,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：产品编号提取与最大重量</t>
+          <t>第 4 题：第4题：按商品编号查价格</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1192,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =MID(A2,6,3)  D2: =MAX(B2:B6)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(VLOOKUP("A1003",A2:C5,3,FALSE),"无此商品")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：员工工资等级查询</t>
+          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1210,10 +1217,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>C8: =VLOOKUP(B8,A2:C6,3,FALSE)  D8: =IF(C8&gt;=8000,"高薪","普通")</t>
-        </is>
+      <c r="B18" s="2">
+        <f>INDEX(B2:B5,MATCH("赵强",C2:C5,0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1244,7 +1250,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1262,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7（仓库列），条件是「上海仓」，求和区域是 C2:C7（重量列），因此可得到上海仓所有商品重量之和 120+150+60=330 kg。</t>
+          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)。这里求和区域是C列重量，条件区域A列限制为“上海仓”，条件区域B列限制为“电子类”。ROUND用于四舍五入，语法为ROUND(数值,小数位数)，1表示保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+          <t>第 2 题：第2题：订单笔数统计</t>
         </is>
       </c>
     </row>
@@ -1275,14 +1281,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 函数语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。本案例有两个条件：B2:B8 等于「华东区」，C2:C8 大于等于 1000。满足条件的订单为 A001、A003、A006，共 3 单。</t>
+          <t>COUNTIFS用于多条件计数，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2...)。这里用A列限制销售员为“张三”，B列用两个条件限制日期区间，C列限制状态为“已完成”。IFERROR用于捕获错误，语法为IFERROR(表达式,出错时返回的值)，这里出错时返回0。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+          <t>第 3 题：第3题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1300,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。IFERROR(值, 错误时显示内容) 用于捕获错误。当 B2 为空或非日期时，DATEDIF 会报错，此时显示「待确认」；否则返回在途天数。</t>
+          <t>DATEDIF用于计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,返回类型)，"D"表示返回天数。TODAY()返回当前日期，不需要参数。注意开始日期要早于结束日期，否则可能出错。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：产品编号提取与最大重量</t>
+          <t>第 4 题：第4题：按商品编号查价格</t>
         </is>
       </c>
     </row>
@@ -1313,14 +1319,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID(文本, 起始位置, 截取长度) 从文本中指定位置开始截取字符。这里 A2 的第 6 位开始取 3 个字符，得到如「A00」「B00」等批次号。MAX(区域) 返回区域中的最大值，即重量列最大值 22.1 kg。RIGHT 函数可用于从右侧截取，但本题提取中间字符更适合 MID。</t>
+          <t>VLOOKUP用于按列查找，语法为VLOOKUP(查找值,查找区域,返回第几列,是否精确匹配)。这里查找值“A1003”在A列，查找区域A2:C5，返回第3列单价，FALSE表示精确匹配。IFERROR用于查不到时返回“无此商品”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：员工工资等级查询</t>
+          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1338,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 查找区域, 返回列号, 精确匹配) 在区域首列查找 B8 的值，返回第 3 列工资。FALSE 表示精确匹配。IF(条件, 真值, 假值) 判断工资是否 &gt;=8000。E003 对应工资 8800，因此 D8 显示「高薪」。</t>
+          <t>INDEX用于返回区域中指定位置的值，语法为INDEX(区域,行号)。MATCH用于查找值在区域中的位置，语法为MATCH(查找值,查找区域,匹配类型)，0表示精确匹配。这里MATCH找到“赵强”在C2:C5中的第3行，INDEX再从B2:B5中返回第3个值，即客户电话。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,84 +476,61 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是仓库管理员，需要统计不同仓库中「电子类」商品的重量合计，并把结果保留1位小数。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在数据区域外的单元格中，计算「上海仓」且「商品类别」为「电子类」的重量合计，并四舍五入保留1位小数。</t>
+          <t>要求：你是一家物流公司的数据员，需要按仓库名称汇总出库重量，先练习单条件求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，计算所有“上海仓”的出库重量总和。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>仓库</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>商品类别</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>电子类</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>12.5</v>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>出库重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>服装类</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8.199999999999999</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>服装类</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>5.3</v>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -562,525 +539,508 @@
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>电子类</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>7.8</v>
+      <c r="B8" s="4" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>电子类</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>10.1</v>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>430</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>电子类</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>6.4</v>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>760</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：订单笔数统计</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是销售助理，需要统计每个销售员在指定日期范围内完成的订单笔数，并用IFERROR避免错误值显示。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在数据区域外的单元格中，统计「张三」在2024/5/1至2024/5/5期间、状态为「已完成」的订单笔数。若公式出错则显示0。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>订单日期</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>订单状态</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责记录每个订单的到货状态，需要统计“异常”的订单数量，为后续跟进做准备。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/1</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，统计到货状态为“异常”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/2</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>到货状态</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>DD001</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024/5/3</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>未完成</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>DD002</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024/5/4</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>异常</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>DD003</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2024/5/5</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>DD004</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2024/5/6</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>异常</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>DD005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>DD006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：到港天数计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流跟单员，需要根据货物到港日期计算截至今天已经到港多少天。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在数据区域外的单元格中，计算运单号「YD001」的货物从到港日期到今天已经经过的天数。</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：客服需要根据货物编码查询单价，如果编码不存在，要显示“未找到”，避免出现错误值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 输入货物编码 A1004，在 H2 单元格输入公式，查询该编码对应的单价；若查不到则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>货物编码</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>货物名称</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>轴承</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>电机</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/10</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>A1001</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/18</t>
-        </is>
+          <t>打印纸</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>25.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>A1002</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>电缆</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2024/5/25</t>
-        </is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A1003</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>A1004</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>中性笔</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A1005</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>档案盒</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按商品编号查价格</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是采购专员，需要根据商品编号从价格表中查出对应单价，如果查不到则显示“无此商品”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在数据区域外的单元格中，根据商品编号「A1003」查找对应单价；如果找不到，显示“无此商品”。</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>A1001</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>打印纸</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>25.5</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓储管理中需要计算每批货物从入库到今天已经存放了多少天，便于判断是否超期。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>A1002</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>3.2</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算 PC001 从入库日期到今天的在库天数，并向下填充。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>A1003</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>8.800000000000001</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>入库日期</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>在库天数</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>A1004</t>
+          <t>PC001</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>19.9</v>
-      </c>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>PC002</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-12</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>PC003</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>PC004</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是客服人员，需要根据客户姓名从客户台账中查找客户电话。由于姓名列在电话列右边，适合用INDEX+MATCH组合。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在数据区域外的单元格中，根据客户姓名「赵强」查找对应客户电话。</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>客户电话</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>客户姓名</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>王明</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张货物信息表，需要根据货物编码查找货物名称，练习比 VLOOKUP 更灵活的 INDEX+MATCH 组合。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>李华</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 输入货物编码 B2004，在 H2 单元格输入公式，查找并返回该编码对应的货物名称。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>赵强</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>货物编码</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>供应商</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>B2001</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>13600004444</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>孙丽</t>
+          <t>顺达包装</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>B2002</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>胶带</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>顺达包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>B2003</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>气泡膜</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>安捷包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>B2004</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>缠绕膜</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>安捷包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>B2005</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>标签纸</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>永盛印刷</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1107,7 +1067,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1078,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>ROUND(SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"电子类"),1)</f>
+        <f>SUMIF(A2:A7,"上海仓",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1132,7 +1092,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单笔数统计</t>
+          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1103,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IFERROR(COUNTIFS(A2:A7,"张三",B2:B7,"&gt;=2024/5/1",B2:B7,"&lt;=2024/5/5",C2:C7,"已完成"),0)</f>
+        <f>COUNTIF(B2:B7,"异常")</f>
         <v/>
       </c>
     </row>
@@ -1157,7 +1117,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数计算</t>
+          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(C2,TODAY(),"D")</f>
+        <f>IFERROR(VLOOKUP(G2,A2:C6,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1142,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查价格</t>
+          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1153,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP("A1003",A2:C5,3,FALSE),"无此商品")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1207,7 +1167,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
+          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1178,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(B2:B5,MATCH("赵强",C2:C5,0))</f>
+        <f>INDEX(B2:B6,MATCH(G2,A2:A6,0))</f>
         <v/>
       </c>
     </row>
@@ -1250,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
         </is>
       </c>
     </row>
@@ -1262,14 +1222,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)。这里求和区域是C列重量，条件区域A列限制为“上海仓”，条件区域B列限制为“电子类”。ROUND用于四舍五入，语法为ROUND(数值,小数位数)，1表示保留1位小数。</t>
+          <t>SUMIF 用于单条件求和，语法是 =SUMIF(条件区域, 条件, 求和区域)。这里条件区域 A2:A7 里找出“上海仓”，再对对应 B2:B7 的数值求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单笔数统计</t>
+          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
         </is>
       </c>
     </row>
@@ -1281,14 +1241,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS用于多条件计数，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2...)。这里用A列限制销售员为“张三”，B列用两个条件限制日期区间，C列限制状态为“已完成”。IFERROR用于捕获错误，语法为IFERROR(表达式,出错时返回的值)，这里出错时返回0。</t>
+          <t>COUNTIF 用于单条件计数，语法是 =COUNTIF(条件区域, 条件)。它会统计 B2:B7 中等于“异常”的单元格个数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数计算</t>
+          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1260,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF用于计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,返回类型)，"D"表示返回天数。TODAY()返回当前日期，不需要参数。注意开始日期要早于结束日期，否则可能出错。</t>
+          <t>VLOOKUP 按首列查找并返回指定列的值，语法 =VLOOKUP(查找值, 查找区域, 返回列号, FALSE)。IFERROR 用来捕获查找失败产生的错误，语法 =IFERROR(内容, 错误时显示值)。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按商品编号查价格</t>
+          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
         </is>
       </c>
     </row>
@@ -1319,14 +1279,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP用于按列查找，语法为VLOOKUP(查找值,查找区域,返回第几列,是否精确匹配)。这里查找值“A1003”在A列，查找区域A2:C5，返回第3列单价，FALSE表示精确匹配。IFERROR用于查不到时返回“无此商品”。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF 用于计算两个日期之间的差值，语法 =DATEDIF(开始日期, 结束日期, 单位)，"d" 表示按天数计算。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH反向查找客户电话</t>
+          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1298,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX用于返回区域中指定位置的值，语法为INDEX(区域,行号)。MATCH用于查找值在区域中的位置，语法为MATCH(查找值,查找区域,匹配类型)，0表示精确匹配。这里MATCH找到“赵强”在C2:C5中的第3行，INDEX再从B2:B5中返回第3个值，即客户电话。</t>
+          <t>MATCH 返回查找值在区域中的相对位置，语法 =MATCH(查找值, 查找区域, 0)，0 表示精确匹配。INDEX 根据位置返回区域中的值，语法 =INDEX(返回区域, 位置)。两者组合可以实现灵活查表。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家物流公司的数据员，需要按仓库名称汇总出库重量，先练习单条件求和。</t>
+          <t>要求：你在一家物流公司做台账，需要统计『上海仓』的入库总重量。数据在 A1:B6，A列是仓库，B列是重量(kg)。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算所有“上海仓”的出库重量总和。</t>
+          <t>任务：在 D2 单元格输入公式，计算『上海仓』的入库总重量。</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>出库重量(kg)</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,17 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>850</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -540,507 +540,384 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>430</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>760</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责到港货物台账，需要先算出货物从到港到今天已经存放了多少天，再按每天 3.5 元计算仓储费，结果保留 2 位小数。数据在 A1:C4，A列是货物编号，B列是到港日期(文本日期)，C列是货物名称。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设今天是 2024-03-20。在 D2 单元格输入公式，计算 C001 的到港天数；在 E2 单元格输入公式，计算 C001 的仓储费并保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责记录每个订单的到货状态，需要统计“异常”的订单数量，为后续跟进做准备。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，统计到货状态为“异常”的订单数量。</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>到货状态</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DD001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>托盘</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DD002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>DD003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>DD004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>异常</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>DD005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>异常</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>练习函数：IF</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>DD006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在电商仓库做库存管理，需要根据现有库存数量判断是否低于安全线。规则：库存小于 50 显示『需补货』，否则显示『正常』。数据在 A1:B5，A列是商品，B列是库存。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，判断 A4纸 是否需要补货，并向下填充到 C5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A4纸</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服需要根据货物编码查询单价，如果编码不存在，要显示“未找到”，避免出现错误值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 输入货物编码 A1004，在 H2 单元格输入公式，查询该编码对应的单价；若查不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>货物编码</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>A1001</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>打印纸</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A1002</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A1003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>16.9</v>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>A1004</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>中性笔</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张发货记录表，编码格式为『WH-仓库编号-序号』，例如 WH-SH-001 表示上海仓。需要提取中间的仓库编号，并统计 SH 仓库出现了多少次。数据在 A1:B5，A列是编码，B列是数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，提取 A2 中的仓库编号；在 D2 单元格输入公式，统计编码中仓库编号为 SH 的记录条数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>WH-SH-001</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>WH-BJ-002</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>WH-SH-003</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>WH-GZ-004</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张运费单价表，需要根据目的地从价目表中查找单价。如果目的地不存在，则显示『未找到』。数据在 A1:B6，A列是目的地，B列是运费单价；在 D1:E3 给出查询示例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，根据 D2 的目的地『广州』查找对应运费单价，若查不到则显示『未找到』。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>运费单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
         <v>3.5</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>A1005</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>档案盒</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓储管理中需要计算每批货物从入库到今天已经存放了多少天，便于判断是否超期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算 PC001 从入库日期到今天的在库天数，并向下填充。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>批次号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>入库日期</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>在库天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>PC001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>PC002</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>PC003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>PC004</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张货物信息表，需要根据货物编码查找货物名称，练习比 VLOOKUP 更灵活的 INDEX+MATCH 组合。</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 输入货物编码 B2004，在 H2 单元格输入公式，查找并返回该编码对应的货物名称。</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>货物编码</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>B2001</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>顺达包装</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>B2002</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>胶带</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>顺达包装</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>B2003</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>气泡膜</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>安捷包装</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>B2004</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>缠绕膜</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>安捷包装</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>B2005</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>标签纸</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>永盛印刷</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1067,7 +944,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
         </is>
       </c>
     </row>
@@ -1078,7 +955,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"上海仓",B2:B7)</f>
+        <f>SUMIF(A2:A6,"上海仓",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1092,7 +969,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
+          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
         </is>
       </c>
     </row>
@@ -1102,9 +979,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIF(B2:B7,"异常")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2:=DATEDIF(B2,DATE(2024,3,20),"d")；E2:=ROUND(D2*3.5,2)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1117,7 +995,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
+          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1006,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(G2,A2:C6,3,FALSE),"未找到")</f>
+        <f>IF(B2&lt;50,"需补货","正常")</f>
         <v/>
       </c>
     </row>
@@ -1142,7 +1020,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
+          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
         </is>
       </c>
     </row>
@@ -1152,9 +1030,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2:=MID(A2,4,2)；D2:=COUNTIF(C2:C5,"SH")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1167,7 +1046,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1057,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(B2:B6,MATCH(G2,A2:A6,0))</f>
+        <f>IFERROR(INDEX(B2:B6,MATCH(D2,A2:A6,0)),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1210,7 +1089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
         </is>
       </c>
     </row>
@@ -1222,14 +1101,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法是 =SUMIF(条件区域, 条件, 求和区域)。这里条件区域 A2:A7 里找出“上海仓”，再对对应 B2:B7 的数值求和。</t>
+          <t>SUMIF 用于按单个条件求和，语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是"上海仓"，求和区域是 B2:B6。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计到货异常次数</t>
+          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1120,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于单条件计数，语法是 =COUNTIF(条件区域, 条件)。它会统计 B2:B7 中等于“异常”的单元格个数。</t>
+          <t>DATEDIF 用于计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, "d")，其中 "d" 表示按天计算。ROUND 用于四舍五入，语法：ROUND(数字, 小数位数)，这里保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 IFERROR 和 VLOOKUP 做货物单价查询</t>
+          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
         </is>
       </c>
     </row>
@@ -1260,14 +1139,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 按首列查找并返回指定列的值，语法 =VLOOKUP(查找值, 查找区域, 返回列号, FALSE)。IFERROR 用来捕获查找失败产生的错误，语法 =IFERROR(内容, 错误时显示值)。</t>
+          <t>IF 用于条件判断，语法：IF(条件, 条件成立时返回的值, 条件不成立时返回的值)。这里条件是 B2&lt;50，成立返回"需补货"，否则返回"正常"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 DATEDIF 和 TODAY 计算在库天数</t>
+          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
         </is>
       </c>
     </row>
@@ -1279,14 +1158,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF 用于计算两个日期之间的差值，语法 =DATEDIF(开始日期, 结束日期, 单位)，"d" 表示按天数计算。</t>
+          <t>MID 用于从文本中间提取指定长度字符，语法：MID(文本, 起始位置, 提取长度)。这里从第 4 位开始提取 2 位。COUNTIF 用于按条件计数，语法：COUNTIF(区域, 条件)。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX 和 MATCH 做货物名称精确查询</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1177,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH 返回查找值在区域中的相对位置，语法 =MATCH(查找值, 查找区域, 0)，0 表示精确匹配。INDEX 根据位置返回区域中的值，语法 =INDEX(返回区域, 位置)。两者组合可以实现灵活查表。</t>
+          <t>MATCH 用于查找值在区域中的位置，语法：MATCH(查找值, 查找区域, 0)，0 表示精确匹配。INDEX 用于根据位置返回值，语法：INDEX(返回区域, 行号)。IFERROR 用于捕获错误，语法：IFERROR(原公式, 出错时返回的值)，这里查不到时返回"未找到"。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,33 +490,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做台账，需要统计『上海仓』的入库总重量。数据在 A1:B6，A列是仓库，B列是重量(kg)。</t>
+          <t>要求：你在一家物流仓库做台账，需要按「货物名称」快速汇总已出库的重量。请用 SUMIF 完成条件求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算『上海仓』的入库总重量。</t>
+          <t>任务：在 E2 单元格输入公式，计算「纸箱」的总出库重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>货物名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>出库重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -526,7 +526,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>塑料箱</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -536,17 +536,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>木箱</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -556,11 +556,11 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -573,351 +573,399 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
+          <t>第 2 题：第2题：统计到货批次数量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责到港货物台账，需要先算出货物从到港到今天已经存放了多少天，再按每天 3.5 元计算仓储费，结果保留 2 位小数。数据在 A1:C4，A列是货物编号，B列是到港日期(文本日期)，C列是货物名称。</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：假设今天是 2024-03-20。在 D2 单元格输入公式，计算 C001 的到港天数；在 E2 单元格输入公式，计算 C001 的仓储费并保留 2 位小数。</t>
+          <t>要求：你在做采购到货台账，需要统计某个供应商出现了多少个到货批次，以及「已到货」状态的批次数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，统计「华远」的到货批次数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>到货状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>华远</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
+          <t>已到货</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>天成</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
+          <t>未到货</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>华远</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>华远</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>未到货</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>天成</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>练习函数：IF</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在电商仓库做库存管理，需要根据现有库存数量判断是否低于安全线。规则：库存小于 50 显示『需补货』，否则显示『正常』。数据在 A1:B5，A列是商品，B列是库存。</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，判断 A4纸 是否需要补货，并向下填充到 C5。</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>库存</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售台账中记录了客户、状态和金额。你需要同时按「状态=已到货」和「金额&gt;=1000」统计订单数量，并汇总这些订单的金额。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A4纸</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>30</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格统计满足「状态=已到货」且「金额&gt;=1000」的订单数量；在 E3 单元格汇总这些订单的金额。</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>80</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>45</v>
+          <t>华远</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>60</v>
+          <t>天成</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>未到货</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>华远</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>华远</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>天成</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>已到货</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张发货记录表，编码格式为『WH-仓库编号-序号』，例如 WH-SH-001 表示上海仓。需要提取中间的仓库编号，并统计 SH 仓库出现了多少次。数据在 A1:B5，A列是编码，B列是数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，提取 A2 中的仓库编号；在 D2 单元格输入公式，统计编码中仓库编号为 SH 的记录条数。</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>编码</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>WH-SH-001</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>12</v>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流台账中记录了发货日期，你需要计算每批货物从发货到今天已经过去了多少天。如果日期为空或格式错误，则显示“待确认”。</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>WH-BJ-002</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>8</v>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算 A001 批次从发货日期到今天的天数；如果日期为空或错误，则显示“待确认”。然后向下填充到 C5。</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>WH-SH-003</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>15</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>批次</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>WH-GZ-004</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>6</v>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张运费单价表，需要根据目的地从价目表中查找单价。如果目的地不存在，则显示『未找到』。数据在 A1:B6，A列是目的地，B列是运费单价；在 D1:E3 给出查询示例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，根据 D2 的目的地『广州』查找对应运费单价，若查不到则显示『未找到』。</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>运费单价</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>3.5</v>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张货物重量对照表，需要根据货物编码查找重量，并将结果保留 1 位小数。请分别用 VLOOKUP、XLOOKUP、INDEX+MATCH 完成查表。</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>4.2</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 输入货物编码“A1002”，在 H2 用 VLOOKUP 查找重量并保留 1 位小数；在 I2 用 XLOOKUP 查找重量并保留 1 位小数；在 J2 用 INDEX+MATCH 查找重量并保留 1 位小数。</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>3.8</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>货物编码</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>4</v>
+          <t>A1001</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>12.345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>4.5</v>
+          <t>A1002</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>塑料箱</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>8.567</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>A1003</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>20.111</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -944,7 +992,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
@@ -955,7 +1003,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"上海仓",B2:B6)</f>
+        <f>SUMIF(A2:A6,"纸箱",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -969,7 +1017,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
+          <t>第 2 题：第2题：统计到货批次数量</t>
         </is>
       </c>
     </row>
@@ -979,10 +1027,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>D2:=DATEDIF(B2,DATE(2024,3,20),"d")；E2:=ROUND(D2*3.5,2)</t>
-        </is>
+      <c r="B6" s="2">
+        <f>COUNTIF(A2:A6,"华远")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -995,7 +1042,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
+          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
         </is>
       </c>
     </row>
@@ -1005,9 +1052,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>IF(B2&lt;50,"需补货","正常")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>E2：=COUNTIFS(B2:B6,"已到货",C2:C6,"&gt;=1000")；E3：=SUMIFS(C2:C6,B2:B6,"已到货",C2:C6,"&gt;=1000")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1020,7 +1068,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
+          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1030,10 +1078,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2:=MID(A2,4,2)；D2:=COUNTIF(C2:C5,"SH")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待确认")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1093,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
+          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1056,9 +1103,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(INDEX(B2:B6,MATCH(D2,A2:A6,0)),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>H2：=ROUND(VLOOKUP(G2,A2:C4,3,FALSE),1)；I2：=ROUND(XLOOKUP(G2,A2:A4,C2:C4),1)；J2：=ROUND(INDEX(C2:C4,MATCH(G2,A2:A4,0)),1)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1089,7 +1137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库总重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1101,14 +1149,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是"上海仓"，求和区域是 B2:B6。</t>
+          <t>SUMIF 用于单条件求和，语法是：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“纸箱”，求和区域是 B2:B6，所以会把所有纸箱对应的出库重量相加。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并计算应付仓储费</t>
+          <t>第 2 题：第2题：统计到货批次数量</t>
         </is>
       </c>
     </row>
@@ -1120,14 +1168,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, "d")，其中 "d" 表示按天计算。ROUND 用于四舍五入，语法：ROUND(数字, 小数位数)，这里保留 2 位小数。</t>
+          <t>COUNTIF 用于单条件计数，语法是：COUNTIF(条件区域, 条件)。这里统计 A2:A6 中等于“华远”的单元格个数，所以可以得到华远的到货批次数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单数量判断是否需要补货</t>
+          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1187,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IF 用于条件判断，语法：IF(条件, 条件成立时返回的值, 条件不成立时返回的值)。这里条件是 B2&lt;50，成立返回"需补货"，否则返回"正常"。</t>
+          <t>COUNTIFS 用于多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。SUMIFS 用于多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。注意 SUMIFS 的求和区域要放在最前面。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从编码中提取仓库编号并统计数量</t>
+          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1158,14 +1206,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID 用于从文本中间提取指定长度字符，语法：MID(文本, 起始位置, 提取长度)。这里从第 4 位开始提取 2 位。COUNTIF 用于按条件计数，语法：COUNTIF(区域, 条件)。</t>
+          <t>TODAY() 返回今天的日期，DATEDIF(开始日期, 结束日期, "d") 计算两个日期之间的天数。IFERROR(公式, 错误时显示值) 可以在日期为空或格式错误时返回“待确认”。这个公式适合计算到港天数、账龄天数等。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查运费单价，并用 IFERROR 处理未找到</t>
+          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1225,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH 用于查找值在区域中的位置，语法：MATCH(查找值, 查找区域, 0)，0 表示精确匹配。INDEX 用于根据位置返回值，语法：INDEX(返回区域, 行号)。IFERROR 用于捕获错误，语法：IFERROR(原公式, 出错时返回的值)，这里查不到时返回"未找到"。</t>
+          <t>VLOOKUP(查找值, 表格区域, 返回列号, FALSE) 适合从左向右查表；XLOOKUP(查找值, 查找区域, 返回区域) 更灵活，不要求返回列在右侧；INDEX(返回区域, MATCH(查找值, 查找区域, 0)) 是经典组合查表。ROUND(数值, 1) 表示保留 1 位小数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,107 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流仓库做台账，需要按「货物名称」快速汇总已出库的重量。请用 SUMIF 完成条件求和。</t>
+          <t>要求：你负责整理一份物流发货台账，需要快速算出发往“上海”的货物总重量，熟悉按条件求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 单元格输入公式，计算「纸箱」的总出库重量。</t>
+          <t>任务：在空白单元格（如 E2）输入公式，计算目的地为“上海”的货物总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>出库重量</t>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>120</v>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>塑料箱</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>80</v>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>95</v>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>60</v>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>15.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>40</v>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +603,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货批次数量</t>
+          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
         </is>
       </c>
     </row>
@@ -587,385 +617,528 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你在做采购到货台账，需要统计某个供应商出现了多少个到货批次，以及「已到货」状态的批次数。</t>
+          <t>要求：销售助理需要统计订单明细表里金额大于500元的订单有多少笔，用于判断大额订单占比。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 单元格输入公式，统计「华远」的到货批次数。</t>
+          <t>任务：在空白单元格（如 E2）输入公式，统计金额大于500的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>到货状态</t>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>华远</t>
+          <t>A1001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>天成</t>
+          <t>A1002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>未到货</t>
-        </is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>680</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>华远</t>
+          <t>A1003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>华远</t>
+          <t>A1004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>未到货</t>
-        </is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>天成</t>
+          <t>A1005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A1006</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售台账中记录了客户、状态和金额。你需要同时按「状态=已到货」和「金额&gt;=1000」统计订单数量，并汇总这些订单的金额。</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格统计满足「状态=已到货」且「金额&gt;=1000」的订单数量；在 E3 单元格汇总这些订单的金额。</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库管理员有一份入库流水，需要统计“华东仓”中“家电”品类的总入库数量，练习多条件求和。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>华远</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>已到货</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>1200</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（如 F2）输入公式，计算仓库为“华东仓”且品类为“家电”的总入库数量。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>天成</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>未到货</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>800</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>入库单号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>华远</t>
+          <t>RK001</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1500</v>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>华远</t>
+          <t>RK002</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>900</v>
+          <t>华南仓</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>天成</t>
+          <t>RK003</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>已到货</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>2000</v>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>RK004</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>RK005</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>华北仓</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>RK006</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流台账中记录了发货日期，你需要计算每批货物从发货到今天已经过去了多少天。如果日期为空或格式错误，则显示“待确认”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算 A001 批次从发货日期到今天的天数；如果日期为空或错误，则显示“待确认”。然后向下填充到 C5。</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>批次</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：从订单表中查找客户电话</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>要求：客服收到客户“李四”的咨询，需要根据客户姓名快速从订单表中查出他的联系电话。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（如 F2）输入公式，根据姓名“李四”查找对应的电话。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>13600004444</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张货物重量对照表，需要根据货物编码查找重量，并将结果保留 1 位小数。请分别用 VLOOKUP、XLOOKUP、INDEX+MATCH 完成查表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 输入货物编码“A1002”，在 H2 用 VLOOKUP 查找重量并保留 1 位小数；在 I2 用 XLOOKUP 查找重量并保留 1 位小数；在 J2 用 INDEX+MATCH 查找重量并保留 1 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>货物编码</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>A1001</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>12.345</v>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>A1002</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>塑料箱</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>8.567</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>要求：商品台账中需要根据编号查找价格，如果编号不存在，则显示“未找到”，避免出现错误值影响报表。</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>A1003</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>20.111</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（如 F2）输入公式，根据编号“P003”查找单价；若查不到则显示“未找到”。</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>中性笔</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -992,7 +1165,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1176,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"纸箱",B2:B6)</f>
+        <f>SUMIF(B2:B6,"上海",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1017,7 +1190,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货批次数量</t>
+          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1201,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(A2:A6,"华远")</f>
+        <f>COUNTIF(C2:C7,"&gt;500")</f>
         <v/>
       </c>
     </row>
@@ -1042,7 +1215,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
+          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1225,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>E2：=COUNTIFS(B2:B6,"已到货",C2:C6,"&gt;=1000")；E3：=SUMIFS(C2:C6,B2:B6,"已到货",C2:C6,"&gt;=1000")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>SUMIFS(D2:D7,B2:B7,"华东仓",C2:C7,"家电")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1068,7 +1240,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
+          <t>第 4 题：第4题：从订单表中查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1251,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待确认")</f>
+        <f>VLOOKUP("李四",A2:C5,2,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1093,7 +1265,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
+          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1275,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>H2：=ROUND(VLOOKUP(G2,A2:C4,3,FALSE),1)；I2：=ROUND(XLOOKUP(G2,A2:A4,C2:C4),1)；J2：=ROUND(INDEX(C2:C4,MATCH(G2,A2:A4,0)),1)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IFERROR(XLOOKUP("P003",A2:A5,C2:C5),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1137,7 +1308,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1320,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法是：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“纸箱”，求和区域是 B2:B6，所以会把所有纸箱对应的出库重量相加。</t>
+          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是目的地列 B2:B6，条件是“上海”，求和区域是重量列 C2:C6，得到 12.5+20+7.5=40。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货批次数量</t>
+          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1339,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于单条件计数，语法是：COUNTIF(条件区域, 条件)。这里统计 A2:A6 中等于“华远”的单元格个数，所以可以得到华远的到货批次数。</t>
+          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)。这里对金额列 C2:C7 使用条件 "&gt;500"，统计大于500的单元格个数，结果为 3（680、1200、900）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计高价值已到货订单</t>
+          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
         </is>
       </c>
     </row>
@@ -1187,14 +1358,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。SUMIFS 用于多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。注意 SUMIFS 的求和区域要放在最前面。</t>
+          <t>SUMIFS 是多条件求和函数，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是 D2:D7，第一个条件是 B2:B7 等于“华东仓”，第二个条件是 C2:C7 等于“家电”，结果为 30+45+10=85。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数并处理错误</t>
+          <t>第 4 题：第4题：从订单表中查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1206,14 +1377,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期，DATEDIF(开始日期, 结束日期, "d") 计算两个日期之间的天数。IFERROR(公式, 错误时显示值) 可以在日期为空或格式错误时返回“待确认”。这个公式适合计算到港天数、账龄天数等。</t>
+          <t>VLOOKUP 用于按列查找，语法为 VLOOKUP(查找值, 查找区域, 返回第几列, 精确匹配FALSE)。这里在 A2:C5 的第一列查找“李四”，返回第2列的电话，并使用 FALSE 精确匹配，结果为 13900002222。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按货物编码查重量并四舍五入</t>
+          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1396,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表格区域, 返回列号, FALSE) 适合从左向右查表；XLOOKUP(查找值, 查找区域, 返回区域) 更灵活，不要求返回列在右侧；INDEX(返回区域, MATCH(查找值, 查找区域, 0)) 是经典组合查表。ROUND(数值, 1) 表示保留 1 位小数。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，这里在 A2:A5 中查找“P003”，返回 C2:C5 中对应单价，结果为 8。IFERROR 用于包裹可能出错的公式，语法为 IFERROR(公式, 出错时显示的值)，查不到时显示“未找到”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,121 +476,151 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责整理一份物流发货台账，需要快速算出发往“上海”的货物总重量，熟悉按条件求和。</t>
+          <t>要求：你是仓库文员，需要从入库台账中统计「上海仓」的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如 E2）输入公式，计算目的地为“上海”的货物总重量。</t>
+          <t>任务：请在 G2 单元格输入公式，计算「上海仓」的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>入库单号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>目的地</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>RK001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>A4纸</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>RK002</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>RK003</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>20</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>RK004</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>15.5</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
+          <t>RK005</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>7.5</v>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A4纸</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -603,542 +633,457 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
+          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流跟单员需要统计到港状态为「未到港」的订单数量，并找出其中最长等待天数。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：销售助理需要统计订单明细表里金额大于500元的订单有多少笔，用于判断大额订单占比。</t>
+          <t>任务：请在 G2 单元格统计「未到港」的订单数量；在 G3 单元格计算「未到港」订单中的最长等待天数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如 E2）输入公式，统计金额大于500的订单笔数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>目的港</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>等待天数</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SO001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A1001</t>
+          <t>SO002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>320</v>
+          <t>宁波港</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A1002</t>
+          <t>SO003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>680</v>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A1003</t>
+          <t>SO004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>450</v>
+          <t>深圳港</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A1004</t>
+          <t>SO005</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1200</v>
+          <t>宁波港</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A1005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A1006</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>900</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售助理需要根据商品名称，从价格表中查找单价；如果查不到，就显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 单元格输入商品名称「文件夹」，在 H2 单元格用公式查找其单价；若查不到则显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库管理员有一份入库流水，需要统计“华东仓”中“家电”品类的总入库数量，练习多条件求和。</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A4纸</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>22.5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如 F2）输入公式，计算仓库为“华东仓”且品类为“家电”的总入库数量。</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>入库单号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>RK001</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>30</v>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>RK002</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>华南仓</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>25</v>
+          <t>计算器</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>RK003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>RK004</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>45</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>RK005</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>华北仓</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：运费报价表按「城市」和「重量段」交叉存放价格，需要用 INDEX+MATCH 精确查找。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 输入城市「广州」，在 G3 输入重量段「5-10kg」，在 G4 用公式查找对应运费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>0-5kg</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>5-10kg</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>10kg以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>RK006</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="D40" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从订单表中查找客户电话</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服收到客户“李四”的咨询，需要根据客户姓名快速从订单表中查出他的联系电话。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如 F2）输入公式，根据姓名“李四”查找对应的电话。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：财务需要根据应收台账计算每笔款项从开票日到今天的账龄月数，并把金额保留到整数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格计算今天的日期；在 F2 单元格计算「甲公司」从开票日到今天的账龄月数；在 G2 单元格把应收金额四舍五入到整数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>电话</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>13600004444</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>开票日期</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>应收金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>甲公司</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1250.4</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>乙公司</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>980.6</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品台账中需要根据编号查找价格，如果编号不存在，则显示“未找到”，避免出现错误值影响报表。</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>丙公司</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>1733.2</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如 F2）输入公式，根据编号“P003”查找单价；若查不到则显示“未找到”。</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>丁公司</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>520.9</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>中性笔</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1165,7 +1110,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1121,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"上海",C2:C6)</f>
+        <f>SUMIFS(D2:D6,B2:B6,"上海仓")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1135,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
+          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
         </is>
       </c>
     </row>
@@ -1200,9 +1145,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIF(C2:C7,"&gt;500")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>G2: =COUNTIF(C2:C6,"未到港")；G3: =MAX(IF(C2:C6="未到港",D2:D6))（新版本可直接回车；旧版本按 Ctrl+Shift+Enter）</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1215,7 +1161,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
+          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1172,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(D2:D7,B2:B7,"华东仓",C2:C7,"家电")</f>
+        <f>IFERROR(VLOOKUP(G2,A2:B6,2,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1186,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从订单表中查找客户电话</t>
+          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1197,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP("李四",A2:C5,2,FALSE)</f>
+        <f>INDEX(B2:D5,MATCH(G2,A2:A5,0),MATCH(G3,B1:D1,0))</f>
         <v/>
       </c>
     </row>
@@ -1265,7 +1211,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
+          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
         </is>
       </c>
     </row>
@@ -1275,9 +1221,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP("P003",A2:A5,C2:C5),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>E2: =TODAY()；F2: =DATEDIF(B2,TODAY(),"M")；G2: =ROUND(C2,0)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1308,7 +1255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按目的地汇总重量</t>
+          <t>第 1 题：第1题：按仓库汇总入库重量</t>
         </is>
       </c>
     </row>
@@ -1320,14 +1267,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是目的地列 B2:B6，条件是“上海”，求和区域是重量列 C2:C6，得到 12.5+20+7.5=40。</t>
+          <t>SUMIFS 用于按条件求和。语法：=SUMIFS(求和区域, 条件区域1, 条件1, ...)。这里求和区域是 D2:D6「重量」，条件区域是 B2:B6「仓库」，条件是「上海仓」。结果应为 12.5+6.2+3.8=22.5。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单中金额大于500的笔数</t>
+          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
         </is>
       </c>
     </row>
@@ -1339,14 +1286,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)。这里对金额列 C2:C7 使用条件 "&gt;500"，统计大于500的单元格个数，结果为 3（680、1200、900）。</t>
+          <t>COUNTIF 语法：=COUNTIF(条件区域, 条件)，统计满足条件的单元格个数。MAX 用于求最大值；结合 IF 可先筛选「未到港」再取最大天数。若不想用数组公式，也可用 =MAXIFS(D2:D6,C2:C6,"未到港")。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库和品类双条件汇总入库数量</t>
+          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
         </is>
       </c>
     </row>
@@ -1358,14 +1305,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 是多条件求和函数，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是 D2:D7，第一个条件是 B2:B7 等于“华东仓”，第二个条件是 C2:C7 等于“家电”，结果为 30+45+10=85。</t>
+          <t>VLOOKUP 语法：=VLOOKUP(查找值, 表格区域, 返回第几列, FALSE)。这里在 A2:B6 的第一列查找 G2 的值，返回第 2 列「单价」。IFERROR 用于捕获错误值，语法：=IFERROR(原公式, 出错时显示内容)，避免出现 #N/A。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从订单表中查找客户电话</t>
+          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
         </is>
       </c>
     </row>
@@ -1377,14 +1324,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 用于按列查找，语法为 VLOOKUP(查找值, 查找区域, 返回第几列, 精确匹配FALSE)。这里在 A2:C5 的第一列查找“李四”，返回第2列的电话，并使用 FALSE 精确匹配，结果为 13900002222。</t>
+          <t>INDEX 语法：=INDEX(数据区域, 第几行, 第几列)，用于返回交叉位置的值。MATCH 语法：=MATCH(查找值, 查找区域, 0)，返回查找值在区域中的相对位置。这里第一个 MATCH 找城市所在行，第二个 MATCH 找重量段所在列，最后交给 INDEX 取出对应运费。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按商品编号查找价格并处理找不到的情况</t>
+          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1343,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，这里在 A2:A5 中查找“P003”，返回 C2:C5 中对应单价，结果为 8。IFERROR 用于包裹可能出错的公式，语法为 IFERROR(公式, 出错时显示的值)，查不到时显示“未找到”。</t>
+          <t>TODAY 返回当前日期。DATEDIF 语法：=DATEDIF(开始日期, 结束日期, "M")，"M" 表示相差的整月数。ROUND 语法：=ROUND(数值, 小数位数)，这里第 2 个参数为 0，表示保留到整数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,614 +476,593 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：第1题：快递重量汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要从入库台账中统计「上海仓」的入库总重量。</t>
+          <t>要求：你是仓库文员，需要按快递公司汇总包裹重量。请根据下面的台账，计算「顺丰」公司的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 G2 单元格输入公式，计算「上海仓」的入库总重量。</t>
+          <t>任务：在空白单元格中输入公式，计算快递公司为「顺丰」的包裹总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>入库单号</t>
+          <t>快递公司</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+          <t>包裹重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>RK001</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>A4纸</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>12.5</v>
+          <t>顺丰</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>RK002</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>8</v>
+          <t>中通</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>RK003</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>6.2</v>
+          <t>顺丰</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>RK004</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3.8</v>
+          <t>圆通</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>RK005</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>A4纸</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>15</v>
+          <t>顺丰</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>中通</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流跟单员需要统计到港状态为「未到港」的订单数量，并找出其中最长等待天数。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：超重包裹数量统计</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 单元格统计「未到港」的订单数量；在 G3 单元格计算「未到港」订单中的最长等待天数。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>目的港</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>等待天数</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流主管想快速知道有多少个包裹重量超过 3 公斤，以便安排特殊处理。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SO001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>5</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格中输入公式，统计重量大于 3 公斤的包裹数量。</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SO002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>宁波港</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>未到港</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>18</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>包裹编号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SO003</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>未到港</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>12</v>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SO004</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>深圳港</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>7</v>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SO005</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>宁波港</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>未到港</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>25</v>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售助理需要根据商品名称，从价格表中查找单价；如果查不到，就显示「未找到」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 单元格输入商品名称「文件夹」，在 H2 单元格用公式查找其单价；若查不到则显示「未找到」。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件统计到港包裹</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A4纸</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>22.5</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：港口调度员需要统计「上海港」且状态为「已到港」的包裹数量，并汇总这些包裹的重量。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>3.5</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格中分别输入两个公式：①统计上海港且已到港的包裹数量；②汇总这些包裹的总重量。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>8.800000000000001</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>15</v>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>计算器</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>36</v>
+          <t>宁波港</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>宁波港</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：运费报价表按「城市」和「重量段」交叉存放价格，需要用 INDEX+MATCH 精确查找。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 输入城市「广州」，在 G3 输入重量段「5-10kg」，在 G4 用公式查找对应运费。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>0-5kg</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>5-10kg</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>10kg以上</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>30</v>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：运费计算与错误处理</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>35</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：运费规则：重量 × 单价。如果单价为空或为 0，会导致除零或错误，请用 IFERROR 处理，并将运费保留 2 位小数。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>32</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，计算每个包裹的运费，保留 2 位小数；若出错则显示「待核价」。然后向下填充到 D6。</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>36</v>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>包裹编号</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>单价(元/kg)</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：财务需要根据应收台账计算每笔款项从开票日到今天的账龄月数，并把金额保留到整数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 E2 单元格计算今天的日期；在 F2 单元格计算「甲公司」从开票日到今天的账龄月数；在 G2 单元格把应收金额四舍五入到整数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>开票日期</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>应收金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1250.4</v>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>乙公司</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>980.6</v>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>丙公司</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>1733.2</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事台账中记录了员工入职日期、部门、工号。请完成：①计算每位员工的到岗天数（截至今天）；②根据工号查找员工姓名；③根据姓名查找所属部门。</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>丁公司</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>520.9</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>任务：①在 E2 输入公式计算张伟的到岗天数（截至今天）；②在空白单元格根据工号 SH003 查找姓名；③根据姓名「赵敏」查找部门。</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>物流部</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>2022-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>SH002</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>仓储部</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SH003</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>物流部</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>SH004</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>客服部</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1110,7 +1089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：第1题：快递重量汇总</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1100,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(D2:D6,B2:B6,"上海仓")</f>
+        <f>SUMIF(A2:A7,"顺丰",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1135,7 +1114,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
+          <t>第 2 题：第2题：超重包裹数量统计</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1124,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>G2: =COUNTIF(C2:C6,"未到港")；G3: =MAX(IF(C2:C6="未到港",D2:D6))（新版本可直接回车；旧版本按 Ctrl+Shift+Enter）</t>
-        </is>
+      <c r="B6" s="2">
+        <f>COUNTIF(B2:B7,"&gt;3")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1161,7 +1139,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
+          <t>第 3 题：第3题：多条件统计到港包裹</t>
         </is>
       </c>
     </row>
@@ -1171,9 +1149,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(G2,A2:B6,2,FALSE),"未找到")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>数量：=COUNTIFS(A2:A7,"上海港",B2:B7,"已到港")；重量：=SUMIFS(C2:C7,A2:A7,"上海港",B2:B7,"已到港")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1165,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
+          <t>第 4 题：第4题：运费计算与错误处理</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1176,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>INDEX(B2:D5,MATCH(G2,A2:A5,0),MATCH(G3,B1:D1,0))</f>
+        <f>IFERROR(ROUND(B2*C2,2),"待核价")</f>
         <v/>
       </c>
     </row>
@@ -1211,7 +1190,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
+          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1202,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>E2: =TODAY()；F2: =DATEDIF(B2,TODAY(),"M")；G2: =ROUND(C2,0)</t>
+          <t>①到岗天数：=DATEDIF(D2,TODAY(),"D")；②查姓名：=VLOOKUP("SH003",A2:D5,2,FALSE) 或 =XLOOKUP("SH003",A2:A5,B2:B5)；③查部门：=INDEX(C2:C5,MATCH("赵敏",B2:B5,0))</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1234,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按仓库汇总入库重量</t>
+          <t>第 1 题：第1题：快递重量汇总</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1246,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于按条件求和。语法：=SUMIFS(求和区域, 条件区域1, 条件1, ...)。这里求和区域是 D2:D6「重量」，条件区域是 B2:B6「仓库」，条件是「上海仓」。结果应为 12.5+6.2+3.8=22.5。</t>
+          <t>SUMIF 用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A7 是条件区域，条件为「顺丰」，B2:B7 是要求和的重量列。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计未到港单数与最长等待天数</t>
+          <t>第 2 题：第2题：超重包裹数量统计</t>
         </is>
       </c>
     </row>
@@ -1286,14 +1265,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 语法：=COUNTIF(条件区域, 条件)，统计满足条件的单元格个数。MAX 用于求最大值；结合 IF 可先筛选「未到港」再取最大天数。若不想用数组公式，也可用 =MAXIFS(D2:D6,C2:C6,"未到港")。</t>
+          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)。条件大于 3 需要写成 "&gt;3"，统计 B2:B7 中满足条件的个数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 VLOOKUP 查商品单价</t>
+          <t>第 3 题：第3题：多条件统计到港包裹</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1284,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 语法：=VLOOKUP(查找值, 表格区域, 返回第几列, FALSE)。这里在 A2:B6 的第一列查找 G2 的值，返回第 2 列「单价」。IFERROR 用于捕获错误值，语法：=IFERROR(原公式, 出错时显示内容)，避免出现 #N/A。</t>
+          <t>COUNTIFS 支持多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2)。SUMIFS 支持多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。注意 SUMIFS 的求和区域在最前面。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 INDEX+MATCH 做双向查表</t>
+          <t>第 4 题：第4题：运费计算与错误处理</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1303,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>INDEX 语法：=INDEX(数据区域, 第几行, 第几列)，用于返回交叉位置的值。MATCH 语法：=MATCH(查找值, 查找区域, 0)，返回查找值在区域中的相对位置。这里第一个 MATCH 找城市所在行，第二个 MATCH 找重量段所在列，最后交给 INDEX 取出对应运费。</t>
+          <t>ROUND 用于四舍五入，语法为 ROUND(数值, 小数位数)。IFERROR 用于捕获错误，语法为 IFERROR(表达式, 出错时显示的值)。这里先计算 B2*C2 并保留 2 位小数，如果出错则显示「待核价」。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算账龄并做四舍五入</t>
+          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1322,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TODAY 返回当前日期。DATEDIF 语法：=DATEDIF(开始日期, 结束日期, "M")，"M" 表示相差的整月数。ROUND 语法：=ROUND(数值, 小数位数)，这里第 2 个参数为 0，表示保留到整数。</t>
+          <t>TODAY 返回当天日期；DATEDIF 计算两个日期之间的天数，语法为 DATEDIF(开始日期,结束日期,"D")。VLOOKUP 按首列查找，语法为 VLOOKUP(查找值,表格区域,返回列号,FALSE)。XLOOKUP 更灵活，语法为 XLOOKUP(查找值,查找区域,返回区域)。INDEX+MATCH 组合中，MATCH 找到位置，INDEX 按位置取值。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,593 +476,557 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要按快递公司汇总包裹重量。请根据下面的台账，计算「顺丰」公司的总重量。</t>
+          <t>要求：你是物流公司调度员，需要从运输台账中统计“华东线”的总重量。请使用 SUMIFS 函数完成。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格中输入公式，计算快递公司为「顺丰」的包裹总重量。</t>
+          <t>任务：在空白单元格（如 G2）输入公式，计算“线路”为“华东线”的总重量，结果应为 470。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>快递公司</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>包裹重量(kg)</t>
+          <t>线路</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>货物类型</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>顺丰</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>2.5</v>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>中通</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1.8</v>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>华南线</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>顺丰</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>3.2</v>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>电器</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>圆通</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2.1</v>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>华北线</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>顺丰</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1.5</v>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>中通</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：超重包裹数量统计</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：电商运营需要统计“已完成”且“金额大于等于100”的订单数量。如果统计公式出现错误，希望显示为“待检查”。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（如 G2）输入公式，统计“状态”为“已完成”且“金额”大于等于100的订单数，并用 IFERROR 包裹结果。正确结果应为 2。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流主管想快速知道有多少个包裹重量超过 3 公斤，以便安排特殊处理。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格中输入公式，统计重量大于 3 公斤的包裹数量。</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DD001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DD002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>2.5</v>
+          <t>DD003</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>待付款</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>3.8</v>
+          <t>DD004</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>1.2</v>
+          <t>DD005</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>3</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>5.1</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：国际物流中，需要根据到港日期和发货日期计算运输天数，并判断是否超过30天。超过则标记“超期”，否则标记“正常”。假设今天是 2024-06-01，但到港日期已给出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式计算第1行货物的运输天数，并判断是否超期，结果显示“超期”或“正常”。正确结果应为“正常”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>货物</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>机械配件</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>纺织品</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件统计到港包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：港口调度员需要统计「上海港」且状态为「已到港」的包裹数量，并汇总这些包裹的重量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格中分别输入两个公式：①统计上海港且已到港的包裹数量；②汇总这些包裹的总重量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>港口</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>宁波港</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>未到港</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>10</v>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>6.5</v>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事台账中，员工编号第3-4位表示部门代码。需要先提取部门代码，再用 VLOOKUP 查找部门名称。</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>宁波港</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>未到港</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>7.2</v>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格用 MID 提取员工编号第3-4位作为部门代码，然后在 D2 用 VLOOKUP 根据部门代码查找部门名称。部门对照表为：HR=人事部，IT=技术部，FN=财务部。正确结果：C2为“20”，D2为“人事部”。</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>9</v>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>部门代码</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>部门名称</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>HR2023001</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>IT2023002</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FN2023003</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>HR2023004</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：运费计算与错误处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>要求：运费规则：重量 × 单价。如果单价为空或为 0，会导致除零或错误，请用 IFERROR 处理，并将运费保留 2 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，计算每个包裹的运费，保留 2 位小数；若出错则显示「待核价」。然后向下填充到 D6。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>单价(元/kg)</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>3.2</v>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>要求：采购表中记录了多种产品的单价。需要根据产品名称查找单价，并将结果保留两位小数。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>4</v>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（如 D2）输入公式，查找“文件夹”的单价，并四舍五入保留两位小数。正确结果应为 8.91。</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>0</v>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A4纸</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>2.8</v>
+        <v>12.345</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>3.678</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>8.912000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>15.499</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>要求：人事台账中记录了员工入职日期、部门、工号。请完成：①计算每位员工的到岗天数（截至今天）；②根据工号查找员工姓名；③根据姓名查找所属部门。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>任务：①在 E2 输入公式计算张伟的到岗天数（截至今天）；②在空白单元格根据工号 SH003 查找姓名；③根据姓名「赵敏」查找部门。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>工号</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>SH001</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>物流部</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>2022-03-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>SH002</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>仓储部</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>SH003</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>物流部</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>SH004</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>客服部</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>2022-11-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1089,7 +1053,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1064,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"顺丰",B2:B7)</f>
+        <f>SUMIFS(D2:D6,B2:B6,"华东线")</f>
         <v/>
       </c>
     </row>
@@ -1114,7 +1078,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：超重包裹数量统计</t>
+          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1089,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B7,"&gt;3")</f>
+        <f>IFERROR(COUNTIFS(B2:B6,"已完成",C2:C6,"&gt;=100"),"待检查")</f>
         <v/>
       </c>
     </row>
@@ -1139,7 +1103,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计到港包裹</t>
+          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1149,10 +1113,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>数量：=COUNTIFS(A2:A7,"上海港",B2:B7,"已到港")；重量：=SUMIFS(C2:C7,A2:A7,"上海港",B2:B7,"已到港")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>IF(DATEDIF(A2,B2,"d")&gt;30,"超期","正常")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1165,7 +1128,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：运费计算与错误处理</t>
+          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
         </is>
       </c>
     </row>
@@ -1175,9 +1138,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(ROUND(B2*C2,2),"待核价")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =MID(A2,3,2) ；D2: =VLOOKUP(C2,{"HR","人事部";"IT","技术部";"FN","财务部"},2,FALSE)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1190,7 +1154,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
+          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1164,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>①到岗天数：=DATEDIF(D2,TODAY(),"D")；②查姓名：=VLOOKUP("SH003",A2:D5,2,FALSE) 或 =XLOOKUP("SH003",A2:A5,B2:B5)；③查部门：=INDEX(C2:C5,MATCH("赵敏",B2:B5,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>ROUND(INDEX(B2:B5,MATCH("文件夹",A2:A5,0)),2)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1234,7 +1197,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量汇总</t>
+          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1246,14 +1209,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A7 是条件区域，条件为「顺丰」，B2:B7 是要求和的重量列。</t>
+          <t>SUMIFS 用于按一个或多个条件求和，语法为：=SUMIFS(求和区域, 条件区域1, 条件1, ...)。这里求和区域是 D2:D6 的重量，条件区域是 B2:B6 的线路，条件是“华东线”。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：超重包裹数量统计</t>
+          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
         </is>
       </c>
     </row>
@@ -1265,14 +1228,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法为 COUNTIF(区域, 条件)。条件大于 3 需要写成 "&gt;3"，统计 B2:B7 中满足条件的个数。</t>
+          <t>COUNTIFS 按多个条件计数，语法为：=COUNTIFS(区域1,条件1,区域2,条件2,...)。IFERROR 用于捕获错误，语法为：=IFERROR(原公式, 出错时显示的内容)。这里若 COUNTIFS 正常则返回 2，否则显示“待检查”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计到港包裹</t>
+          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1284,14 +1247,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 支持多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2)。SUMIFS 支持多条件求和，语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。注意 SUMIFS 的求和区域在最前面。</t>
+          <t>DATEDIF 计算两个日期之间的差值，语法为：=DATEDIF(开始日期,结束日期,单位)，单位“d”表示天数。IF 判断条件，语法为：=IF(条件,真值,假值)。这里运输天数为 24 天，不大于 30，所以返回“正常”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：运费计算与错误处理</t>
+          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
         </is>
       </c>
     </row>
@@ -1303,14 +1266,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROUND 用于四舍五入，语法为 ROUND(数值, 小数位数)。IFERROR 用于捕获错误，语法为 IFERROR(表达式, 出错时显示的值)。这里先计算 B2*C2 并保留 2 位小数，如果出错则显示「待核价」。</t>
+          <t>MID 从文本中间提取字符，语法为：=MID(文本,起始位置,字符个数)。VLOOKUP 按列查找，语法为：=VLOOKUP(查找值,查找区域,返回列号,精确匹配)。这里查找区域用了数组常量，也可以放在单元格区域。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：员工到岗天数与信息查找</t>
+          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1285,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TODAY 返回当天日期；DATEDIF 计算两个日期之间的天数，语法为 DATEDIF(开始日期,结束日期,"D")。VLOOKUP 按首列查找，语法为 VLOOKUP(查找值,表格区域,返回列号,FALSE)。XLOOKUP 更灵活，语法为 XLOOKUP(查找值,查找区域,返回区域)。INDEX+MATCH 组合中，MATCH 找到位置，INDEX 按位置取值。</t>
+          <t>INDEX 返回区域中指定位置的值，语法为：=INDEX(区域,行号)。MATCH 返回查找值在区域中的位置，语法为：=MATCH(查找值,查找区域,0)。ROUND 四舍五入，语法为：=ROUND(数值,小数位数)。这里先用 MATCH 找到“文件夹”在第3行，INDEX 返回 B5 的值 8.912，再 ROUND 为 8.91。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,151 +476,121 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是物流公司调度员，需要从运输台账中统计“华东线”的总重量。请使用 SUMIFS 函数完成。</t>
+          <t>要求：你在一家物流公司做仓库台账，需要按“品类”汇总入库重量，先练习最基础的条件求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如 G2）输入公式，计算“线路”为“华东线”的总重量，结果应为 470。</t>
+          <t>任务：在空白单元格输入公式，计算“电子产品”的入库重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>线路</t>
+          <t>品类</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>货物类型</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+          <t>入库重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>华南线</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>电器</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>200</v>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>华北线</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>50</v>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>150</v>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -633,317 +603,280 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
+          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：电商运营需要统计“已完成”且“金额大于等于100”的订单数量。如果统计公式出现错误，希望显示为“待检查”。</t>
+          <t>要求：货代台账中记录了每票货物的“到港日期”，你需要计算从到港当天到今天已经过去的天数，用于提醒客户提货。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如 G2）输入公式，统计“状态”为“已完成”且“金额”大于等于100的订单数，并用 IFERROR 包裹结果。正确结果应为 2。</t>
+          <t>任务：在 D2 单元格输入公式，计算 BL001 从到港日期到今天的相隔天数（按整天计算）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>提单号</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>DD001</t>
+          <t>BL001</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>120</v>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DD002</t>
+          <t>BL002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>80</v>
+          <t>2024-05-10</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DD003</t>
+          <t>BL003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>待付款</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>200</v>
+          <t>2024-05-20</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DD004</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>DD005</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>300</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司按月销售额计算提成：销售额达到 10000 及以上提成 5%，否则提成 3%。提成金额保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算张三的提成金额，并向下填充。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：国际物流中，需要根据到港日期和发货日期计算运输天数，并判断是否超过30天。超过则标记“超期”，否则标记“正常”。假设今天是 2024-06-01，但到港日期已给出。</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>员工</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>提成</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式计算第1行货物的运输天数，并判断是否超期，结果显示“超期”或“正常”。正确结果应为“正常”。</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
-      </c>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>机械配件</t>
-        </is>
-      </c>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
-        </is>
-      </c>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>纺织品</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>要求：电商订单台账中记录了每个订单的“状态”和“金额”。你需要统计“已付款”订单的笔数，以及“已付款”订单的金额合计。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>要求：人事台账中，员工编号第3-4位表示部门代码。需要先提取部门代码，再用 VLOOKUP 查找部门名称。</t>
+          <t>任务：在空白单元格输入两个公式：1）统计“已付款”订单笔数；2）统计“已付款”订单金额合计。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格用 MID 提取员工编号第3-4位作为部门代码，然后在 D2 用 VLOOKUP 根据部门代码查找部门名称。部门对照表为：HR=人事部，IT=技术部，FN=财务部。正确结果：C2为“20”，D2为“人事部”。</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>部门代码</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>部门名称</t>
-        </is>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>已付款</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>HR2023001</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>IT2023002</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
+          <t>已付款</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>299</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>FN2023003</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
+          <t>已付款</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>399</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HR2023004</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -955,31 +888,36 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
+          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>要求：采购表中记录了多种产品的单价。需要根据产品名称查找单价，并将结果保留两位小数。</t>
+          <t>要求：订单表中只有商品编号，需要从“商品价格表”中查找对应单价。若查不到编号，显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（如 D2）输入公式，查找“文件夹”的单价，并四舍五入保留两位小数。正确结果应为 8.91。</t>
+          <t>任务：假设订单编号在 F2 单元格，请在 G2 输入公式查找单价，若查不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>产品名称</t>
+          <t>商品编号</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
@@ -988,41 +926,61 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>A4纸</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>12.345</v>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>3.678</v>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>8.912000000000001</v>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>699</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>15.499</v>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="51">
@@ -1053,7 +1011,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1022,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(D2:D6,B2:B6,"华东线")</f>
+        <f>SUMIF(B2:B6,"电子产品",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1078,7 +1036,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
+          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1047,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IFERROR(COUNTIFS(B2:B6,"已完成",C2:C6,"&gt;=100"),"待检查")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1061,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
+          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1072,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IF(DATEDIF(A2,B2,"d")&gt;30,"超期","正常")</f>
+        <f>ROUND(IF(B2&gt;=10000,B2*5%,B2*3%),2)</f>
         <v/>
       </c>
     </row>
@@ -1128,7 +1086,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
+          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1138,10 +1096,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =MID(A2,3,2) ；D2: =VLOOKUP(C2,{"HR","人事部";"IT","技术部";"FN","财务部"},2,FALSE)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>COUNTIF(B2:B6,"已付款")；=SUMIFS(C2:C6,B2:B6,"已付款")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1154,7 +1111,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
+          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1122,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(INDEX(B2:B5,MATCH("文件夹",A2:A5,0)),2)</f>
+        <f>IFERROR(XLOOKUP(F2,A2:A5,C2:C5,"未找到"),"未找到") 或 =IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1197,7 +1154,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账中按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1209,14 +1166,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于按一个或多个条件求和，语法为：=SUMIFS(求和区域, 条件区域1, 条件1, ...)。这里求和区域是 D2:D6 的重量，条件区域是 B2:B6 的线路，条件是“华东线”。</t>
+          <t>SUMIF 语法：SUMIF(条件区域,条件,求和区域)。这里条件区域是品类列 B2:B6，条件是“电子产品”，求和区域是重量列 C2:C6。结果应为 120+80+100=300。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单数量并处理无结果情况</t>
+          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1228,14 +1185,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 按多个条件计数，语法为：=COUNTIFS(区域1,条件1,区域2,条件2,...)。IFERROR 用于捕获错误，语法为：=IFERROR(原公式, 出错时显示的内容)。这里若 COUNTIFS 正常则返回 2，否则显示“待检查”。</t>
+          <t>TODAY() 返回今天的日期；DATEDIF(开始日期,结束日期,"d") 返回两个日期之间的整天数。这里开始日期是 B2，结束日期用 TODAY()。注意：到港日期需是 Excel 可识别的日期格式。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数并判断是否超期</t>
+          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1204,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 计算两个日期之间的差值，语法为：=DATEDIF(开始日期,结束日期,单位)，单位“d”表示天数。IF 判断条件，语法为：=IF(条件,真值,假值)。这里运输天数为 24 天，不大于 30，所以返回“正常”。</t>
+          <t>IF(条件,真值,假值) 判断销售额是否 &gt;=10000；ROUND(数值,2) 将结果四舍五入保留 2 位小数。张三结果：12000*5%=600。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从员工编号中提取部门代码并查找部门名称</t>
+          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1266,14 +1223,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID 从文本中间提取字符，语法为：=MID(文本,起始位置,字符个数)。VLOOKUP 按列查找，语法为：=VLOOKUP(查找值,查找区域,返回列号,精确匹配)。这里查找区域用了数组常量，也可以放在单元格区域。</t>
+          <t>COUNTIF(区域,条件) 统计满足条件的单元格个数；SUMIFS(求和区域,条件区域1,条件1,...) 按多个条件求和，这里只有一个条件。笔数结果为 3，金额合计为 199+299+399=897。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名称查找最新单价并四舍五入</t>
+          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1242,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX 返回区域中指定位置的值，语法为：=INDEX(区域,行号)。MATCH 返回查找值在区域中的位置，语法为：=MATCH(查找值,查找区域,0)。ROUND 四舍五入，语法为：=ROUND(数值,小数位数)。这里先用 MATCH 找到“文件夹”在第3行，INDEX 返回 B5 的值 8.912，再 ROUND 为 8.91。</t>
+          <t>XLOOKUP(查找值,查找区域,返回区域,[未找到值]) 是最新查找函数；VLOOKUP(查找值,表格区域,返回列号,FALSE) 是经典查找函数。IFERROR(公式,"未找到") 可让查找失败时显示友好提示。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,515 +476,614 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做仓库台账，需要按“品类”汇总入库重量，先练习最基础的条件求和。</t>
+          <t>要求：你是物流公司的数据员，需要根据出港台账，统计「上海仓 -&gt; 北京仓」这条线路的总重量，用于核算运输成本。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格输入公式，计算“电子产品”的入库重量合计。</t>
+          <t>任务：请在工作表空白单元格 E2 输入公式，计算出发仓为「上海仓」且到达仓为「北京仓」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>出发仓</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>品类</t>
+          <t>到达仓</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>入库重量(kg)</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>80</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>杭州仓</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：货代台账中记录了每票货物的“到港日期”，你需要计算从到港当天到今天已经过去的天数，用于提醒客户提货。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：到港天数计算与显示处理</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算 BL001 从到港日期到今天的相隔天数（按整天计算）。</t>
+          <t>要求：你负责跟进国际物流到港进度，需要根据「预计到港日期」计算距离今天还有多少天；如果日期为空或格式错误，不要显示错误值，而是显示“待确认”。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算 B2 的预计到港日期距离今天还有多少天；若计算失败则显示“待确认”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>提单号</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>BL001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BL002</t>
+          <t>BL001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>BL002</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>BL003</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BL004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>要求：公司按月销售额计算提成：销售额达到 10000 及以上提成 5%，否则提成 3%。提成金额保留 2 位小数。</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算张三的提成金额，并向下填充。</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>员工</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>提成</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份电商销售台账，需要统计「耳机」在「华东」地区的订单笔数，并顺手统计所有「耳机」的销售金额合计。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 F2 输入公式统计商品为「耳机」且地区为「华东」的订单笔数；在 F3 输入公式统计所有「耳机」的销售金额合计。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>299</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>要求：电商订单台账中记录了每个订单的“状态”和“金额”。你需要统计“已付款”订单的笔数，以及“已付款”订单的金额合计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入两个公式：1）统计“已付款”订单笔数；2）统计“已付款”订单金额合计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>199</v>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>99</v>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库需要按「品类」汇总重量，并找出当前入库记录中的最大单件重量，同时把汇总重量保留 1 位小数，方便汇报。</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>299</v>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 输入公式计算「生鲜」的总重量，并四舍五入保留 1 位小数；在 D3 输入公式找出所有记录中的最大重量。</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>399</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>18.26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张商品价目表，需要根据订单中的商品编号自动查出商品名称和单价。商品编号前 2 位表示分类，后 3 位表示序号，例如 SP1001。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 输入公式，根据 F2 中的商品编号「SP2002」查出商品名称；在 G3 输入公式查出该商品单价。要求至少使用 XLOOKUP 或 VLOOKUP，并可用 INDEX+MATCH 作为另一种思路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>SP1001</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>无线鼠标</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：订单表中只有商品编号，需要从“商品价格表”中查找对应单价。若查不到编号，显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设订单编号在 F2 单元格，请在 G2 输入公式查找单价，若查不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SP1002</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>机械键盘</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SP2001</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>蓝牙耳机</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>SP2002</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>头戴耳机</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>SP3001</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>显示器</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="C56" s="4" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1011,7 +1110,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1121,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"电子产品",C2:C6)</f>
+        <f>SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"北京仓")</f>
         <v/>
       </c>
     </row>
@@ -1036,7 +1135,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
+          <t>第 2 题：第2题：到港天数计算与显示处理</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1146,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>IFERROR(DATEDIF(TODAY(),B2,"d"),"待确认")</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1160,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
+          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
         </is>
       </c>
     </row>
@@ -1071,9 +1170,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>ROUND(IF(B2&gt;=10000,B2*5%,B2*3%),2)</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F2: =COUNTIFS(B2:B7,"耳机",C2:C7,"华东")；F3: =SUMIF(B2:B7,"耳机",D2:D7)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1086,7 +1186,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
+          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1096,9 +1196,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>COUNTIF(B2:B6,"已付款")；=SUMIFS(C2:C6,B2:B6,"已付款")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D2: =ROUND(SUMIF(A2:A7,"生鲜",B2:B7),1)；D3: =MAX(B2:B7)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1111,7 +1212,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
+          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
         </is>
       </c>
     </row>
@@ -1121,9 +1222,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP(F2,A2:A5,C2:C5,"未找到"),"未找到") 或 =IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>G2: =XLOOKUP(F2,A2:A6,B2:B6)；G3: =INDEX(C2:C6,MATCH(F2,A2:A6,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1154,7 +1256,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1268,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法：SUMIF(条件区域,条件,求和区域)。这里条件区域是品类列 B2:B6，条件是“电子产品”，求和区域是重量列 C2:C6。结果应为 120+80+100=300。</t>
+          <t>SUMIFS 用于多条件求和，语法为 =SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题求和区域是 C2:C7 的重量，条件区域 A2:A7 要等于“上海仓”，条件区域 B2:B7 要等于“北京仓”。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算（TODAY + DATEDIF）</t>
+          <t>第 2 题：第2题：到港天数计算与显示处理</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1287,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期；DATEDIF(开始日期,结束日期,"d") 返回两个日期之间的整天数。这里开始日期是 B2，结束日期用 TODAY()。注意：到港日期需是 Excel 可识别的日期格式。</t>
+          <t>TODAY() 返回今天的日期；DATEDIF(开始日期,结束日期,"d") 计算两个日期相差的天数，"d" 表示按天。IFERROR(公式,"待确认") 表示如果公式出错，就显示“待确认”，避免出现 #NUM! 或 #VALUE!。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售提成计算（IF + ROUND）</t>
+          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1306,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IF(条件,真值,假值) 判断销售额是否 &gt;=10000；ROUND(数值,2) 将结果四舍五入保留 2 位小数。张三结果：12000*5%=600。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 =COUNTIFS(条件区域1,条件1,条件区域2,条件2...)。SUMIF 用于单条件求和，语法为 =SUMIF(条件区域,条件,求和区域)，本题统计所有商品为“耳机”的金额合计。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单数量与金额统计（COUNTIF + SUMIFS）</t>
+          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1325,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(区域,条件) 统计满足条件的单元格个数；SUMIFS(求和区域,条件区域1,条件1,...) 按多个条件求和，这里只有一个条件。笔数结果为 3，金额合计为 199+299+399=897。</t>
+          <t>SUMIF 先按条件“生鲜”汇总重量；ROUND(数值,1) 表示保留 1 位小数。MAX(B2:B7) 用于返回区域中的最大值，适合找最大单件重量。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品单价查找（XLOOKUP/VLOOKUP + IFERROR）</t>
+          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1344,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找区域,返回区域,[未找到值]) 是最新查找函数；VLOOKUP(查找值,表格区域,返回列号,FALSE) 是经典查找函数。IFERROR(公式,"未找到") 可让查找失败时显示友好提示。</t>
+          <t>XLOOKUP(查找值,查找区域,返回区域) 可直接按商品编号返回名称。INDEX(返回区域,行号) 配合 MATCH(查找值,查找区域,0) 可实现精确查表：MATCH 找到编号所在行，INDEX 再返回对应单价。RIGHT 和 MID 常用于从编号中提取分类或序号，例如 MID(F2,3,3) 可取出后 3 位序号。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -476,40 +476,40 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是物流公司的数据员，需要根据出港台账，统计「上海仓 -&gt; 北京仓」这条线路的总重量，用于核算运输成本。</t>
+          <t>要求：你在一家快递公司做运营助理，需要从一份快递重量台账中，快速算出「朝阳网点」所有包裹的总重量。请使用 SUMIF 按条件汇总。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在工作表空白单元格 E2 输入公式，计算出发仓为「上海仓」且到达仓为「北京仓」的总重量。</t>
+          <t>任务：假设以上数据从 A1 开始。请在 F2 单元格输入公式，计算「朝阳网点」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>出发仓</t>
+          <t>网点</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>到达仓</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -521,91 +521,91 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>朝阳网点</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>120.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>海淀网点</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>80</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>朝阳网点</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>99.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>丰台网点</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>杭州仓</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>60</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>朝阳网点</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD005</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>150</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>海淀网点</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>YD006</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -618,468 +618,538 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算与显示处理</t>
+          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责跟进国际物流到港进度，需要根据「预计到港日期」计算距离今天还有多少天；如果日期为空或格式错误，不要显示错误值，而是显示“待确认”。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式，计算 B2 的预计到港日期距离今天还有多少天；若计算失败则显示“待确认”。</t>
+          <t>要求：你是连锁便利店的数据专员，需要统计「上海」地区中「已完成」状态的订单数量，方便评估履约情况。请使用 COUNTIFS 完成多条件计数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>提单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设以上数据从 A1 开始。请在 G2 单元格输入公式，统计城市为「上海」且状态为「已完成」的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>BL001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>BL002</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
+          <t>DD001</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>BL003</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr"/>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>DD002</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>BL004</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
+          <t>DD003</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>DD004</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>DD005</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>DD006</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份电商销售台账，需要统计「耳机」在「华东」地区的订单笔数，并顺手统计所有「耳机」的销售金额合计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 F2 输入公式统计商品为「耳机」且地区为「华东」的订单笔数；在 F3 输入公式统计所有「耳机」的销售金额合计。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>199</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在国际物流公司负责到港台账，需要先计算每票货物的在途天数（到港日期减起运日期），再汇总「海运」方式且在途天数大于等于 20 天的货物总重量。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>299</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设以上数据从 A1 开始，起运日期和到港日期为日期格式。请先在 E2 单元格输入公式计算第 1 票货物的在途天数，再在 G2 单元格输入公式汇总「海运」且 E 列在途天数大于等于 20 的重量。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>199</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>运输方式</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>起运日期</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>重量(吨)</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>海运</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>耳机</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>399</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>空运</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>海运</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>耳机</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>199</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>海运</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>陆运</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库需要按「品类」汇总重量，并找出当前入库记录中的最大单件重量，同时把汇总重量保留 1 位小数，方便汇报。</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D2 输入公式计算「生鲜」的总重量，并四舍五入保留 1 位小数；在 D3 输入公式找出所有记录中的最大重量。</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>18.26</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是电商仓管，需要根据订单里的商品编号，从商品资料表中查出对应单价，用于后续计算订单金额。请使用 VLOOKUP 完成精确匹配。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>5.14</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设商品资料在 A1:C5，订单查询编号放在 E2，例如 E2 为「SP003」。请在 F2 单元格输入公式，查找该商品编号对应的单价。</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>22.78</v>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>家电</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>30.5</v>
+          <t>SP001</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>抽纸</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>16.42</v>
+          <t>SP002</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>39.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>7.91</v>
+          <t>SP003</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>矿泉水</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SP004</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>大米</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张商品价目表，需要根据订单中的商品编号自动查出商品名称和单价。商品编号前 2 位表示分类，后 3 位表示序号，例如 SP1001。</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 G2 输入公式，根据 F2 中的商品编号「SP2002」查出商品名称；在 G3 输入公式查出该商品单价。要求至少使用 XLOOKUP 或 VLOOKUP，并可用 INDEX+MATCH 作为另一种思路。</t>
+          <t>要求：你是培训机构的教务老师，需要根据学员成绩判断等级，并在查询学员信息时避免出现错误值。先用 IF 判断成绩等级，再用 IFERROR 包裹 VLOOKUP 让查不到时显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据从 A1 开始，成绩在 C 列。请先在 D2 输入公式判断等级：成绩大于等于 90 为「优秀」，大于等于 60 为「及格」，否则为「不及格」；再在 F2 输入公式，根据 E2 的学员编号查询姓名，如果查不到则显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>SP1001</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>无线鼠标</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>89</v>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>学员编号</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>成绩</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SP1002</t>
+          <t>X001</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>299</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>SP2001</t>
+          <t>X002</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>蓝牙耳机</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>199</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>SP2002</t>
+          <t>X003</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>头戴耳机</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>399</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>SP3001</t>
+          <t>X004</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>899</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
@@ -1110,7 +1180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1191,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"上海仓",B2:B7,"北京仓")</f>
+        <f>SUMIF(A2:A7,"朝阳网点",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1135,7 +1205,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算与显示处理</t>
+          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1216,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IFERROR(DATEDIF(TODAY(),B2,"d"),"待确认")</f>
+        <f>COUNTIFS(A2:A7,"上海",C2:C7,"已完成")</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1230,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
+          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
         </is>
       </c>
     </row>
@@ -1170,10 +1240,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>F2: =COUNTIFS(B2:B7,"耳机",C2:C7,"华东")；F3: =SUMIF(B2:B7,"耳机",D2:D7)</t>
-        </is>
+      <c r="B10" s="2">
+        <f>DATEDIF(B2,C2,"d")；=SUMIFS(D2:D6,A2:A6,"海运",E2:E6,"&gt;=20")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1255,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
+          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1265,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>D2: =ROUND(SUMIF(A2:A7,"生鲜",B2:B7),1)；D3: =MAX(B2:B7)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1212,7 +1280,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
+          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1290,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2: =XLOOKUP(F2,A2:A6,B2:B6)；G3: =INDEX(C2:C6,MATCH(F2,A2:A6,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IF(C2&gt;=90,"优秀",IF(C2&gt;=60,"及格","不及格"))；=IFERROR(VLOOKUP(E2,A2:C5,2,FALSE),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1256,7 +1323,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
         </is>
       </c>
     </row>
@@ -1268,14 +1335,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法为 =SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题求和区域是 C2:C7 的重量，条件区域 A2:A7 要等于“上海仓”，条件区域 B2:B7 要等于“北京仓”。</t>
+          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A7 是网点列，条件为“朝阳网点”，C2:C7 是重量列。公式会找出所有朝阳网点的行，并把对应重量相加，得到 2.5+3.8+0.9=7.2 kg。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算与显示处理</t>
+          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1354,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期；DATEDIF(开始日期,结束日期,"d") 计算两个日期相差的天数，"d" 表示按天。IFERROR(公式,"待确认") 表示如果公式出错，就显示“待确认”，避免出现 #NUM! 或 #VALUE!。</t>
+          <t>COUNTIFS 语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。A2:A7 判断是否为“上海”，C2:C7 判断是否为“已完成”，两个条件同时满足才计数。结果应为 3 条。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：销售台账按商品统计订单数</t>
+          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
         </is>
       </c>
     </row>
@@ -1306,14 +1373,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 =COUNTIFS(条件区域1,条件1,条件区域2,条件2...)。SUMIF 用于单条件求和，语法为 =SUMIF(条件区域,条件,求和区域)，本题统计所有商品为“耳机”的金额合计。</t>
+          <t>DATEDIF(开始日期,结束日期,"d") 返回两个日期之间的天数，E2 得到 24 天。SUMIFS 语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2,...)，这里对 D2:D6 求和，条件一是运输方式为“海运”，条件二是 E 列在途天数大于等于 20。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：重量汇总、最高值与四舍五入</t>
+          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
         </is>
       </c>
     </row>
@@ -1325,14 +1392,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 先按条件“生鲜”汇总重量；ROUND(数值,1) 表示保留 1 位小数。MAX(B2:B7) 用于返回区域中的最大值，适合找最大单件重量。</t>
+          <t>VLOOKUP 语法为 VLOOKUP(查找值,查找区域,返回第几列,是否精确匹配)。E2 是商品编号，A2:C5 是资料表，单价在第 3 列，FALSE 表示精确匹配。若 E2 为 SP003，则返回 2.0。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据商品编号查价格与名称</t>
+          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1411,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找区域,返回区域) 可直接按商品编号返回名称。INDEX(返回区域,行号) 配合 MATCH(查找值,查找区域,0) 可实现精确查表：MATCH 找到编号所在行，INDEX 再返回对应单价。RIGHT 和 MID 常用于从编号中提取分类或序号，例如 MID(F2,3,3) 可取出后 3 位序号。</t>
+          <t>IF 语法为 IF(条件,真值,假值)，嵌套 IF 可处理多档判断。IFERROR 语法为 IFERROR(原公式,出错时显示的值)，这里包裹 VLOOKUP，当编号不存在导致 #N/A 时，就显示“未找到”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,670 +490,563 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家快递公司做运营助理，需要从一份快递重量台账中，快速算出「朝阳网点」所有包裹的总重量。请使用 SUMIF 按条件汇总。</t>
+          <t>要求：你是仓库管理员，需要统计“华东仓”的总入库重量。请用 SUMIF 按仓库名称汇总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设以上数据从 A1 开始。请在 F2 单元格输入公式，计算「朝阳网点」的总重量。</t>
+          <t>任务：在 G2 单元格输入公式，计算“华东仓”的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>网点</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>货物</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>海淀网点</t>
+          <t>华南仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>塑料件</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>金属件</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>丰台网点</t>
+          <t>华北仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
+          <t>塑料件</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>海淀网点</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>YD006</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单数量区间统计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：电商运营需要统计订单数量大于等于 100 且小于 200 的订单笔数，用于分析中等订单规模。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你是连锁便利店的数据专员，需要统计「上海」地区中「已完成」状态的订单数量，方便评估履约情况。请使用 COUNTIFS 完成多条件计数。</t>
+          <t>任务：在 F2 单元格输入公式，统计数量在 100 到 199 之间的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设以上数据从 A1 开始。请在 G2 单元格输入公式，统计城市为「上海」且状态为「已完成」的订单数量。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>DD001</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>56</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>DD002</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>89</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DD003</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>32</v>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>DD004</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>120</v>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>DD005</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>45</v>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>DD006</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：物流到港天数计算</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>要求：你在国际物流公司负责到港台账，需要先计算每票货物的在途天数（到港日期减起运日期），再汇总「海运」方式且在途天数大于等于 20 天的货物总重量。</t>
+          <t>要求：物流专员需要根据到港日期和发货日期，计算每票货物的运输天数。请用 DATEDIF 按“天”计算。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>任务：假设以上数据从 A1 开始，起运日期和到港日期为日期格式。请先在 E2 单元格输入公式计算第 1 票货物的在途天数，再在 G2 单元格输入公式汇总「海运」且 E 列在途天数大于等于 20 的重量。</t>
+          <t>任务：在 E2 单元格输入公式，计算 YD001 从发货到到港的运输天数。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>运输方式</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>起运日期</t>
+          <t>发货日期</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
           <t>到港日期</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>重量(吨)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>海运</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>18.5</v>
+          <t>2025-01-06</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>空运</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>2.3</v>
+          <t>2025-01-10</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>海运</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>12</v>
+          <t>2025-01-09</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>海运</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>陆运</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-30</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>8.800000000000001</v>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：客户编码提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>练习函数：RIGHT</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：客户编码格式为“城市-序号”，例如“SH-1001”。现在需要提取编码右侧的 4 位序号，方便后续匹配。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，提取 A2 单元格客户编码右侧的 4 位序号。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是电商仓管，需要根据订单里的商品编号，从商品资料表中查出对应单价，用于后续计算订单金额。请使用 VLOOKUP 完成精确匹配。</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>客户编码</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设商品资料在 A1:C5，订单查询编号放在 E2，例如 E2 为「SP003」。请在 F2 单元格输入公式，查找该商品编号对应的单价。</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SH-1001</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>BJ-1002</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>SP001</t>
+          <t>GZ-1003</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>抽纸</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>12.5</v>
+          <t>王五</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>SP002</t>
+          <t>SZ-1004</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>39.9</v>
+          <t>赵六</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>SP003</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>矿泉水</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>SP004</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>大米</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>58</v>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：产品单价查表匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售助理需要根据产品编号，从价格表中查找对应单价，填入订单表。请用 VLOOKUP 完成精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>要求：你是培训机构的教务老师，需要根据学员成绩判断等级，并在查询学员信息时避免出现错误值。先用 IF 判断成绩等级，再用 IFERROR 包裹 VLOOKUP 让查不到时显示「未找到」。</t>
+          <t>任务：在 G2 单元格输入产品编号“P003”，在 H2 单元格输入公式，从 A2:C5 区域查找该产品单价。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据从 A1 开始，成绩在 C 列。请先在 D2 输入公式判断等级：成绩大于等于 90 为「优秀」，大于等于 60 为「及格」，否则为「不及格」；再在 F2 输入公式，根据 E2 的学员编号查询姓名，如果查不到则显示「未找到」。</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>学员编号</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>成绩</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>X001</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>中性笔</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>X002</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>文件夹</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>X003</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>订书机</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>X004</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1180,7 +1073,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1084,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"朝阳网点",C2:C7)</f>
+        <f>SUMIF(A2:A6,"华东仓",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1205,7 +1098,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
+          <t>第 2 题：第2题：订单数量区间统计</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1109,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A7,"上海",C2:C7,"已完成")</f>
+        <f>COUNTIFS(C2:C7,"&gt;=100",C2:C7,"&lt;200")</f>
         <v/>
       </c>
     </row>
@@ -1230,7 +1123,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
+          <t>第 3 题：第3题：物流到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1134,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,C2,"d")；=SUMIFS(D2:D6,A2:A6,"海运",E2:E6,"&gt;=20")</f>
+        <f>DATEDIF(B2,C2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1255,7 +1148,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
+          <t>第 4 题：第4题：客户编码提取</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1159,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <f>RIGHT(A2,4)</f>
         <v/>
       </c>
     </row>
@@ -1280,7 +1173,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
+          <t>第 5 题：第5题：产品单价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1184,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IF(C2&gt;=90,"优秀",IF(C2&gt;=60,"及格","不及格"))；=IFERROR(VLOOKUP(E2,A2:C5,2,FALSE),"未找到")</f>
+        <f>VLOOKUP(G2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1323,7 +1216,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：快递重量台账——用SUMIF汇总某网点重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1335,14 +1228,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A7 是网点列，条件为“朝阳网点”，C2:C7 是重量列。公式会找出所有朝阳网点的行，并把对应重量相加，得到 2.5+3.8+0.9=7.2 kg。</t>
+          <t>SUMIF 的语法是 =SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是仓库名称区域，条件是“华东仓”，C2:C6 是重量区域，所以会把华东仓对应的 120、150、50 相加，结果为 320。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：门店销售统计——用COUNTIFS统计同时满足两个条件的订单数</t>
+          <t>第 2 题：第2题：订单数量区间统计</t>
         </is>
       </c>
     </row>
@@ -1354,14 +1247,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。A2:A7 判断是否为“上海”，C2:C7 判断是否为“已完成”，两个条件同时满足才计数。结果应为 3 条。</t>
+          <t>COUNTIFS 可以按多个条件计数，语法是 =COUNTIFS(区域1,条件1,区域2,条件2...)。本题对同一个区域 C2:C7 设置两个条件：&gt;=100 和 &lt;200，满足条件的订单有 A002、A003、A005、A006，共 4 笔。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与重量汇总——用DATEDIF计算到港天数，再用SUMIFS汇总对应重量</t>
+          <t>第 3 题：第3题：物流到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1373,14 +1266,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,"d") 返回两个日期之间的天数，E2 得到 24 天。SUMIFS 语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2,...)，这里对 D2:D6 求和，条件一是运输方式为“海运”，条件二是 E 列在途天数大于等于 20。</t>
+          <t>DATEDIF 的语法是 =DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数。B2 是 2025-01-01，C2 是 2025-01-06，相差 5 天，所以结果为 5。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：商品单价查找——用VLOOKUP按商品编号查单价</t>
+          <t>第 4 题：第4题：客户编码提取</t>
         </is>
       </c>
     </row>
@@ -1392,14 +1285,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 语法为 VLOOKUP(查找值,查找区域,返回第几列,是否精确匹配)。E2 是商品编号，A2:C5 是资料表，单价在第 3 列，FALSE 表示精确匹配。若 E2 为 SP003，则返回 2.0。</t>
+          <t>RIGHT 的语法是 =RIGHT(文本, 提取字符数)。A2 为“SH-1001”，右侧 4 位是“1001”，所以公式返回 1001。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：成绩等级与错误处理——用IF判断等级，再用IFERROR处理查询错误</t>
+          <t>第 5 题：第5题：产品单价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1304,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IF 语法为 IF(条件,真值,假值)，嵌套 IF 可处理多档判断。IFERROR 语法为 IFERROR(原公式,出错时显示的值)，这里包裹 VLOOKUP，当编号不存在导致 #N/A 时，就显示“未找到”。</t>
+          <t>VLOOKUP 的语法是 =VLOOKUP(查找值, 查找区域, 返回第几列, 精确/近似)。G2 是查找值“P003”，A2:C5 是查找区域，单价在第 3 列，FALSE 表示精确匹配。P003 对应“文件夹”，单价为 8。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：统计某快递网点派件重量</t>
         </is>
       </c>
     </row>
@@ -490,107 +490,137 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，需要统计“华东仓”的总入库重量。请用 SUMIF 按仓库名称汇总重量。</t>
+          <t>要求：你在一家快递网点做台账，需要按“网点”汇总当天派件总重量，方便核算车辆装载情况。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 G2 单元格输入公式，计算“华东仓”的总重量。</t>
+          <t>任务：在 G2 单元格统计“朝阳网点”的总派件重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>货物</t>
+          <t>网点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+          <t>朝阳网点</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SF001</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华南仓</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>80</v>
+          <t>海淀网点</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SF002</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>金属件</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>150</v>
+          <t>朝阳网点</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SF003</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>20.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华北仓</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>60</v>
+          <t>丰台网点</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SF004</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>50</v>
+          <t>朝阳网点</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SF005</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="11">
@@ -603,7 +633,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量区间统计</t>
+          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
         </is>
       </c>
     </row>
@@ -617,14 +647,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：电商运营需要统计订单数量大于等于 100 且小于 200 的订单笔数，用于分析中等订单规模。</t>
+          <t>要求：物流公司需要统计“已到港”且“重量大于等于10kg”的订单数量，用于判断是否需要安排大车提货。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格输入公式，统计数量在 100 到 199 之间的订单笔数。</t>
+          <t>任务：在 F2 单元格统计状态为“已到港”且重量大于等于10kg的订单数量。</t>
         </is>
       </c>
     </row>
@@ -636,12 +666,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>客户</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
@@ -653,11 +683,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>已到港</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -668,11 +698,11 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>运输中</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -683,11 +713,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>已到港</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -698,11 +728,11 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>已到港</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>220</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -713,340 +743,372 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>已到港</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：物流到港天数计算</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：船务台账中记录了预计到港日和实际到港日，需要计算实际到港比预计晚了多少天；如果没有实际到港日，则显示“未到港”。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格计算第2行船舶的到港延误天数；若实际到港日为空，则显示“未到港”。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流专员需要根据到港日期和发货日期，计算每票货物的运输天数。请用 DATEDIF 按“天”计算。</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>船名</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>实际到港日</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，计算 YD001 从发货到到港的运输天数。</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>远洋1号</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>远洋2号</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>远洋3号</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-06-12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>远洋4号</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-06-15</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按重量区间判断运费档位</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：客户编码提取</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：快递计费时，先按重量四舍五入到整数公斤，再判断运费档位：小于等于5kg为“小件”，大于5kg为“大件”。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>练习函数：RIGHT</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格计算四舍五入后的计费重量，在 D2 单元格根据 C2 判断“小件”或“大件”。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：客户编码格式为“城市-序号”，例如“SH-1001”。现在需要提取编码右侧的 4 位序号，方便后续匹配。</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>计费重量</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>档位</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，提取 A2 单元格客户编码右侧的 4 位序号。</t>
-        </is>
-      </c>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KD001</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>客户编码</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>客户姓名</t>
-        </is>
-      </c>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>KD002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>SH-1001</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
+          <t>KD003</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>BJ-1002</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
+          <t>KD004</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>GZ-1003</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>SZ-1004</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：订单表中只有商品名称和数量，需要从商品价格表里查出单价，再计算金额；同时汇总某商品的总销售金额。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：产品单价查表匹配</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 用 XLOOKUP 查出苹果的单价，在 D2 计算金额，并在 G10 汇总苹果的总销售金额。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售助理需要根据产品编号，从价格表中查找对应单价，填入订单表。请用 VLOOKUP 完成精确匹配。</t>
-        </is>
-      </c>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 单元格输入产品编号“P003”，在 H2 单元格输入公式，从 A2:C5 区域查找该产品单价。</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>5</v>
-      </c>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>中性笔</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr"/>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>8</v>
-      </c>
+          <t>商品价格表</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>15</v>
-      </c>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1073,7 +1135,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：统计某快递网点派件重量</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"华东仓",C2:C6)</f>
+        <f>SUMIF(B2:B6,"朝阳网点",D2:D6)</f>
         <v/>
       </c>
     </row>
@@ -1098,7 +1160,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量区间统计</t>
+          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1171,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(C2:C7,"&gt;=100",C2:C7,"&lt;200")</f>
+        <f>COUNTIFS(B2:B6,"已到港",C2:C6,"&gt;=10")</f>
         <v/>
       </c>
     </row>
@@ -1123,7 +1185,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数计算</t>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1196,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,C2,"d")</f>
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"未到港")</f>
         <v/>
       </c>
     </row>
@@ -1148,7 +1210,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：客户编码提取</t>
+          <t>第 4 题：第4题：按重量区间判断运费档位</t>
         </is>
       </c>
     </row>
@@ -1158,9 +1220,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>RIGHT(A2,4)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =ROUND(B2,0)，D2: =IF(C2&lt;=5,"小件","大件")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1173,7 +1236,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品单价查表匹配</t>
+          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1183,9 +1246,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>VLOOKUP(G2,A2:C5,3,FALSE)</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>C2: =XLOOKUP(A2,A8:A10,B8:B10)，D2: =B2*C2，G10: =SUMIFS(D2:D5,A2:A5,"苹果")</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1216,7 +1280,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：统计某快递网点派件重量</t>
         </is>
       </c>
     </row>
@@ -1228,14 +1292,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 的语法是 =SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是仓库名称区域，条件是“华东仓”，C2:C6 是重量区域，所以会把华东仓对应的 120、150、50 相加，结果为 320。</t>
+          <t>SUMIF 用于按一个条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6 的网点，条件是“朝阳网点”，求和区域是 D2:D6 的重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量区间统计</t>
+          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1311,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 可以按多个条件计数，语法是 =COUNTIFS(区域1,条件1,区域2,条件2...)。本题对同一个区域 C2:C7 设置两个条件：&gt;=100 和 &lt;200，满足条件的订单有 A002、A003、A005、A006，共 4 笔。</t>
+          <t>COUNTIFS 用于多条件计数。语法：COUNTIFS(区域1,条件1,区域2,条件2...)。这里统计 B 列为“已到港”，且 C 列重量大于等于10的行数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数计算</t>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1266,14 +1330,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 的语法是 =DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数。B2 是 2025-01-01，C2 是 2025-01-06，相差 5 天，所以结果为 5。</t>
+          <t>DATEDIF 可计算两个日期之间的天数，语法：DATEDIF(开始日期,结束日期,"d")。当 C2 为空时 DATEDIF 会报错，所以用 IFERROR 包住，出错时返回“未到港”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：客户编码提取</t>
+          <t>第 4 题：第4题：按重量区间判断运费档位</t>
         </is>
       </c>
     </row>
@@ -1285,14 +1349,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT 的语法是 =RIGHT(文本, 提取字符数)。A2 为“SH-1001”，右侧 4 位是“1001”，所以公式返回 1001。</t>
+          <t>ROUND(数值,0) 表示四舍五入到整数。IF(条件,成立时结果,不成立时结果) 用于二选一判断。先算计费重量，再按计费重量判断档位。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品单价查表匹配</t>
+          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1368,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 的语法是 =VLOOKUP(查找值, 查找区域, 返回第几列, 精确/近似)。G2 是查找值“P003”，A2:C5 是查找区域，单价在第 3 列，FALSE 表示精确匹配。P003 对应“文件夹”，单价为 8。</t>
+          <t>XLOOKUP 语法：XLOOKUP(查找值,查找区域,返回区域)，这里用商品名在价格表中查单价。金额=数量×单价。SUMIFS 可对商品为“苹果”的金额求和。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某快递网点派件重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家快递网点做台账，需要按“网点”汇总当天派件总重量，方便核算车辆装载情况。</t>
+          <t>要求：你是仓库文员，需要统计某个供应商本月入库的总重量，方便月底对账。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 G2 单元格统计“朝阳网点”的总派件重量。</t>
+          <t>任务：在 F2 单元格输入公式，统计供应商为“华信”的总重量。</t>
         </is>
       </c>
     </row>
@@ -509,118 +509,118 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>网点</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>货物</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>重量kg</t>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华信</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SF001</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>海淀网点</t>
+          <t>佳通</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SF002</t>
+          <t>塑料件</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华信</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SF003</t>
+          <t>泡沫</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>丰台网点</t>
+          <t>瑞达</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SF004</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>朝阳网点</t>
+          <t>华信</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SF005</t>
+          <t>塑料件</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -633,28 +633,28 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
+          <t>第 2 题：第2题：订单数量计数</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司需要统计“已到港”且“重量大于等于10kg”的订单数量，用于判断是否需要安排大车提货。</t>
+          <t>要求：电商客服需要统计“已完成”状态的订单数量，以便填写日报。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格统计状态为“已到港”且重量大于等于10kg的订单数量。</t>
+          <t>任务：在 F2 单元格输入公式，统计状态为“已完成”的订单数。</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>重量kg</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
@@ -683,11 +688,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>12</v>
+          <t>张先生</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="19">
@@ -698,11 +708,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>15</v>
+          <t>李女士</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>待付款</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="20">
@@ -713,11 +728,16 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>8</v>
+          <t>王先生</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="21">
@@ -728,11 +748,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>10</v>
+          <t>赵女士</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="22">
@@ -743,11 +768,16 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>已到港</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>20</v>
+          <t>陈先生</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -760,102 +790,106 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：到港天数计算</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：船务台账中记录了预计到港日和实际到港日，需要计算实际到港比预计晚了多少天；如果没有实际到港日，则显示“未到港”。</t>
+          <t>要求：物流专员需要根据到港日期计算货物已经到港多少天，用于提醒客户提货。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格计算第2行船舶的到港延误天数；若实际到港日为空，则显示“未到港”。</t>
+          <t>任务：在 E2 单元格输入公式，计算 BL001 货物从到港日期到今天已经过了多少天。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>船名</t>
+          <t>提单号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>预计到港日</t>
+          <t>货物</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>实际到港日</t>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>远洋1号</t>
+          <t>BL001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>钢材</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>远洋2号</t>
+          <t>BL002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>远洋3号</t>
+          <t>BL003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>远洋4号</t>
+          <t>BL004</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>化工品</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -869,54 +903,54 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按重量区间判断运费档位</t>
+          <t>第 4 题：第4题：销售提成计算</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>要求：快递计费时，先按重量四舍五入到整数公斤，再判断运费档位：小于等于5kg为“小件”，大于5kg为“大件”。</t>
+          <t>要求：销售助理需要按规则计算提成：销售额大于等于 10000 提成 5%，否则提成 3%；提成金额保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格计算四舍五入后的计费重量，在 D2 单元格根据 C2 判断“小件”或“大件”。</t>
+          <t>任务：在 D2 单元格输入公式，根据 B2 销售额计算提成金额，并保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>重量kg</t>
+          <t>销售额</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>计费重量</t>
+          <t>提成比例</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>档位</t>
+          <t>提成金额</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>KD001</t>
+          <t>刘一</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4.6</v>
+        <v>12000</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -924,11 +958,11 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>KD002</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>5.4</v>
+        <v>8000</v>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
@@ -936,11 +970,11 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>KD003</t>
+          <t>吴三</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>3.2</v>
+        <v>15000</v>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
@@ -948,11 +982,11 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>KD004</t>
+          <t>郑四</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>8.1</v>
+        <v>9500</v>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr"/>
@@ -967,148 +1001,118 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
+          <t>第 5 题：第5题：商品信息查表匹配</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>要求：订单表中只有商品名称和数量，需要从商品价格表里查出单价，再计算金额；同时汇总某商品的总销售金额。</t>
+          <t>要求：客服收到客户询问商品编码，需要根据商品名称快速查出单价；如果查不到，显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 用 XLOOKUP 查出苹果的单价，在 D2 计算金额，并在 G10 汇总苹果的总销售金额。</t>
+          <t>任务：在 F2 单元格输入公式，根据 E2 中的商品名称“显示器”查找对应单价；如果查不到，显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>商品编码</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>商品名称</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
           <t>单价</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>无线鼠标</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>机械键盘</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>299</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>899</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>U盘</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr"/>
-      <c r="B53" s="4" t="inlineStr"/>
-      <c r="C53" s="4" t="inlineStr"/>
-      <c r="D53" s="4" t="inlineStr"/>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>摄像头</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>商品价格表</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1135,7 +1139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某快递网点派件重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1150,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"朝阳网点",D2:D6)</f>
+        <f>SUMIF(B2:B6,"华信",D2:D6)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1164,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
+          <t>第 2 题：第2题：订单数量计数</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1175,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B6,"已到港",C2:C6,"&gt;=10")</f>
+        <f>COUNTIF(C2:C6,"已完成")</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1189,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1200,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"未到港")</f>
+        <f>DATEDIF(C2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1210,7 +1214,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按重量区间判断运费档位</t>
+          <t>第 4 题：第4题：销售提成计算</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1224,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =ROUND(B2,0)，D2: =IF(C2&lt;=5,"小件","大件")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>ROUND(IF(B2&gt;=10000,B2*0.05,B2*0.03),2)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1236,7 +1239,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
+          <t>第 5 题：第5题：商品信息查表匹配</t>
         </is>
       </c>
     </row>
@@ -1246,10 +1249,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>C2: =XLOOKUP(A2,A8:A10,B8:B10)，D2: =B2*C2，G10: =SUMIFS(D2:D5,A2:A5,"苹果")</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IFERROR(VLOOKUP(E2,B2:C6,2,FALSE),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1280,7 +1282,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某快递网点派件重量</t>
+          <t>第 1 题：第1题：仓库入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1292,14 +1294,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按一个条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6 的网点，条件是“朝阳网点”，求和区域是 D2:D6 的重量。</t>
+          <t>SUMIF 用于按条件求和，语法：=SUMIF(条件区域, 条件, 求和区域)。这里条件区域是供应商列 B2:B6，条件是“华信”，求和区域是重量列 D2:D6，结果为 120+45+70=235。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标且已到港的订单数</t>
+          <t>第 2 题：第2题：订单数量计数</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1313,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数。语法：COUNTIFS(区域1,条件1,区域2,条件2...)。这里统计 B 列为“已到港”，且 C 列重量大于等于10的行数。</t>
+          <t>COUNTIF 用于按条件计数，语法：=COUNTIF(条件区域, 条件)。这里统计 C2:C6 中等于“已完成”的单元格个数，结果为 3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1330,14 +1332,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 可计算两个日期之间的天数，语法：DATEDIF(开始日期,结束日期,"d")。当 C2 为空时 DATEDIF 会报错，所以用 IFERROR 包住，出错时返回“未到港”。</t>
+          <t>TODAY() 返回今天的日期；DATEDIF 用于计算两个日期之间的差值，语法：=DATEDIF(开始日期, 结束日期, "d")，其中 "d" 表示天数。这里从 C2 的到港日期算到今天。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按重量区间判断运费档位</t>
+          <t>第 4 题：第4题：销售提成计算</t>
         </is>
       </c>
     </row>
@@ -1349,14 +1351,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROUND(数值,0) 表示四舍五入到整数。IF(条件,成立时结果,不成立时结果) 用于二选一判断。先算计费重量，再按计费重量判断档位。</t>
+          <t>IF 用于条件判断，语法：=IF(条件, 真值, 假值)。ROUND 用于四舍五入，语法：=ROUND(数字, 小数位数)。这里先判断销售额是否大于等于 10000，再按比例计算，最后保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP 查商品单价并计算金额</t>
+          <t>第 5 题：第5题：商品信息查表匹配</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1370,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法：XLOOKUP(查找值,查找区域,返回区域)，这里用商品名在价格表中查单价。金额=数量×单价。SUMIFS 可对商品为“苹果”的金额求和。</t>
+          <t>VLOOKUP 用于按列查找，语法：=VLOOKUP(查找值, 查找区域, 返回列号, 精确匹配)。这里在 B2:C6 中查找 E2 的商品名称，返回第 2 列单价。IFERROR 用于处理错误，语法：=IFERROR(公式, 错误时显示内容)，查不到时显示“未找到”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,151 +476,129 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIF</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是仓库文员，需要根据发货台账，按“发货地区”汇总重量，并统计“华东”地区中“已发货”的重量。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要统计某个供应商本月入库的总重量，方便月底对账。</t>
+          <t>任务：在空白单元格 F2 计算“华东”地区的总重量；在 F3 计算“华东”地区且状态为“已发货”的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，统计供应商为“华信”的总重量。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>发货地区</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华信</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>120</v>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>佳通</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
+          <t>未发货</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华信</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>泡沫</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>45</v>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>瑞达</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>60</v>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华信</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>70</v>
+          <t>未发货</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -633,486 +611,439 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：订单数量合格判定</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是电商运营助理，需要判断订单是否达到最低发货数量，并对可能出现的异常计算结果显示“数据异常”。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：电商客服需要统计“已完成”状态的订单数量，以便填写日报。</t>
+          <t>任务：在 E2:E6 判断每个订单是否达标：数量大于等于最低要求显示“达标”，否则显示“未达标”。如果数量为空导致计算出错，则显示“数据异常”。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，统计状态为“已完成”的订单数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>最低要求</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>纸巾</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>张先生</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>199</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>李女士</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>待付款</t>
-        </is>
+          <t>牙膏</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>王先生</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
+          <t>洗发水</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="n">
-        <v>299</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>赵女士</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
+          <t>垃圾袋</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>陈先生</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：到港天数与金额取整</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：到港天数计算</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流跟单员，需要根据到港日期计算截至今天的到港天数，并把货物金额四舍五入保留到整数。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：物流专员需要根据到港日期计算货物已经到港多少天，用于提醒客户提货。</t>
+          <t>任务：在 D2:D5 计算每个提单从到港日期到今天已经过去的天数；在 E2:E5 将货物金额四舍五入保留 0 位小数。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，计算 BL001 货物从到港日期到今天已经过了多少天。</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>提单号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>货物金额</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>提单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BL001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1234.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>BL001</t>
+          <t>BL002</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>987.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>BL002</t>
+          <t>BL003</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>木材</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>555.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>BL003</t>
+          <t>BL004</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>设备</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>2000.95</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>BL004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>化工品</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：从商品编码中提取信息</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：销售提成计算</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是商品资料管理员，商品编码有固定格式：前 2 位是仓库代码，中间 3 位是品类代码，最后 4 位是流水号。请从编码中提取流水号后 2 位和品类代码。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>要求：销售助理需要按规则计算提成：销售额大于等于 10000 提成 5%，否则提成 3%；提成金额保留两位小数。</t>
+          <t>任务：在 C2:C5 提取商品编码最后 2 位作为流水尾号；在 D2:D5 提取第 3 到第 5 位作为品类代码。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式，根据 B2 销售额计算提成金额，并保留两位小数。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>提成比例</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>提成金额</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SH001A1001</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>马克杯</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>刘一</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
+          <t>GZ002B2035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>收纳盒</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
+          <t>SH003C7788</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>台灯</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>吴三</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
+          <t>BJ004D5602</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>郑四</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：按商品名称查价格与库存</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：商品信息查表匹配</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是销售助理，需要根据订单表中的商品名称，从商品价格表中查找对应单价和库存。请分别练习 XLOOKUP、VLOOKUP 以及 INDEX+MATCH 三种查表方式。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>要求：客服收到客户询问商品编码，需要根据商品名称快速查出单价；如果查不到，显示“未找到”。</t>
+          <t>任务：在 G2 根据 F2 中的商品名称用 XLOOKUP 查找单价；在 G3 用 VLOOKUP 查找库存；在 G4 用 INDEX+MATCH 查找单价。假设 F2 是“台灯”，F3 是“笔记本”，F4 是“收纳盒”。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，根据 E2 中的商品名称“显示器”查找对应单价；如果查不到，显示“未找到”。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>库存</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>马克杯</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>无线鼠标</t>
-        </is>
+          <t>收纳盒</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>39.9</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>机械键盘</t>
-        </is>
+          <t>台灯</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>89</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>299</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>12.5</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>899</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>U盘</t>
-        </is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>3.5</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>49</v>
+        <v>500</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>摄像头</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1139,7 +1070,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1149,9 +1080,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"华信",D2:D6)</f>
-        <v/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>F2: =SUMIF(A2:A7,"华东",C2:C7) ；F3: =SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"已发货")</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1164,7 +1096,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：订单数量合格判定</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1107,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(C2:C6,"已完成")</f>
+        <f>IFERROR(IF(C2&gt;=D2,"达标","未达标"),"数据异常")</f>
         <v/>
       </c>
     </row>
@@ -1189,7 +1121,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数计算</t>
+          <t>第 3 题：第3题：到港天数与金额取整</t>
         </is>
       </c>
     </row>
@@ -1199,9 +1131,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>DATEDIF(C2,TODAY(),"d")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D2: =DATEDIF(B2,TODAY(),"d") ；E2: =ROUND(C2,0)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1214,7 +1147,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：销售提成计算</t>
+          <t>第 4 题：第4题：从商品编码中提取信息</t>
         </is>
       </c>
     </row>
@@ -1224,9 +1157,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>ROUND(IF(B2&gt;=10000,B2*0.05,B2*0.03),2)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =RIGHT(A2,2) ；D2: =MID(A2,3,3)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1239,7 +1173,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品信息查表匹配</t>
+          <t>第 5 题：第5题：按商品名称查价格与库存</t>
         </is>
       </c>
     </row>
@@ -1249,9 +1183,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(VLOOKUP(E2,B2:C6,2,FALSE),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>G2: =XLOOKUP(F2,A2:A6,B2:B6) ；G3: =VLOOKUP(F3,A2:C6,3,FALSE) ；G4: =INDEX(B2:B6,MATCH(F4,A2:A6,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1282,7 +1217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1229,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按条件求和，语法：=SUMIF(条件区域, 条件, 求和区域)。这里条件区域是供应商列 B2:B6，条件是“华信”，求和区域是重量列 D2:D6，结果为 120+45+70=235。</t>
+          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题先按地区汇总重量，再叠加状态条件统计华东已发货重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：订单数量合格判定</t>
         </is>
       </c>
     </row>
@@ -1313,14 +1248,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法：=COUNTIF(条件区域, 条件)。这里统计 C2:C6 中等于“已完成”的单元格个数，结果为 3。</t>
+          <t>IF 函数语法为 IF(判断条件, 条件成立返回值, 条件不成立返回值)。IFERROR 函数语法为 IFERROR(原公式, 出错时显示内容)。先用 IF 判断数量是否达到最低要求，再外套 IFERROR，避免空值或异常数据造成错误显示。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数计算</t>
+          <t>第 3 题：第3题：到港天数与金额取整</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1267,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期；DATEDIF 用于计算两个日期之间的差值，语法：=DATEDIF(开始日期, 结束日期, "d")，其中 "d" 表示天数。这里从 C2 的到港日期算到今天。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF 语法为 DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。ROUND 语法为 ROUND(数值, 保留小数位数)，第二位为 0 表示四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：销售提成计算</t>
+          <t>第 4 题：第4题：从商品编码中提取信息</t>
         </is>
       </c>
     </row>
@@ -1351,14 +1286,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IF 用于条件判断，语法：=IF(条件, 真值, 假值)。ROUND 用于四舍五入，语法：=ROUND(数字, 小数位数)。这里先判断销售额是否大于等于 10000，再按比例计算，最后保留两位小数。</t>
+          <t>RIGHT 函数语法为 RIGHT(文本, 提取字符数)，用于从右侧提取指定长度字符。MID 函数语法为 MID(文本, 开始位置, 提取字符数)，用于从指定位置开始提取字符。本题用 RIGHT 取最后 2 位，用 MID 从第 3 位开始取 3 位。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品信息查表匹配</t>
+          <t>第 5 题：第5题：按商品名称查价格与库存</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1305,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 用于按列查找，语法：=VLOOKUP(查找值, 查找区域, 返回列号, 精确匹配)。这里在 B2:C6 中查找 E2 的商品名称，返回第 2 列单价。IFERROR 用于处理错误，语法：=IFERROR(公式, 错误时显示内容)，查不到时显示“未找到”。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，默认精确匹配，简单直观。VLOOKUP 语法为 VLOOKUP(查找值, 表格区域, 返回列号, FALSE)，其中 FALSE 表示精确匹配。INDEX+MATCH 中，MATCH 定位查找值在区域中的位置，INDEX 根据位置返回对应结果，适合更灵活的查表。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,129 +476,121 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是仓库文员，需要根据发货台账，按“发货地区”汇总重量，并统计“华东”地区中“已发货”的重量。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 F2 计算“华东”地区的总重量；在 F3 计算“华东”地区且状态为“已发货”的总重量。</t>
+          <t>要求：你负责管理一个电商仓库的出库台账。现在需要按仓库名称汇总出库重量，用于日报统计。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>发货地区</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 E2 输入公式，计算“上海仓”的出库总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>120</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>出库重量</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>A款</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>未发货</t>
+          <t>B款</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>C款</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>A款</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>未发货</t>
+          <t>B款</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -611,28 +603,28 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量合格判定</t>
+          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你是电商运营助理，需要判断订单是否达到最低发货数量，并对可能出现的异常计算结果显示“数据异常”。</t>
+          <t>要求：物流主管需要快速查看广州仓的订单笔数，并找出所有订单中最大的单笔出库重量，用于异常检查。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2:E6 判断每个订单是否达标：数量大于等于最低要求显示“达标”，否则显示“未达标”。如果数量为空导致计算出错，则显示“数据异常”。</t>
+          <t>任务：请在单元格 E2 输入公式统计“广州仓”的订单数量；在单元格 E3 输入公式计算所有订单中的最大出库重量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -642,102 +634,84 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>最低要求</t>
+          <t>出库重量</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>纸巾</t>
+          <t>A款</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>洗衣液</t>
+          <t>B款</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>牙膏</t>
+          <t>C款</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>洗发水</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="n">
-        <v>90</v>
+          <t>A款</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>垃圾袋</t>
+          <t>B款</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -749,301 +723,291 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与金额取整</t>
+          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流跟单员，需要根据到港日期计算截至今天的到港天数，并把货物金额四舍五入保留到整数。</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2:D5 计算每个提单从到港日期到今天已经过去的天数；在 E2:E5 将货物金额四舍五入保留 0 位小数。</t>
+          <t>要求：客服收到一个订单号 D1003，需要从订单明细表中快速查出对应客户名称和金额。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>提单号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>货物金额</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 E2 输入公式，根据 E1 中的订单号“D1003”查找对应客户名称。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>BL001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1234.56</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>BL002</t>
+          <t>D1001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>987.49</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>BL003</t>
+          <t>D1002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>555.55</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>BL004</t>
+          <t>D1003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2000.95</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>D1004</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从商品编码中提取信息</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是商品资料管理员，商品编码有固定格式：前 2 位是仓库代码，中间 3 位是品类代码，最后 4 位是流水号。请从编码中提取流水号后 2 位和品类代码。</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2:C5 提取商品编码最后 2 位作为流水尾号；在 D2:D5 提取第 3 到第 5 位作为品类代码。</t>
+          <t>要求：商品部需要根据商品编号从价格表中查找单价，如果编号不存在，希望显示“未找到”，避免出现错误值。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 E2 输入公式，根据 E1 中的商品编号“P003”查找单价；如果查不到，则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>SH001A1001</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>马克杯</t>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>GZ002B2035</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>收纳盒</t>
-        </is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>SH003C7788</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>台灯</t>
-        </is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>BJ004D5602</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
-        </is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>699</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按商品名称查价格与库存</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是销售助理，需要根据订单表中的商品名称，从商品价格表中查找对应单价和库存。请分别练习 XLOOKUP、VLOOKUP 以及 INDEX+MATCH 三种查表方式。</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>任务：在 G2 根据 F2 中的商品名称用 XLOOKUP 查找单价；在 G3 用 VLOOKUP 查找库存；在 G4 用 INDEX+MATCH 查找单价。假设 F2 是“台灯”，F3 是“笔记本”，F4 是“收纳盒”。</t>
+          <t>要求：物流跟单员需要计算货物从发运日期到今天已经过去的天数，同时从订单编号中提取后三位作为批次号，方便内部登记。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>库存</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 D2 输入公式，计算第一条订单从发运日期到今天的到港天数；在单元格 E2 输入公式，提取订单编号“ORD202405001”的后三位。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>马克杯</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>120</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>收纳盒</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>80</v>
+          <t>ORD202405001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>台灯</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>45</v>
+          <t>ORD202405002</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>200</v>
+          <t>ORD202405003</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1070,7 +1034,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
         </is>
       </c>
     </row>
@@ -1080,10 +1044,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>F2: =SUMIF(A2:A7,"华东",C2:C7) ；F3: =SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"已发货")</t>
-        </is>
+      <c r="B2" s="2">
+        <f>SUMIFS(C2:C6,A2:A6,"上海仓")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1096,7 +1059,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量合格判定</t>
+          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
         </is>
       </c>
     </row>
@@ -1106,9 +1069,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>IFERROR(IF(C2&gt;=D2,"达标","未达标"),"数据异常")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>E2：=COUNTIF(A2:A6,"广州仓")；E3：=MAX(C2:C6)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1121,7 +1085,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与金额取整</t>
+          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
         </is>
       </c>
     </row>
@@ -1131,10 +1095,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>D2: =DATEDIF(B2,TODAY(),"d") ；E2: =ROUND(C2,0)</t>
-        </is>
+      <c r="B10" s="2">
+        <f>VLOOKUP(E1,A2:C5,2,FALSE)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1147,7 +1110,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从商品编码中提取信息</t>
+          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
         </is>
       </c>
     </row>
@@ -1157,10 +1120,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =RIGHT(A2,2) ；D2: =MID(A2,3,3)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(XLOOKUP(E1,A2:A5,C2:C5,"未找到"),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1173,7 +1135,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按商品名称查价格与库存</t>
+          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1147,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>G2: =XLOOKUP(F2,A2:A6,B2:B6) ；G3: =VLOOKUP(F3,A2:C6,3,FALSE) ；G4: =INDEX(B2:B6,MATCH(F4,A2:A6,0))</t>
+          <t>D2：=DATEDIF(B2,TODAY(),"d")；E2：=RIGHT(A2,3)</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1191,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题先按地区汇总重量，再叠加状态条件统计华东已发货重量。</t>
+          <t>SUMIFS 用于按一个或多个条件对指定区域求和。语法为 =SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题求和区域是 C2:C6 的出库重量，条件区域是 A2:A6，条件是“上海仓”。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量合格判定</t>
+          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
         </is>
       </c>
     </row>
@@ -1248,14 +1210,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IF 函数语法为 IF(判断条件, 条件成立返回值, 条件不成立返回值)。IFERROR 函数语法为 IFERROR(原公式, 出错时显示内容)。先用 IF 判断数量是否达到最低要求，再外套 IFERROR，避免空值或异常数据造成错误显示。</t>
+          <t>COUNTIF 用于统计满足条件的单元格个数，语法为 =COUNTIF(条件区域, 条件)。MAX 用于返回一组数值中的最大值，语法为 =MAX(数值区域)。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与金额取整</t>
+          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1229,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF 语法为 DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。ROUND 语法为 ROUND(数值, 保留小数位数)，第二位为 0 表示四舍五入到整数。</t>
+          <t>VLOOKUP 用于在表格首列查找值，并返回指定列的数据。语法为 =VLOOKUP(查找值, 查找区域, 返回列序号, 匹配方式)。第四参数 FALSE 表示精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从商品编码中提取信息</t>
+          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
         </is>
       </c>
     </row>
@@ -1286,14 +1248,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT 函数语法为 RIGHT(文本, 提取字符数)，用于从右侧提取指定长度字符。MID 函数语法为 MID(文本, 开始位置, 提取字符数)，用于从指定位置开始提取字符。本题用 RIGHT 取最后 2 位，用 MID 从第 3 位开始取 3 位。</t>
+          <t>XLOOKUP 用于在一个区域中查找值，并返回另一个区域中对应的结果。语法为 =XLOOKUP(查找值, 查找区域, 返回区域, 未找到时显示值)。IFERROR 用于捕获错误并返回指定内容，语法为 =IFERROR(公式, 错误时显示值)。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按商品名称查价格与库存</t>
+          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1267,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，默认精确匹配，简单直观。VLOOKUP 语法为 VLOOKUP(查找值, 表格区域, 返回列号, FALSE)，其中 FALSE 表示精确匹配。INDEX+MATCH 中，MATCH 定位查找值在区域中的位置，INDEX 根据位置返回对应结果，适合更灵活的查表。</t>
+          <t>DATEDIF 用于计算两个日期之间的差值，语法为 =DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。TODAY 返回今天的日期。RIGHT 用于从文本右侧提取指定数量的字符，语法为 =RIGHT(文本, 字符数)。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,28 +476,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责管理一个电商仓库的出库台账。现在需要按仓库名称汇总出库重量，用于日报统计。</t>
+          <t>要求：你是仓库管理员，现有一份入库台账，记录了每个仓库的入库件数。老板想知道『上海仓』一共入库了多少件。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E2 输入公式，计算“上海仓”的出库总重量。</t>
+          <t>任务：假设数据在 A1:B7，请在 D2 单元格输入公式，计算『上海仓』的入库件数合计。</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>出库重量</t>
+          <t>入库件数</t>
         </is>
       </c>
     </row>
@@ -524,13 +519,8 @@
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>A款</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+      <c r="B6" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +529,8 @@
           <t>北京仓</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>B款</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>80</v>
+      <c r="B7" s="4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -554,13 +539,8 @@
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>C款</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>95</v>
+      <c r="B8" s="4" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +549,8 @@
           <t>广州仓</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>A款</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>110</v>
+      <c r="B9" s="4" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -584,133 +559,106 @@
           <t>上海仓</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>B款</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>60</v>
+      <c r="B10" s="4" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流主管需要快速查看广州仓的订单笔数，并找出所有订单中最大的单笔出库重量，用于异常检查。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E2 输入公式统计“广州仓”的订单数量；在单元格 E3 输入公式计算所有订单中的最大出库重量。</t>
+          <t>要求：物流专员需要跟踪每批货物的到港天数。『到港日期』已记录，今天日期用 TODAY() 自动获取，计算从到港到今天已经过了多少天。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>出库重量</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:B5，请在 C2 单元格输入公式，计算 L001 批次从到港日期到今天的总天数，并向下填充到 C5。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>A款</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>120</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>B款</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>80</v>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>C款</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>95</v>
+          <t>2024-05-10</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>A款</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>110</v>
+          <t>2024-05-18</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>L004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>B款</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>60</v>
+          <t>2024-05-25</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -723,291 +671,340 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
+          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：财务需要按重量区间统计运费。现有一份运单明细，包含『重量(kg)』和『运费(元)』。要求统计重量大于等于100kg且小于500kg的运单运费总和，并将结果四舍五入保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：客服收到一个订单号 D1003，需要从订单明细表中快速查出对应客户名称和金额。</t>
+          <t>任务：假设数据在 A1:C7，请在 E2 单元格输入公式，统计重量 &gt;=100 且 &lt;500 的运费合计，结果四舍五入保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在单元格 E2 输入公式，根据 E1 中的订单号“D1003”查找对应客户名称。</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>运费(元)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Y001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>120.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>D1001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
+          <t>Y002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>199</v>
+        <v>240.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>D1002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
+          <t>Y003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>300</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>350</v>
+        <v>500.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>D1003</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
+          <t>Y004</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>450</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>128</v>
+        <v>760.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>D1004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
+          <t>Y005</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Y006</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>200.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品部需要根据商品编号从价格表中查找单价，如果编号不存在，希望显示“未找到”，避免出现错误值。</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E2 输入公式，根据 E1 中的商品编号“P003”查找单价；如果查不到，则显示“未找到”。</t>
+          <t>要求：客服收到客户询问运单号『Y003』的运费。你需要根据运单明细表，用 VLOOKUP 精确查找运费；如果运单号不存在，则显示『未找到』而不是错误值。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C5，请在 E2 输入要查询的运单号『Y003』，在 F2 单元格输入公式，返回该运单的运费；若查不到则显示『未找到』。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>89</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>收货人</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>运费(元)</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>Y001</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>45</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>Y002</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>699</v>
+        <v>240.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>Y003</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>耳机</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>129</v>
+        <v>500.3</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Y004</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>760.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流跟单员需要计算货物从发运日期到今天已经过去的天数，同时从订单编号中提取后三位作为批次号，方便内部登记。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 D2 输入公式，计算第一条订单从发运日期到今天的到港天数；在单元格 E2 输入公式，提取订单编号“ORD202405001”的后三位。</t>
+          <t>要求：运费表中行是目的地，列是重量档位。现在需要根据客户指定的『目的地』和『重量档位』，精确查出对应运费。相比 VLOOKUP，INDEX+MATCH 可以向左查、也可以双向查。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:D5，请在 F2 输入目的地『上海』，G2 输入重量档位『101-200kg』，在 H2 单元格用 INDEX+MATCH 查出对应运费。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>ORD202405001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>0-50kg</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>51-100kg</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>101-200kg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ORD202405002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>ORD202405003</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-15</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1034,7 +1031,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1042,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C6,A2:A6,"上海仓")</f>
+        <f>SUMIF(A2:A7,"上海仓",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1056,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
+          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1069,10 +1066,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>E2：=COUNTIF(A2:A6,"广州仓")；E3：=MAX(C2:C6)</t>
-        </is>
+      <c r="B6" s="2">
+        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1085,7 +1081,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
+          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1092,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(E1,A2:C5,2,FALSE)</f>
+        <f>ROUND(SUMIFS(C2:C7,B2:B7,"&gt;=100",B2:B7,"&lt;500"),1)</f>
         <v/>
       </c>
     </row>
@@ -1110,7 +1106,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
+          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1117,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(XLOOKUP(E1,A2:A5,C2:C5,"未找到"),"未找到")</f>
+        <f>IFERROR(VLOOKUP(E2,A2:C5,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1135,7 +1131,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1141,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>D2：=DATEDIF(B2,TODAY(),"d")；E2：=RIGHT(A2,3)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>INDEX(B2:D5,MATCH(F2,A2:A5,0),MATCH(G2,B1:D1,0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1179,7 +1174,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的出库重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1186,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于按一个或多个条件对指定区域求和。语法为 =SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题求和区域是 C2:C6 的出库重量，条件区域是 A2:A6，条件是“上海仓”。</t>
+          <t>SUMIF 语法：=SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7（仓库列），条件是"上海仓"，求和区域是 B2:B7（件数列）。它会把所有满足『仓库=上海仓』的件数相加，得到 320+250+130=700。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计订单数量和最大出库重量</t>
+          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1205,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于统计满足条件的单元格个数，语法为 =COUNTIF(条件区域, 条件)。MAX 用于返回一组数值中的最大值，语法为 =MAX(数值区域)。</t>
+          <t>TODAY() 返回今天的日期，并会自动更新。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数，"d" 表示按天计算。公式 =DATEDIF(B2,TODAY(),"d") 即从到港日期 B2 到今天相差的天数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按订单号精确查找客户名称</t>
+          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1224,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 用于在表格首列查找值，并返回指定列的数据。语法为 =VLOOKUP(查找值, 查找区域, 返回列序号, 匹配方式)。第四参数 FALSE 表示精确匹配。</t>
+          <t>SUMIFS 语法：=SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里对 C2:C7 求和，条件为 B2:B7 大于等于100且小于500。ROUND(数值,1) 把结果四舍五入到 1 位小数。符合条件的运费是 240.8+500.3+760.2+200.6=1701.9，结果仍为 1701.9。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据商品编号查找价格并处理查不到的情况</t>
+          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1248,14 +1243,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 用于在一个区域中查找值，并返回另一个区域中对应的结果。语法为 =XLOOKUP(查找值, 查找区域, 返回区域, 未找到时显示值)。IFERROR 用于捕获错误并返回指定内容，语法为 =IFERROR(公式, 错误时显示值)。</t>
+          <t>VLOOKUP(查找值, 查找区域, 返回第几列, FALSE) 表示精确查找。这里在 A2:C5 的第一列查找 E2 的运单号，返回第 3 列的运费。IFERROR(公式,"未找到") 表示如果公式出错就显示『未找到』。Y003 对应运费 500.3。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算到港天数并提取订单编号后三位</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1262,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的差值，语法为 =DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。TODAY 返回今天的日期。RIGHT 用于从文本右侧提取指定数量的字符，语法为 =RIGHT(文本, 字符数)。</t>
+          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置。第一个 MATCH 在 A2:A5 中找到『上海』在第 2 行；第二个 MATCH 在 B1:D1 中找到『101-200kg』在第 3 列。INDEX(B2:D5, 行号, 列号) 返回该行列交叉处的值，即 100。这样就实现了按行、按列的双向精确查找。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,101 +476,136 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，现有一份入库台账，记录了每个仓库的入库件数。老板想知道『上海仓』一共入库了多少件。</t>
+          <t>要求：你在一家物流公司做运营助理，需要从「运输台账」中按「线路」汇总「重量(kg)」。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:B7，请在 D2 单元格输入公式，计算『上海仓』的入库件数合计。</t>
+          <t>任务：在空白单元格 G2 中输入公式，计算「线路」为“华东线”的「重量(kg)」总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>入库件数</t>
+          <t>线路</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>320</v>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>180</v>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>华南线</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>250</v>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>400</v>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>华北线</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>130</v>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>220</v>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>华南线</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="12">
@@ -583,28 +618,28 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
+          <t>第 2 题：第2题：到港天数与超期判断</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：物流专员需要跟踪每批货物的到港天数。『到港日期』已记录，今天日期用 TODAY() 自动获取，计算从到港到今天已经过了多少天。</t>
+          <t>要求：你在做进口货物跟踪表，需要根据「到港日期」计算从今天起已经过了多少天，并判断是否超过 30 天。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:B5，请在 C2 单元格输入公式，计算 L001 批次从到港日期到今天的总天数，并向下填充到 C5。</t>
+          <t>任务：在 C2 输入公式计算 A001 从到港日期到今天的天数；在 D2 输入公式：如果天数大于 30，显示“超期”，否则显示“正常”。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>批次号</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -616,48 +651,48 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-04-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>L004</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-18</t>
         </is>
       </c>
     </row>
@@ -671,117 +706,129 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
+          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>要求：财务需要按重量区间统计运费。现有一份运单明细，包含『重量(kg)』和『运费(元)』。要求统计重量大于等于100kg且小于500kg的运单运费总和，并将结果四舍五入保留1位小数。</t>
+          <t>要求：销售台账中记录了每笔订单的「地区」和「金额」。你需要统计「华东」地区金额大于等于 1000 的订单笔数，并找出所有订单中的最高金额。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C7，请在 E2 单元格输入公式，统计重量 &gt;=100 且 &lt;500 的运费合计，结果四舍五入保留 1 位小数。</t>
+          <t>任务：在 F2 输入公式统计「地区」为“华东”且「金额」&gt;=1000 的订单笔数；在 F3 输入公式计算「金额」列的最大值。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>运费(元)</t>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Y001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>80</v>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>120.5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Y002</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>150</v>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>240.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Y003</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>300</v>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>500.3</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Y004</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>450</v>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>760.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Y005</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>50</v>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Y006</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>120</v>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>200.6</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="34">
@@ -794,217 +841,200 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
+          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>要求：客服收到客户询问运单号『Y003』的运费。你需要根据运单明细表，用 VLOOKUP 精确查找运费；如果运单号不存在，则显示『未找到』而不是错误值。</t>
+          <t>要求：仓库称重记录中，重量有小数。你需要先把每件货物重量四舍五入到整数，再按「品类」汇总重量。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:C5，请在 E2 输入要查询的运单号『Y003』，在 F2 单元格输入公式，返回该运单的运费；若查不到则显示『未找到』。</t>
+          <t>任务：在 C2 输入公式把 B2 的重量四舍五入到整数；在 E2 输入公式汇总「品类」为“电子产品”的四舍五入后重量总和。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>品类</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>收货人</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>运费(元)</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Y001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>120.5</v>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>12.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Y002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>240.8</v>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>8.76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Y003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>500.3</v>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>5.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Y004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>760.2</v>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>7.89</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：运费表中行是目的地，列是重量档位。现在需要根据客户指定的『目的地』和『重量档位』，精确查出对应运费。相比 VLOOKUP，INDEX+MATCH 可以向左查、也可以双向查。</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:D5，请在 F2 输入目的地『上海』，G2 输入重量档位『101-200kg』，在 H2 单元格用 INDEX+MATCH 查出对应运费。</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>0-50kg</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>51-100kg</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>101-200kg</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张库存表，需要根据「商品编号」快速查出对应的「商品名称」和「库存数量」。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>90</v>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F2 输入商品编号“P1003”，在 G2 输入公式查出对应的「商品名称」；在 H2 输入公式查出对应的「库存数量」。</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>100</v>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>库存数量</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>40</v>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>无线鼠标</t>
+        </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>45</v>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>机械键盘</t>
+        </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P1003</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>P1004</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>USB线</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1031,7 +1061,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1072,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"上海仓",B2:B7)</f>
+        <f>SUMIFS(C2:C7,B2:B7,"华东线")</f>
         <v/>
       </c>
     </row>
@@ -1056,7 +1086,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
+          <t>第 2 题：第2题：到港天数与超期判断</t>
         </is>
       </c>
     </row>
@@ -1066,9 +1096,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>C2:=DATEDIF(B2,TODAY(),"d")；D2:=IF(C2&gt;30,"超期","正常")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1081,7 +1112,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
+          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
         </is>
       </c>
     </row>
@@ -1091,9 +1122,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>ROUND(SUMIFS(C2:C7,B2:B7,"&gt;=100",B2:B7,"&lt;500"),1)</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F2:=COUNTIFS(B2:B7,"华东",C2:C7,"&gt;=1000")；F3:=MAX(C2:C7)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1106,7 +1138,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
+          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
         </is>
       </c>
     </row>
@@ -1116,9 +1148,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(E2,A2:C5,3,FALSE),"未找到")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2:=ROUND(B2,0)；E2:=SUMIF(A2:A6,"电子产品",C2:C6)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1131,7 +1164,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
+          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
         </is>
       </c>
     </row>
@@ -1141,9 +1174,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>INDEX(B2:D5,MATCH(F2,A2:A5,0),MATCH(G2,B1:D1,0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>G2:=XLOOKUP(F2,A2:A5,B2:B5)；H2:=XLOOKUP(F2,A2:A5,C2:C5)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1174,7 +1208,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库件数（SUMIF）</t>
+          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
         </is>
       </c>
     </row>
@@ -1186,14 +1220,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法：=SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A7（仓库列），条件是"上海仓"，求和区域是 B2:B7（件数列）。它会把所有满足『仓库=上海仓』的件数相加，得到 320+250+130=700。</t>
+          <t>SUMIFS 用于按多个条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题只有一个条件：线路等于“华东线”，所以对 C2:C7 求和即可。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数（TODAY + DATEDIF）</t>
+          <t>第 2 题：第2题：到港天数与超期判断</t>
         </is>
       </c>
     </row>
@@ -1205,14 +1239,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期，并会自动更新。DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数，"d" 表示按天计算。公式 =DATEDIF(B2,TODAY(),"d") 即从到港日期 B2 到今天相差的天数。</t>
+          <t>TODAY() 返回今天日期；DATEDIF(开始日期, 结束日期, "d") 计算相差天数。IF(条件, 真值, 假值) 用来做条件判断。注意：B2 需是真正的日期格式，若不是可用 DATEVALUE 转换。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按重量区间汇总运费（SUMIFS + ROUND）</t>
+          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
         </is>
       </c>
     </row>
@@ -1224,14 +1258,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法：=SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里对 C2:C7 求和，条件为 B2:B7 大于等于100且小于500。ROUND(数值,1) 把结果四舍五入到 1 位小数。符合条件的运费是 240.8+500.3+760.2+200.6=1701.9，结果仍为 1701.9。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。MAX 返回区域最大值。注意金额条件写作 "&gt;=1000"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 VLOOKUP 查运单运费并处理错误（VLOOKUP + IFERROR）</t>
+          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
         </is>
       </c>
     </row>
@@ -1243,14 +1277,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 查找区域, 返回第几列, FALSE) 表示精确查找。这里在 A2:C5 的第一列查找 E2 的运单号，返回第 3 列的运费。IFERROR(公式,"未找到") 表示如果公式出错就显示『未找到』。Y003 对应运费 500.3。</t>
+          <t>ROUND(数值, 小数位数) 用于四舍五入，0 表示保留整数。SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里求和区域是 C2:C6（已四舍五入后的重量）。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 双向查找运费（INDEX + MATCH）</t>
+          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1296,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置。第一个 MATCH 在 A2:A5 中找到『上海』在第 2 行；第二个 MATCH 在 B1:D1 中找到『101-200kg』在第 3 列。INDEX(B2:D5, 行号, 列号) 返回该行列交叉处的值，即 100。这样就实现了按行、按列的双向精确查找。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)。它比 VLOOKUP 更灵活，不需要列序号，且默认精确匹配。G2 返回商品名称，H2 返回库存数量。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,43 +476,38 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做运营助理，需要从「运输台账」中按「线路」汇总「重量(kg)」。</t>
+          <t>要求：你是仓库文员，需要统计「华东仓」所有发货单的重量总和。样例数据来自一张发货台账，包含仓库和重量两列。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 G2 中输入公式，计算「线路」为“华东线”的「重量(kg)」总和。</t>
+          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，计算出「华东仓」的重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>线路</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>重量(kg)</t>
         </is>
@@ -521,118 +516,95 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1200</v>
+          <t>120</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>华南仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>华南线</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>800</v>
+          <t>80</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1500</v>
+          <t>95</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>华北仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>华北线</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>600</v>
+          <t>60</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>900</v>
+          <t>110</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>华南线</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单数量条件计数</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：到港天数与超期判断</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你在做进口货物跟踪表，需要根据「到港日期」计算从今天起已经过了多少天，并判断是否超过 30 天。</t>
+          <t>要求：电商客服需要统计「已完成」订单的数量，用于日报。样例数据是一张订单状态表。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 输入公式计算 A001 从到港日期到今天的天数；在 D2 输入公式：如果天数大于 30，显示“超期”，否则显示“正常”。</t>
+          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，统计状态为「已完成」的订单数量。</t>
         </is>
       </c>
     </row>
@@ -644,7 +616,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>到港日期</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
@@ -656,7 +628,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -668,7 +640,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>待付款</t>
         </is>
       </c>
     </row>
@@ -680,7 +652,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
@@ -692,349 +664,383 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>已取消</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售台账中记录了每笔订单的「地区」和「金额」。你需要统计「华东」地区金额大于等于 1000 的订单笔数，并找出所有订单中的最高金额。</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 输入公式统计「地区」为“华东”且「金额」&gt;=1000 的订单笔数；在 F3 输入公式计算「金额」列的最大值。</t>
+          <t>要求：物流专员需要根据到港日期和发货日期计算运输天数。如果日期缺失或格式不对，不要显示错误值，而是显示“待补录”。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C4，请在 D2 单元格输入公式并向下填充，计算每单从发货到到港的天数；若无法计算则显示「待补录」。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1200</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>800</v>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1500</v>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>600</v>
-      </c>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>S006</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>2000</v>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：财务需要汇总「华东区」且「已签收」的运费总额，并把结果保留 1 位小数。样例数据是区域运费明细表。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，汇总「华东区」且「已签收」的运费，并将结果四舍五入到 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库称重记录中，重量有小数。你需要先把每件货物重量四舍五入到整数，再按「品类」汇总重量。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 输入公式把 B2 的重量四舍五入到整数；在 E2 输入公式汇总「品类」为“电子产品”的四舍五入后重量总和。</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>128.456</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>98.765</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>12.34</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>50.123</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>8.76</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>76.889</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>5.45</v>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>66.666</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>3.21</v>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：多条件订单数量统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：运营需要统计「华东区」且状态为「已付款」的订单数，用于区域销售分析。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，统计区域为「华东区」且状态为「已付款」的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张库存表，需要根据「商品编号」快速查出对应的「商品名称」和「库存数量」。</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 输入商品编号“P1003”，在 G2 输入公式查出对应的「商品名称」；在 H2 输入公式查出对应的「库存数量」。</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>已付款</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>库存数量</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>已付款</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>P1001</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>无线鼠标</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>50</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>未付款</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>P1002</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>机械键盘</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>30</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>已付款</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>P1003</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>20</v>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>已付款</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>P1004</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>USB线</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1061,7 +1067,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1078,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C7,B2:B7,"华东线")</f>
+        <f>SUMIF(A2:A6,"华东仓",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1086,7 +1092,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数与超期判断</t>
+          <t>第 2 题：第2题：订单数量条件计数</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1102,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>C2:=DATEDIF(B2,TODAY(),"d")；D2:=IF(C2&gt;30,"超期","正常")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>COUNTIF(B2:B6,"已完成")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1112,7 +1117,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1127,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>F2:=COUNTIFS(B2:B7,"华东",C2:C7,"&gt;=1000")；F3:=MAX(C2:C7)</t>
-        </is>
+      <c r="B10" s="2">
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"待补录")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1138,7 +1142,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
+          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1152,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2:=ROUND(B2,0)；E2:=SUMIF(A2:A6,"电子产品",C2:C6)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>ROUND(SUMIFS(C2:C6,A2:A6,"华东区",B2:B6,"已签收"),1)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1164,7 +1167,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
+          <t>第 5 题：第5题：多条件订单数量统计</t>
         </is>
       </c>
     </row>
@@ -1174,10 +1177,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2:=XLOOKUP(F2,A2:A5,B2:B5)；H2:=XLOOKUP(F2,A2:A5,C2:C5)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>COUNTIFS(B2:B6,"华东区",C2:C6,"已付款")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按线路汇总重量</t>
+          <t>第 1 题：第1题：仓库发货重量汇总</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1222,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于按多个条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题只有一个条件：线路等于“华东线”，所以对 C2:C7 求和即可。</t>
+          <t>SUMIF 用于按单个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“华东仓”，求和区域是 B2:B6。结果应为 120+95+110=325。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数与超期判断</t>
+          <t>第 2 题：第2题：订单数量条件计数</t>
         </is>
       </c>
     </row>
@@ -1239,14 +1241,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天日期；DATEDIF(开始日期, 结束日期, "d") 计算相差天数。IF(条件, 真值, 假值) 用来做条件判断。注意：B2 需是真正的日期格式，若不是可用 DATEVALUE 转换。</t>
+          <t>COUNTIF 用于按单个条件计数，语法是 COUNTIF(条件区域, 条件)。这里在 B2:B6 中统计“已完成”出现次数，结果为 3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单数量区间计数与最大值</t>
+          <t>第 3 题：第3题：物流到港天数与异常处理</t>
         </is>
       </c>
     </row>
@@ -1258,14 +1260,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。MAX 返回区域最大值。注意金额条件写作 "&gt;=1000"。</t>
+          <t>DATEDIF 可计算两个日期之间的天数，语法是 DATEDIF(开始日期, 结束日期, "d")。IFERROR 用来把错误结果显示为指定内容，语法是 IFERROR(值, 错误时显示内容)。第三行到港日期为空会报错，因此显示“待补录”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：重量四舍五入与单条件求和</t>
+          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1277,14 +1279,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROUND(数值, 小数位数) 用于四舍五入，0 表示保留整数。SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里求和区域是 C2:C6（已四舍五入后的重量）。</t>
+          <t>SUMIFS 支持多个条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。ROUND 用于四舍五入，语法是 ROUND(数值, 小数位数)。先求出 128.456+76.889=205.345，再保留 1 位小数为 205.3。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：XLOOKUP 查表匹配库存</t>
+          <t>第 5 题：第5题：多条件订单数量统计</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1298,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)。它比 VLOOKUP 更灵活，不需要列序号，且默认精确匹配。G2 返回商品名称，H2 返回库存数量。</t>
+          <t>COUNTIFS 用于多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里统计 B 列为“华东区”且 C 列为“已付款”的行，结果为 2。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要统计「华东仓」所有发货单的重量总和。样例数据来自一张发货台账，包含仓库和重量两列。</t>
+          <t>要求：你是仓库文员，需要按“品类”汇总入库重量。现有一张简单入库台账，请统计“纸品”的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，计算出「华东仓」的重量合计。</t>
+          <t>任务：假设数据在A1:B6，请在D2单元格输入公式，计算“纸品”的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>品类</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,61 +516,51 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华南仓</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华北仓</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -583,464 +573,429 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流跟单场景中，需要根据“到港日期”计算截至今天已经到港多少天，用于提醒后续清关。日期以文本展示，实际在Excel中应为日期格式。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：电商客服需要统计「已完成」订单的数量，用于日报。样例数据是一张订单状态表。</t>
+          <t>任务：假设数据在A1:B4，请在C2单元格输入公式，计算YD001截至今天已经到港的天数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，统计状态为「已完成」的订单数量。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>2024-05-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>待付款</t>
+          <t>2024-05-18</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按客户和状态统计订单数</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售助理需要统计“客户为A公司且状态为已发货”的订单数量。如果没有匹配记录，希望显示“无”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在A1:C6，请在E2单元格输入公式，统计客户为“A公司”且状态为“已发货”的订单数；如果结果为0则显示“无”。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流专员需要根据到港日期和发货日期计算运输天数。如果日期缺失或格式不对，不要显示错误值，而是显示“待补录”。</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SO001</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>A公司</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C4，请在 D2 单元格输入公式并向下填充，计算每单从发货到到港的天数；若无法计算则显示「待补录」。</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SO002</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>B公司</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SO003</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>A公司</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>待发货</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>SO004</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>A公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>SO005</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>C公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓储主管需要统计“上海仓”中“纸品”的出库总重量，并将结果保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：财务需要汇总「华东区」且「已签收」的运费总额，并把结果保留 1 位小数。样例数据是区域运费明细表。</t>
+          <t>任务：假设数据在A1:C6，请在E2单元格输入公式，计算“上海仓”中“纸品”的出库总重量，并保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，汇总「华东区」且「已签收」的运费，并将结果四舍五入到 1 位小数。</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>出库重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
-        </is>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>120.456</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>北京仓</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>128.456</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>88.123</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>98.765</t>
-        </is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>60.789</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>50.123</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>95.333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>广州仓</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>76.889</t>
-        </is>
+          <t>纸品</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>70.5</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>华北区</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>66.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：多条件订单数量统计</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：客服需要根据商品编号，从商品资料表中查出售价。现有一张商品资料表和一个查询编号，请完成查表匹配。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在A1:C5，要查询的商品编号“P003”放在E2单元格。请在F2单元格输入公式，返回P003对应的售价。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：运营需要统计「华东区」且状态为「已付款」的订单数，用于区域销售分析。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>售价</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在 A1:C6，请在 E2 单元格输入公式，统计区域为「华东区」且状态为「已付款」的订单数量。</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>8.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>华北区</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>已付款</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1067,7 +1022,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1033,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"华东仓",B2:B6)</f>
+        <f>SUMIF(A2:A6,"纸品",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1092,7 +1047,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"已完成")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1117,7 +1072,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+          <t>第 3 题：第3题：按客户和状态统计订单数</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1083,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"待补录")</f>
+        <f>IFERROR(1/(1/COUNTIFS(B2:B6,"A公司",C2:C6,"已发货")),"无")</f>
         <v/>
       </c>
     </row>
@@ -1142,7 +1097,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
+          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1108,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(SUMIFS(C2:C6,A2:A6,"华东区",B2:B6,"已签收"),1)</f>
+        <f>ROUND(SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"纸品"),1)</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1122,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件订单数量统计</t>
+          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1133,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(B2:B6,"华东区",C2:C6,"已付款")</f>
+        <f>XLOOKUP(E2,A2:A5,C2:C5)</f>
         <v/>
       </c>
     </row>
@@ -1210,7 +1165,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库发货重量汇总</t>
+          <t>第 1 题：第1题：入库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1222,14 +1177,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“华东仓”，求和区域是 B2:B6。结果应为 120+95+110=325。</t>
+          <t>SUMIF用于单条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件是“纸品”，求和区域是B2:B6。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量条件计数</t>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1196,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按单个条件计数，语法是 COUNTIF(条件区域, 条件)。这里在 B2:B6 中统计“已完成”出现次数，结果为 3。</t>
+          <t>TODAY()返回今天日期；DATEDIF用于计算两个日期差。语法：DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。这里用B2作为开始日期，TODAY()作为结束日期。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数与异常处理</t>
+          <t>第 3 题：第3题：按客户和状态统计订单数</t>
         </is>
       </c>
     </row>
@@ -1260,14 +1215,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 可计算两个日期之间的天数，语法是 DATEDIF(开始日期, 结束日期, "d")。IFERROR 用来把错误结果显示为指定内容，语法是 IFERROR(值, 错误时显示内容)。第三行到港日期为空会报错，因此显示“待补录”。</t>
+          <t>COUNTIFS用于多条件计数。语法：COUNTIFS(区域1, 条件1, 区域2, 条件2...)。这里统计B列为A公司且C列为已发货的行数。IFERROR用于处理错误或0结果，公式中“1/(1/数量)”可在数量为0时产生错误，再由IFERROR显示“无”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件运费汇总与四舍五入</t>
+          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
         </is>
       </c>
     </row>
@@ -1279,14 +1234,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 支持多个条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。ROUND 用于四舍五入，语法是 ROUND(数值, 小数位数)。先求出 128.456+76.889=205.345，再保留 1 位小数为 205.3。</t>
+          <t>SUMIFS用于多条件求和。语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里对C列求和，条件是A列为上海仓、B列为纸品。ROUND用于四舍五入，ROUND(数值,1)表示保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件订单数量统计</t>
+          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1253,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里统计 B 列为“华东区”且 C 列为“已付款”的行，结果为 2。</t>
+          <t>XLOOKUP用于按值查找并返回对应结果。语法：XLOOKUP(查找值, 查找区域, 返回区域)。这里在A2:A5中查找E2的“P003”，返回C2:C5中对应售价。也可用INDEX+MATCH：=INDEX(C2:C5,MATCH(E2,A2:A5,0))。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：入库重量汇总</t>
+          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要按“品类”汇总入库重量。现有一张简单入库台账，请统计“纸品”的总重量。</t>
+          <t>要求：你在物流仓库做台账，需要快速汇总某个品类的出库总重量。样例数据记录了不同品类的出库重量，现在要统计“日用品”品类的总出库重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在A1:B6，请在D2单元格输入公式，计算“纸品”的总重量。</t>
+          <t>任务：在空白单元格（例如F2）输入公式，计算“日用品”的总出库重量，并得到结果。</t>
         </is>
       </c>
     </row>
@@ -509,58 +509,88 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>出库重量</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>120</v>
       </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>80</v>
       </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
         <v>95</v>
       </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>金属</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>200</v>
+        <v>60</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>60</v>
+        <v>130</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -573,21 +603,21 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：物流到港天数与重量判断</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：物流跟单场景中，需要根据“到港日期”计算截至今天已经到港多少天，用于提醒后续清关。日期以文本展示，实际在Excel中应为日期格式。</t>
+          <t>要求：你需要根据发货日期和到港日期计算运输天数，并判断是否超时。样例数据中有两票货物，要求计算每票货物的到港天数，并标记是否超过10天。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：假设数据在A1:B4，请在C2单元格输入公式，计算YD001截至今天已经到港的天数。</t>
+          <t>任务：在D2输入公式计算YD001的到港天数，在E2输入公式判断是否超过10天：超过显示“超时”，否则显示“正常”。</t>
         </is>
       </c>
     </row>
@@ -599,6 +629,11 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>到港日期</t>
         </is>
       </c>
@@ -614,6 +649,11 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -623,379 +663,322 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按客户和状态统计订单数</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售台账中记录了不同销售员、不同区域的订单数量。现在要统计“华东”区域且销售员为“小李”的订单笔数，并找出所有订单数量中的最大值。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>要求：销售助理需要统计“客户为A公司且状态为已发货”的订单数量。如果没有匹配记录，希望显示“无”。</t>
+          <t>任务：在F2输入公式统计“华东”区域且销售员为“小李”的订单笔数；在F3输入公式求订单数量最大值。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在A1:C6，请在E2单元格输入公式，统计客户为“A公司”且状态为“已发货”的订单数；如果结果为0则显示“无”。</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>订单数量</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>小李</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>SO001</t>
+          <t>小王</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SO002</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>B公司</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>SO003</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>待发货</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>SO004</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>A公司</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>SO005</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>C公司</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流称重数据中，有些重量需要按两位小数显示，并且要避免出现错误值。样例数据中有一列原始重量，要求计算保留两位小数后的重量；如果公式出错，则显示“检查数据”。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>要求：仓储主管需要统计“上海仓”中“纸品”的出库总重量，并将结果保留1位小数。</t>
+          <t>任务：在C2输入公式，将B2的原始重量四舍五入保留两位小数；并用IFERROR包裹公式，使出错时显示“检查数据”。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在A1:C6，请在E2单元格输入公式，计算“上海仓”中“纸品”的出库总重量，并保留1位小数。</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>原始重量</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>出库重量(kg)</t>
-        </is>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>12.3456</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>纸品</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>120.456</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>8.9876</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>纸品</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>88.123</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>15.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>塑料</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>60.789</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>20.1234</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>纸品</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>95.333</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>纸品</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>70.5</v>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张运单明细表，需要根据运单号查找对应的到港日期。样例数据中包含运单号、到港日期和重量，要求分别用 XLOOKUP 和 INDEX+MATCH 两种方式查找“YD003”的到港日期。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2输入 XLOOKUP 公式查找“YD003”的到港日期；在F3输入 INDEX+MATCH 公式实现同样查找。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服需要根据商品编号，从商品资料表中查出售价。现有一张商品资料表和一个查询编号，请完成查表匹配。</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设数据在A1:C5，要查询的商品编号“P003”放在E2单元格。请在F2单元格输入公式，返回P003对应的售价。</t>
-        </is>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>售价</t>
-        </is>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>12.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>签字笔</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>3.8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1022,7 +1005,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：入库重量汇总</t>
+          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1016,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"纸品",B2:B6)</f>
+        <f>SUMIF(A2:A6,"日用品",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1047,7 +1030,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：物流到港天数与重量判断</t>
         </is>
       </c>
     </row>
@@ -1057,9 +1040,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2：=DATEDIF(B2,C2,"d")；E2：=IF(D2&gt;10,"超时","正常")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1072,7 +1056,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按客户和状态统计订单数</t>
+          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
         </is>
       </c>
     </row>
@@ -1082,9 +1066,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>IFERROR(1/(1/COUNTIFS(B2:B6,"A公司",C2:C6,"已发货")),"无")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F2：=COUNTIFS(B2:B6,"华东",A2:A6,"小李")；F3：=MAX(C2:C6)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1097,7 +1082,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
+          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1093,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"纸品"),1)</f>
+        <f>IFERROR(ROUND(B2,2),"检查数据")</f>
         <v/>
       </c>
     </row>
@@ -1122,7 +1107,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
+          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
         </is>
       </c>
     </row>
@@ -1132,9 +1117,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>XLOOKUP(E2,A2:A5,C2:C5)</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>F2：=XLOOKUP("YD003",A2:A5,B2:B5)；F3：=INDEX(B2:B5,MATCH("YD003",A2:A5,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1165,7 +1151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：入库重量汇总</t>
+          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
         </is>
       </c>
     </row>
@@ -1177,14 +1163,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF用于单条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件是“纸品”，求和区域是B2:B6。</t>
+          <t>SUMIF 用于按单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是品类区域，条件是“日用品”，B2:B6 是要汇总的出库重量，结果为 120+95=215。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：物流到港天数与重量判断</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1182,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY()返回今天日期；DATEDIF用于计算两个日期差。语法：DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。这里用B2作为开始日期，TODAY()作为结束日期。</t>
+          <t>DATEDIF 用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)，"d" 表示天数。IF 用于条件判断，语法为 IF(条件, 真值, 假值)。YD001为7天，显示“正常”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按客户和状态统计订单数</t>
+          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1201,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS用于多条件计数。语法：COUNTIFS(区域1, 条件1, 区域2, 条件2...)。这里统计B列为A公司且C列为已发货的行数。IFERROR用于处理错误或0结果，公式中“1/(1/数量)”可在数量为0时产生错误，再由IFERROR显示“无”。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里统计区域为“华东”且销售员为“小李”的行数，结果为2。MAX 用于求最大值，语法为 MAX(区域)，最大订单数量为15。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按品类和仓库汇总出库重量</t>
+          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1220,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和。语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里对C列求和，条件是A列为上海仓、B列为纸品。ROUND用于四舍五入，ROUND(数值,1)表示保留1位小数。</t>
+          <t>ROUND 用于四舍五入，语法为 ROUND(数值, 小数位数)，这里保留两位小数。IFERROR 用于捕获错误，语法为 IFERROR(原公式, 出错时显示的内容)。这样即使数据有问题，也能友好提示。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据商品编号查表匹配信息</t>
+          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1239,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP用于按值查找并返回对应结果。语法：XLOOKUP(查找值, 查找区域, 返回区域)。这里在A2:A5中查找E2的“P003”，返回C2:C5中对应售价。也可用INDEX+MATCH：=INDEX(C2:C5,MATCH(E2,A2:A5,0))。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，直接返回匹配结果。INDEX+MATCH 是经典组合：MATCH 找到查找值在区域中的位置，INDEX 根据位置返回对应值。两者结果都为“2024-05-20”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,509 +476,687 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
+          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIF</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家物流公司做客服，需要从一张发货台账中统计发往「上海」的总重量，并进一步统计发往「上海」且状态为「已签收」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在物流仓库做台账，需要快速汇总某个品类的出库总重量。样例数据记录了不同品类的出库重量，现在要统计“日用品”品类的总出库重量。</t>
+          <t>任务：在空白单元格 F2 输入公式，计算目的地为「上海」的总重量；在 F3 输入公式，计算目的地为「上海」且状态为「已签收」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（例如F2）输入公式，计算“日用品”的总出库重量，并得到结果。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>出库重量</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>120</v>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>80</v>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>95</v>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>B仓</t>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>60</v>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>B仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：物流到港天数与重量判断</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在电商仓库做订单跟进，需要统计台账中「已签收」的订单数量，并统计「上海」且「已签收」的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你需要根据发货日期和到港日期计算运输天数，并判断是否超时。样例数据中有两票货物，要求计算每票货物的到港天数，并标记是否超过10天。</t>
+          <t>任务：在空白单元格 F2 输入公式，统计状态为「已签收」的订单数；在 F3 输入公式，统计城市为「上海」且状态为「已签收」的订单数。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2输入公式计算YD001的到港天数，在E2输入公式判断是否超过10天：超过显示“超时”，否则显示“正常”。</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DD1001</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>DD1002</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>DD1003</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>259</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>DD1004</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>待发货</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DD1005</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>DD1006</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售台账中记录了不同销售员、不同区域的订单数量。现在要统计“华东”区域且销售员为“小李”的订单笔数，并找出所有订单数量中的最大值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2输入公式统计“华东”区域且销售员为“小李”的订单笔数；在F3输入公式求订单数量最大值。</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>订单数量</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：到港天数与重量评级</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>12</v>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责进口货物到港跟踪，需要根据「发运日期」和「到港日期」计算到港天数，并根据重量判断是否为「大货」。</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>小王</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>8</v>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 输入公式，计算 B001 批次的到港天数（按天数）；在 F2 输入公式，如果重量大于等于 1000 显示「大货」，否则显示「普通货」。</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>15</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>批次</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>10</v>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>9</v>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流称重数据中，有些重量需要按两位小数显示，并且要避免出现错误值。样例数据中有一列原始重量，要求计算保留两位小数后的重量；如果公式出错，则显示“检查数据”。</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2输入公式，将B2的原始重量四舍五入保留两位小数；并用IFERROR包裹公式，使出错时显示“检查数据”。</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>原始重量</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家贸易公司整理商品台账，商品编码有固定规则：前 2 位是类别码，后 3 位是流水号。现在需要提取类别码，并将不含税金额按 13% 税率算出含税金额，保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>12.3456</v>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 输入公式，提取 A2 商品编码的前 2 位类别码；在 E2 输入公式，计算 C2 不含税金额的含税金额，税率 13%，保留 2 位小数。</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>8.9876</v>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>不含税金额</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>15.5</v>
+          <t>AB001</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>螺丝刀</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>19.99</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>20.1234</v>
+          <t>CD102</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>AB205</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>卷尺</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张运单明细表，需要根据运单号查找对应的到港日期。样例数据中包含运单号、到港日期和重量，要求分别用 XLOOKUP 和 INDEX+MATCH 两种方式查找“YD003”的到港日期。</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2输入 XLOOKUP 公式查找“YD003”的到港日期；在F3输入 INDEX+MATCH 公式实现同样查找。</t>
+          <t>要求：你在物流报价组工作，需要根据目的地从运费表中查找首重价格。若查不到目的地，显示「未报价」。同时练习用 INDEX+MATCH 做更灵活的查表。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格 F2 输入目的地「杭州」，在 G2 用 XLOOKUP 查找「杭州」的首重价格，查不到显示「未报价」；在 G3 用 VLOOKUP 查找「上海」的首重价格；在 G4 用 INDEX+MATCH 查找「广州」的续重价格。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>120</v>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>首重价格(元)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>续重价格(元)</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>95</v>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>80</v>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>150</v>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1005,7 +1183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
+          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
         </is>
       </c>
     </row>
@@ -1015,9 +1193,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"日用品",B2:B6)</f>
-        <v/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>F2:=SUMIF(B2:B6,"上海",C2:C6)；F3:=SUMIFS(C2:C6,B2:B6,"上海",D2:D6,"已签收")</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1030,7 +1209,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：物流到港天数与重量判断</t>
+          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1221,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D2：=DATEDIF(B2,C2,"d")；E2：=IF(D2&gt;10,"超时","正常")</t>
+          <t>F2:=COUNTIF(C2:C7,"已签收")；F3:=COUNTIFS(B2:B7,"上海",C2:C7,"已签收")</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1235,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
+          <t>第 3 题：第3题：到港天数与重量评级</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1247,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>F2：=COUNTIFS(B2:B6,"华东",A2:A6,"小李")；F3：=MAX(C2:C6)</t>
+          <t>E2:=DATEDIF(B2,C2,"d")；F2:=IF(D2&gt;=1000,"大货","普通货")</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1261,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
+          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
         </is>
       </c>
     </row>
@@ -1092,9 +1271,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(ROUND(B2,2),"检查数据")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D2:=LEFT(A2,2)；E2:=ROUND(C2*1.13,2)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1107,7 +1287,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
+          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1299,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>F2：=XLOOKUP("YD003",A2:A5,B2:B5)；F3：=INDEX(B2:B5,MATCH("YD003",A2:A5,0))</t>
+          <t>G2:=IFERROR(XLOOKUP(F2,A2:A5,B2:B5,"未报价"),"未报价")；G3:=VLOOKUP("上海",A2:C5,2,FALSE)；G4:=INDEX(C2:C5,MATCH("广州",A2:A5,0))</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1331,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库台账按品类统计出库重量</t>
+          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
         </is>
       </c>
     </row>
@@ -1163,14 +1343,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是品类区域，条件是“日用品”，B2:B6 是要汇总的出库重量，结果为 120+95=215。</t>
+          <t>SUMIF 用于单条件求和，语法是 =SUMIF(条件区域,条件,求和区域)。SUMIFS 用于多条件求和，语法是 =SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。本题先按「目的地」筛选上海，再叠加「状态」筛选已签收。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：物流到港天数与重量判断</t>
+          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
         </is>
       </c>
     </row>
@@ -1182,14 +1362,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)，"d" 表示天数。IF 用于条件判断，语法为 IF(条件, 真值, 假值)。YD001为7天，显示“正常”。</t>
+          <t>COUNTIF 用于单条件计数，语法是 =COUNTIF(条件区域,条件)。COUNTIFS 用于多条件计数，语法是 =COUNTIFS(条件区域1,条件1,条件区域2,条件2)。注意条件中的文字要加英文双引号。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单数量多条件统计与最大值</t>
+          <t>第 3 题：第3题：到港天数与重量评级</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1381,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里统计区域为“华东”且销售员为“小李”的行数，结果为2。MAX 用于求最大值，语法为 MAX(区域)，最大订单数量为15。</t>
+          <t>DATEDIF 语法是 =DATEDIF(开始日期,结束日期,单位)，单位 "d" 表示天数。IF 语法是 =IF(条件,条件成立时的结果,条件不成立时的结果)。本题用 DATEDIF 算到港天数，用 IF 做重量分级。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：产品重量四舍五入与错误处理</t>
+          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1400,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROUND 用于四舍五入，语法为 ROUND(数值, 小数位数)，这里保留两位小数。IFERROR 用于捕获错误，语法为 IFERROR(原公式, 出错时显示的内容)。这样即使数据有问题，也能友好提示。</t>
+          <t>LEFT 用于从文本左侧提取指定个数，语法是 =LEFT(文本,个数)。MID 可从中间提取，语法是 =MID(文本,开始位置,个数)。RIGHT 从右侧提取。ROUND 用于四舍五入，语法是 =ROUND(数值,小数位数)，本题保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据运单号查找到港日期与重量</t>
+          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1419,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找区域, 返回区域)，直接返回匹配结果。INDEX+MATCH 是经典组合：MATCH 找到查找值在区域中的位置，INDEX 根据位置返回对应值。两者结果都为“2024-05-20”。</t>
+          <t>XLOOKUP 语法是 =XLOOKUP(查找值,查找区域,返回区域,[未找到时返回内容])，可直接设置查不到时的结果。VLOOKUP 语法是 =VLOOKUP(查找值,表格区域,返回第几列,FALSE)，FALSE 表示精确匹配。INDEX+MATCH 先用 MATCH 找位置，再用 INDEX 按位置取值，语法是 =INDEX(返回区域,MATCH(查找值,查找区域,0))。IFERROR 可把错误值替换为指定内容。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,570 +476,362 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家物流公司做客服，需要从一张发货台账中统计发往「上海」的总重量，并进一步统计发往「上海」且状态为「已签收」的总重量。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 F2 输入公式，计算目的地为「上海」的总重量；在 F3 输入公式，计算目的地为「上海」且状态为「已签收」的总重量。</t>
+          <t>要求：你在一家物流公司做台账，需要统计“华东仓”的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在空白单元格输入公式，计算“华东仓”的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>入库重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>华南仓</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
+          <t>华北仓</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在电商仓库做订单跟进，需要统计台账中「已签收」的订单数量，并统计「上海」且「已签收」的订单数量。</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：按日期计算客户账期天数</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 F2 输入公式，统计状态为「已签收」的订单数；在 F3 输入公式，统计城市为「上海」且状态为「已签收」的订单数。</t>
+          <t>要求：你在做应收账款台账，需要根据发货日期计算截至今天的账期天数。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算甲公司截至今天的账期天数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DD1001</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>199</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>DD1002</t>
+          <t>甲公司</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>89</t>
+          <t>2024-01-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DD1003</t>
+          <t>乙公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>259</t>
+          <t>2024-02-15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DD1004</t>
+          <t>丙公司</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>待发货</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>2024-03-01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DD1005</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>DD1006</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在销售部门整理订单，需要统计金额大于等于1000的订单数量，并把其中一笔订单金额保留到整数。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：到港天数与重量评级</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 单元格统计金额大于等于1000的订单数量；在 D3 单元格把 A002 的金额四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责进口货物到港跟踪，需要根据「发运日期」和「到港日期」计算到港天数，并根据重量判断是否为「大货」。</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 输入公式，计算 B001 批次的到港天数（按天数）；在 F2 输入公式，如果重量大于等于 1000 显示「大货」，否则显示「普通货」。</t>
-        </is>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>999.6</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>批次</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1200.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1500.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>800.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1000.1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在电商仓库做商品价格查询，需要根据商品编号查找单价；如果查不到，就显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家贸易公司整理商品台账，商品编码有固定规则：前 2 位是类别码，后 3 位是流水号。现在需要提取类别码，并将不含税金额按 13% 税率算出含税金额，保留 2 位小数。</t>
+          <t>任务：请在 F2 输入商品编号“P1003”，在 G2 输入公式查找该商品单价；如果编号不存在则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 输入公式，提取 A2 商品编码的前 2 位类别码；在 E2 输入公式，计算 C2 不含税金额的含税金额，税率 13%，保留 2 位小数。</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>不含税金额</t>
-        </is>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>无线鼠标</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>AB001</t>
+          <t>P1002</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>螺丝刀</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+          <t>机械键盘</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>CD102</t>
+          <t>P1003</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>扳手</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>899</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>AB205</t>
+          <t>P1004</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>卷尺</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
+          <t>USB线</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -1052,106 +844,106 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>要求：你在物流报价组工作，需要根据目的地从运费表中查找首重价格。若查不到目的地，显示「未报价」。同时练习用 INDEX+MATCH 做更灵活的查表。</t>
+          <t>要求：你在人力资源系统里，需要根据员工姓名查找所属部门，避免因列顺序变化导致 VLOOKUP 不方便使用。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 F2 输入目的地「杭州」，在 G2 用 XLOOKUP 查找「杭州」的首重价格，查不到显示「未报价」；在 G3 用 VLOOKUP 查找「上海」的首重价格；在 G4 用 INDEX+MATCH 查找「广州」的续重价格。</t>
+          <t>任务：请在 F2 输入员工姓名“王五”，在 G2 输入公式查找其所属部门。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>目的地</t>
+          <t>员工姓名</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>首重价格(元)</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>续重价格(元)</t>
+          <t>工号</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>E001</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>物流部</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>E002</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>E003</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>人事部</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>E004</t>
         </is>
       </c>
     </row>
@@ -1183,7 +975,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
         </is>
       </c>
     </row>
@@ -1193,10 +985,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>F2:=SUMIF(B2:B6,"上海",C2:C6)；F3:=SUMIFS(C2:C6,B2:B6,"上海",D2:D6,"已签收")</t>
-        </is>
+      <c r="B2" s="2">
+        <f>SUMIF(A2:A6,"华东仓",B2:B6)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1209,7 +1000,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
+          <t>第 2 题：第2题：按日期计算客户账期天数</t>
         </is>
       </c>
     </row>
@@ -1219,10 +1010,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>F2:=COUNTIF(C2:C7,"已签收")；F3:=COUNTIFS(B2:B7,"上海",C2:C7,"已签收")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>DATEDIF(B2,TODAY(),"D")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1235,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与重量评级</t>
+          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
         </is>
       </c>
     </row>
@@ -1245,10 +1035,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>E2:=DATEDIF(B2,C2,"d")；F2:=IF(D2&gt;=1000,"大货","普通货")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>COUNTIF(B2:B6,"&gt;=1000")；=ROUND(B3,0)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1261,7 +1050,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
+          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
         </is>
       </c>
     </row>
@@ -1271,10 +1060,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>D2:=LEFT(A2,2)；E2:=ROUND(C2*1.13,2)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1287,7 +1075,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
         </is>
       </c>
     </row>
@@ -1297,10 +1085,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2:=IFERROR(XLOOKUP(F2,A2:A5,B2:B5,"未报价"),"未报价")；G3:=VLOOKUP("上海",A2:C5,2,FALSE)；G4:=INDEX(C2:C5,MATCH("广州",A2:A5,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>INDEX(B2:B5,MATCH(F2,A2:A5,0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1331,7 +1118,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流台账按目的地汇总重量</t>
+          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
         </is>
       </c>
     </row>
@@ -1343,14 +1130,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法是 =SUMIF(条件区域,条件,求和区域)。SUMIFS 用于多条件求和，语法是 =SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)。本题先按「目的地」筛选上海，再叠加「状态」筛选已签收。</t>
+          <t>SUMIF 用于按一个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“华东仓”，求和区域是 B2:B6。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单台账统计不同物流状态的订单数</t>
+          <t>第 2 题：第2题：按日期计算客户账期天数</t>
         </is>
       </c>
     </row>
@@ -1362,14 +1149,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于单条件计数，语法是 =COUNTIF(条件区域,条件)。COUNTIFS 用于多条件计数，语法是 =COUNTIFS(条件区域1,条件1,条件区域2,条件2)。注意条件中的文字要加英文双引号。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "D") 用于计算两个日期相差的天数，"D" 表示按天计算。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：到港天数与重量评级</t>
+          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
         </is>
       </c>
     </row>
@@ -1381,14 +1168,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 语法是 =DATEDIF(开始日期,结束日期,单位)，单位 "d" 表示天数。IF 语法是 =IF(条件,条件成立时的结果,条件不成立时的结果)。本题用 DATEDIF 算到港天数，用 IF 做重量分级。</t>
+          <t>COUNTIF(区域, 条件) 用于按条件计数，"&gt;=1000" 是条件。ROUND(数字, 小数位数) 用于四舍五入，0 表示保留整数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：取商品编号并计算含税金额</t>
+          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
         </is>
       </c>
     </row>
@@ -1400,14 +1187,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LEFT 用于从文本左侧提取指定个数，语法是 =LEFT(文本,个数)。MID 可从中间提取，语法是 =MID(文本,开始位置,个数)。RIGHT 从右侧提取。ROUND 用于四舍五入，语法是 =ROUND(数值,小数位数)，本题保留 2 位小数。</t>
+          <t>VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 用于精确查找。IFERROR(公式, 错误时显示内容) 可以避免 #N/A 错误，查不到时显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP/VLOOKUP 与 INDEX+MATCH 查运费单价</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1206,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法是 =XLOOKUP(查找值,查找区域,返回区域,[未找到时返回内容])，可直接设置查不到时的结果。VLOOKUP 语法是 =VLOOKUP(查找值,表格区域,返回第几列,FALSE)，FALSE 表示精确匹配。INDEX+MATCH 先用 MATCH 找位置，再用 INDEX 按位置取值，语法是 =INDEX(返回区域,MATCH(查找值,查找区域,0))。IFERROR 可把错误值替换为指定内容。</t>
+          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置。INDEX(返回区域, 位置) 根据位置返回对应内容。两者组合可实现灵活查找。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,28 +476,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
+          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做台账，需要统计“华东仓”的入库总重量。</t>
+          <t>要求：你是仓库管理员，A 列是仓库名，B 列是品类，C 列是入库重量（kg）。现在需要统计「上海仓」中「电子」品类的入库总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在空白单元格输入公式，计算“华东仓”的入库总重量。</t>
+          <t>任务：在 E2 单元格输入公式，计算「上海仓」中「电子」品类的入库总重量。</t>
         </is>
       </c>
     </row>
@@ -509,58 +509,88 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>入库重量</t>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华南仓</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>150</v>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华北仓</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>90</v>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -573,265 +603,267 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：按日期计算客户账期天数</t>
+          <t>第 2 题：统计订单数量（按条件计数）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在做应收账款台账，需要根据发货日期计算截至今天的账期天数。</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式，计算甲公司截至今天的账期天数。</t>
+          <t>要求：这是一张订单台账，A 列是订单编号，B 列是客户等级，C 列是订单金额。需要统计「VIP」客户中金额大于 500 的订单有多少笔。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，统计客户等级为 VIP 且金额大于 500 的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>甲公司</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>客户等级</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>乙公司</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
-        </is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>丙公司</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
-        </is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在销售部门整理订单，需要统计金额大于等于1000的订单数量，并把其中一笔订单金额保留到整数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D2 单元格统计金额大于等于1000的订单数量；在 D3 单元格把 A002 的金额四舍五入到整数。</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：到港天数与日期处理</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>999.6</v>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流台账中记录了每个集装箱的到港日期（A 列）。今天是动态日期，需要计算每个集装箱从到港到今天已经过了多少天。</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1200.4</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算 CTN001 从到港日期到今天经过的天数（结果随今天自动变化）。</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>1500.8</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>集装箱号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>800.2</v>
+          <t>CTN001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1000.1</v>
+          <t>CTN002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CTN003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在电商仓库做商品价格查询，需要根据商品编号查找单价；如果查不到，就显示“未找到”。</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：提取编码并四舍五入计算</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 F2 输入商品编号“P1003”，在 G2 输入公式查找该商品单价；如果编号不存在则显示“未找到”。</t>
+          <t>要求：物料编码由「前缀+数字」组成，需要取出数字部分，并按每单位 3.7 元的单价计算总价，结果保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式：从 B2 对应的物料编码 A2 中取出数字部分（从第 3 个字符开始，取 4 位），乘以数量 B2 再乘以单价 3.7，最后四舍五入保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>无线鼠标</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>89</v>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>物料编码</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>P1002</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>机械键盘</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>299</v>
+          <t>AB1234</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>P1003</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>899</v>
+          <t>CD567</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>P1004</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>USB线</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>19</v>
+          <t>EF89</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -844,111 +876,106 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
+          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>要求：你在人力资源系统里，需要根据员工姓名查找所属部门，避免因列顺序变化导致 VLOOKUP 不方便使用。</t>
+          <t>要求：左边是订单表（A 列商品名、B 列数量），右边是商品价目表（D 列商品名、E 列单价）。需要根据商品名查出单价，计算订单金额；若商品在价目表中查不到，则显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 F2 输入员工姓名“王五”，在 G2 输入公式查找其所属部门。</t>
+          <t>任务：在 C2 单元格输入公式，用商品名 A2 在 D2:D4 中查找对应单价，乘以数量 B2 得到金额；查不到时显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>员工姓名</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>工号</t>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>物流部</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>E004</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -975,7 +1002,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
+          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
         </is>
       </c>
     </row>
@@ -986,7 +1013,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"华东仓",B2:B6)</f>
+        <f>SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"电子")</f>
         <v/>
       </c>
     </row>
@@ -1000,7 +1027,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：按日期计算客户账期天数</t>
+          <t>第 2 题：统计订单数量（按条件计数）</t>
         </is>
       </c>
     </row>
@@ -1011,35 +1038,35 @@
         </is>
       </c>
       <c r="B6" s="2">
+        <f>COUNTIFS(B2:B6,"VIP",C2:C6,"&gt;500")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>（可直接复制公式到题目文件对应单元格验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：到港天数与日期处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>答案：</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
         <f>DATEDIF(B2,TODAY(),"D")</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>（可直接复制公式到题目文件对应单元格验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>答案：</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>COUNTIF(B2:B6,"&gt;=1000")；=ROUND(B3,0)</f>
-        <v/>
-      </c>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -1050,7 +1077,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
+          <t>第 4 题：提取编码并四舍五入计算</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1088,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(F2,A2:C5,3,FALSE),"未找到")</f>
+        <f>ROUND(MID(A2,3,4)*B2*3.7,2)</f>
         <v/>
       </c>
     </row>
@@ -1075,7 +1102,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
+          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1113,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(B2:B5,MATCH(F2,A2:A5,0))</f>
+        <f>IFERROR(XLOOKUP(A2,D2:D4,E2:E4)*B2,"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1118,7 +1145,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定仓库的入库重量</t>
+          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
         </is>
       </c>
     </row>
@@ -1130,14 +1157,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按一个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“华东仓”，求和区域是 B2:B6。</t>
+          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是 C2:C6（重量），第一个条件是仓库列 A2:A6 等于「上海仓」，第二个条件是品类列 B2:B6 等于「电子」。两个条件同时满足的行求和：120+60=180。注意文本条件要加英文双引号。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：按日期计算客户账期天数</t>
+          <t>第 2 题：统计订单数量（按条件计数）</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1176,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "D") 用于计算两个日期相差的天数，"D" 表示按天计算。</t>
+          <t>COUNTIFS 语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)，用于统计同时满足多个条件的单元格个数。这里是 B2:B6 等于「VIP」，C2:C6 大于 500。比较运算符要放在双引号内写成 "&gt;500"。满足条件的只有 A001(800) 和 A004(1200)，共 2 笔。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：统计高金额订单数量并四舍五入金额</t>
+          <t>第 3 题：到港天数与日期处理</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1195,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(区域, 条件) 用于按条件计数，"&gt;=1000" 是条件。ROUND(数字, 小数位数) 用于四舍五入，0 表示保留整数。</t>
+          <t>TODAY() 返回今天的日期且自动更新；DATEDIF(开始日期, 结束日期, "D") 返回两者相差的天数，"D" 表示按天计算。这里 B2 是开始日期，TODAY() 是结束日期。注意 DATEDIF 要求开始日期不能晚于结束日期。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：查找商品单价并处理找不到的情况</t>
+          <t>第 4 题：提取编码并四舍五入计算</t>
         </is>
       </c>
     </row>
@@ -1187,14 +1214,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 用于精确查找。IFERROR(公式, 错误时显示内容) 可以避免 #N/A 错误，查不到时显示“未找到”。</t>
+          <t>MID(文本, 起始位置, 字符个数) 从文本指定位置截取字符，MID(A2,3,4) 表示从第 3 个字符起取 4 位。ROUND(数值, 小数位数) 对结果四舍五入，ROUND(...,2) 保留 2 位小数。以 AB1234 为例：MID 得到 "1234"，乘 10 再乘 3.7 得 45658，保留 2 位仍为 45658。注意 MID 取出的是文本，参与乘法运算时 Excel 会自动转成数字。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查找员工部门</t>
+          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1233,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的位置。INDEX(返回区域, 位置) 根据位置返回对应内容。两者组合可实现灵活查找。</t>
+          <t>XLOOKUP(查找值, 查找数组, 返回数组) 在 D2:D4 中查找 A2 的商品名，找到后返回 E2:E4 对应位置的单价。IFERROR(公式, 替代值) 在公式报错时返回「未找到」，避免出现 #N/A。以苹果为例：单价 3.5×数量 5=17.5。若 A2 填入价目表中没有的商品，XLOOKUP 报错，IFERROR 显示「未找到」。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,57 +476,57 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
+          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，A 列是仓库名，B 列是品类，C 列是入库重量（kg）。现在需要统计「上海仓」中「电子」品类的入库总重量。</t>
+          <t>要求：某物流公司有一份到港货物台账，记录了每票货物的目的城市和重量（kg）。现在需要统计发往「上海」的货物总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 单元格输入公式，计算「上海仓」中「电子」品类的入库总重量。</t>
+          <t>任务：在表格右侧空白单元格（如 E2）输入公式，计算目的城市为「上海」的重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>品类</t>
+          <t>目的城市</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -536,12 +536,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -551,46 +551,46 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
+          <t>YD005</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -603,121 +603,129 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：统计订单数量（按条件计数）</t>
+          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售台账记录了每笔订单的销售员和金额。现在需要统计销售员「小李」且金额大于等于 200 元的订单笔数，并汇总这些订单的金额。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：这是一张订单台账，A 列是订单编号，B 列是客户等级，C 列是订单金额。需要统计「VIP」客户中金额大于 500 的订单有多少笔。</t>
+          <t>任务：在空白单元格输入两个公式：一个统计满足「销售员=小李且金额&gt;=200」的订单笔数，一个汇总这些订单的金额。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，统计客户等级为 VIP 且金额大于 500 的订单笔数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>客户等级</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>小李</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>小王</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>小王</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
@@ -730,69 +738,69 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：到港天数与日期处理</t>
+          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：物流台账中记录了每个集装箱的到港日期（A 列）。今天是动态日期，需要计算每个集装箱从到港到今天已经过了多少天。</t>
+          <t>要求：人事表记录了每位员工的入职日期。需要根据今天的日期，计算每位员工截至今天已经入职的整年数。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格输入公式，计算 CTN001 从到港日期到今天经过的天数（结果随今天自动变化）。</t>
+          <t>任务：在 C2 单元格输入公式，计算张三入职至今的整年数（结果随当天日期自动变化），然后向下填充。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>集装箱号</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>到港日期</t>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>CTN001</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2019/3/15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>CTN002</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2021/7/1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>CTN003</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2023/1/10</t>
         </is>
       </c>
     </row>
@@ -806,50 +814,50 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：提取编码并四舍五入计算</t>
+          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：物料编码由「前缀+数字」组成，需要取出数字部分，并按每单位 3.7 元的单价计算总价，结果保留 2 位小数。</t>
+          <t>要求：有一份运单表记录了部分运单的到港天数。现在要根据运单号在运单表中查询到港天数；如果该运单号在表中不存在（查不到），则显示「无记录」而不是错误值。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式：从 B2 对应的物料编码 A2 中取出数字部分（从第 3 个字符开始，取 4 位），乘以数量 B2 再乘以单价 3.7，最后四舍五入保留 2 位小数。</t>
+          <t>任务：假设待查运单号在 E2（例如 E2 输入「YD006」），在 F2 输入公式，查出其到港天数，查不到则返回「无记录」。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>物料编码</t>
+          <t>运单号</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>到港天数</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>AB1234</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>CD567</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
@@ -859,123 +867,105 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>EF89</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：左边是订单表（A 列商品名、B 列数量），右边是商品价目表（D 列商品名、E 列单价）。需要根据商品名查出单价，计算订单金额；若商品在价目表中查不到，则显示「未找到」。</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格输入公式，用商品名 A2 在 D2:D4 中查找对应单价，乘以数量 B2 得到金额；查不到时显示「未找到」。</t>
+          <t>要求：有一份货品价目表（货品名称、单价）。现在要根据订单中的货品名称，用 INDEX+MATCH 组合查出单价，再乘以数量并四舍五入保留 2 位小数，得到金额。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设订单货品名称在 E2（如「显示器」），数量在 F2（如 3），在 G2 输入公式：查出该货品单价，乘以数量后四舍五入保留 2 位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>货品名称</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>2</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>鼠标</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>4.2</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>899.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>129.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1002,7 +992,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
+          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1003,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"电子")</f>
+        <f>SUMIF(B2:B6,"上海",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1017,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：统计订单数量（按条件计数）</t>
+          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1037,9 +1027,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIFS(B2:B6,"VIP",C2:C6,"&gt;500")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>笔数：=COUNTIFS(B2:B7,"小李",C2:C7,"&gt;=200")；金额：=SUMIFS(C2:C7,B2:B7,"小李",C2:C7,"&gt;=200")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1052,7 +1043,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：到港天数与日期处理</t>
+          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1054,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"D")</f>
+        <f>DATEDIF(B2,TODAY(),"Y")</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1068,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：提取编码并四舍五入计算</t>
+          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1079,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(MID(A2,3,4)*B2*3.7,2)</f>
+        <f>IFERROR(VLOOKUP(E2,A2:B5,2,0),"无记录")</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1093,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
+          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1104,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP(A2,D2:D4,E2:E4)*B2,"未找到")</f>
+        <f>ROUND(INDEX(B2:B5,MATCH(E2,A2:A5,0))*F2,2)</f>
         <v/>
       </c>
     </row>
@@ -1145,7 +1136,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：入库重量汇总（按仓库和品类）</t>
+          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1157,14 +1148,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是 C2:C6（重量），第一个条件是仓库列 A2:A6 等于「上海仓」，第二个条件是品类列 B2:B6 等于「电子」。两个条件同时满足的行求和：120+60=180。注意文本条件要加英文双引号。</t>
+          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6（目的城市列），条件是 "上海"，求和区域是 C2:C6（重量列）。只要目的城市等于上海，就把对应重量相加，结果为 120+95+60=275。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：统计订单数量（按条件计数）</t>
+          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1176,14 +1167,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)，用于统计同时满足多个条件的单元格个数。这里是 B2:B6 等于「VIP」，C2:C6 大于 500。比较运算符要放在双引号内写成 "&gt;500"。满足条件的只有 A001(800) 和 A004(1200)，共 2 笔。</t>
+          <t>COUNTIFS 用于多条件计数，语法 COUNTIFS(区域1,条件1,区域2,条件2...)，本题小李且金额&gt;=200 的订单是 A01、A04、A06，共 3 笔。SUMIFS 语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)，求和区域放最前，结果为 300+500+220=1020。注意比较条件要写成 "&gt;=200" 字符串。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：到港天数与日期处理</t>
+          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1195,14 +1186,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期且自动更新；DATEDIF(开始日期, 结束日期, "D") 返回两者相差的天数，"D" 表示按天计算。这里 B2 是开始日期，TODAY() 是结束日期。注意 DATEDIF 要求开始日期不能晚于结束日期。</t>
+          <t>TODAY() 返回当前日期，无需参数，每天打开表格会自动更新。DATEDIF 语法为 DATEDIF(开始日期,结束日期,单位)，单位 "Y" 表示相差的整年数。这里开始日期是 B2 的入职日期，结束日期是 TODAY()，即可得到截至今天的入职年数。DATEDIF 是隐藏函数，需手工输入。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：提取编码并四舍五入计算</t>
+          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1214,14 +1205,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID(文本, 起始位置, 字符个数) 从文本指定位置截取字符，MID(A2,3,4) 表示从第 3 个字符起取 4 位。ROUND(数值, 小数位数) 对结果四舍五入，ROUND(...,2) 保留 2 位小数。以 AB1234 为例：MID 得到 "1234"，乘 10 再乘 3.7 得 45658，保留 2 位仍为 45658。注意 MID 取出的是文本，参与乘法运算时 Excel 会自动转成数字。</t>
+          <t>VLOOKUP 语法为 VLOOKUP(查找值,查找区域,返回第几列,匹配方式)，第4参数用 0 表示精确匹配。这里在 A2:B5 的第一列找 E2 的运单号，找到后返回第 2 列（到港天数）。当运单号不存在时 VLOOKUP 会返回 #N/A 错误，外层用 IFERROR(值, 出错时显示内容) 把它替换成 "无记录"，让报表更整洁。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：查表匹配单价并算金额（含错误处理）</t>
+          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找数组, 返回数组) 在 D2:D4 中查找 A2 的商品名，找到后返回 E2:E4 对应位置的单价。IFERROR(公式, 替代值) 在公式报错时返回「未找到」，避免出现 #N/A。以苹果为例：单价 3.5×数量 5=17.5。若 A2 填入价目表中没有的商品，XLOOKUP 报错，IFERROR 显示「未找到」。</t>
+          <t>MATCH(查找值,查找区域,0) 返回查找值在区域中的位置，MATCH("显示器",A2:A5,0) 得 3。INDEX(B2:B5,位置) 按位置取出单价区的值，得 899.9。INDEX+MATCH 不受列顺序限制，比 VLOOKUP 更灵活。最后用 ROUND(数值,2) 将 899.9*3 的结果四舍五入保留 2 位小数，得 2699.7。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,28 +476,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：运费台账区间统计</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：某物流公司有一份到港货物台账，记录了每票货物的目的城市和重量（kg）。现在需要统计发往「上海」的货物总重量。</t>
+          <t>要求：物流公司有一份运费台账，记录了每笔运单的线路、货物类型和运费金额。现在需要统计「华东线」且货物类型为「重货」的运费合计，放到 F2 单元格。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在表格右侧空白单元格（如 E2）输入公式，计算目的城市为「上海」的重量合计。</t>
+          <t>任务：在 F2 单元格输入公式，统计线路为「华东线」且货物类型为「重货」的运费总和。</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>目的城市</t>
+          <t>线路</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量kg</t>
+          <t>货物类型</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
@@ -526,11 +531,16 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>重货</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -541,11 +551,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>80</v>
+          <t>华南线</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>轻货</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -556,11 +571,16 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>95</v>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>轻货</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +591,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>150</v>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>重货</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -586,222 +611,260 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>60</v>
+          <t>华南线</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>重货</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>YD006</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>华东线</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>重货</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售台账记录了每笔订单的销售员和金额。现在需要统计销售员「小李」且金额大于等于 200 元的订单笔数，并汇总这些订单的金额。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格输入两个公式：一个统计满足「销售员=小李且金额&gt;=200」的订单笔数，一个汇总这些订单的金额。</t>
+          <t>要求：货代公司需要跟踪每批货物的在途天数。表格记录了装船日期，要求计算每批货物从装船到今天已经过了多少天，结果放在 D 列。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式并向下填充到 D4，计算每批货物从装船日期到今天（TODAY）的天数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>300</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>装船日期</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>已装船天数</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小王</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>150</v>
-      </c>
+          <t>钢材</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>120</v>
-      </c>
+          <t>大米</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>500</v>
-      </c>
+          <t>机械零件</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>小王</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>220</v>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：重量汇总与计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库有一份到货明细，记录了每件货物的品类和重量。需要先统计「生鲜」品类的总重量，再统计「生鲜」品类的件数。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 用公式统计品类为「生鲜」的重量总和；在 E3 用公式统计品类为「生鲜」的件数。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：人事表记录了每位员工的入职日期。需要根据今天的日期，计算每位员工截至今天已经入职的整年数。</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算张三入职至今的整年数（结果随当天日期自动变化），然后向下填充。</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>干货</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2019/3/15</t>
-        </is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2021/7/1</t>
-        </is>
+          <t>生鲜</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>15.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2023/1/10</t>
-        </is>
+          <t>干货</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -814,75 +877,84 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
+          <t>第 4 题：第4题：成绩等级判定与除错</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>要求：有一份运单表记录了部分运单的到港天数。现在要根据运单号在运单表中查询到港天数；如果该运单号在表中不存在（查不到），则显示「无记录」而不是错误值。</t>
+          <t>要求：培训考核表记录了每位学员的得分，需要根据得分判定等级：60 分及以上为「合格」，否则为「不合格」。同时用 IFERROR 处理可能出现的错误值。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>任务：假设待查运单号在 E2（例如 E2 输入「YD006」），在 F2 输入公式，查出其到港天数，查不到则返回「无记录」。</t>
+          <t>任务：在 C2 单元格输入公式并向下填充，用 IF 判断得分是否≥60，返回「合格」或「不合格」；再用 IFERROR 包裹，使出错时显示「待录入」。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>到港天数</t>
+          <t>得分</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>12</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>8</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>6</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -894,31 +966,36 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
+          <t>第 5 题：第5题：物流报价查表匹配</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>要求：有一份货品价目表（货品名称、单价）。现在要根据订单中的货品名称，用 INDEX+MATCH 组合查出单价，再乘以数量并四舍五入保留 2 位小数，得到金额。</t>
+          <t>要求：物流公司有一张按目的地和重量段制定的运费单价表（元/kg）。现需要根据目的地和重量段查出单价，并计算运费（重量×单价，保留两位小数）。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>任务：假设订单货品名称在 E2（如「显示器」），数量在 F2（如 3），在 G2 输入公式：查出该货品单价，乘以数量后四舍五入保留 2 位小数。</t>
+          <t>任务：在 E2 单元格用 XLOOKUP 或多个函数组合，根据 D2 中的「目的地」和「重量段」两个条件查出单价，再用 ROUND 计算运费（重量 20kg，保留两位小数）。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>货品名称</t>
+          <t>目的地</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>重量段</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
@@ -927,45 +1004,95 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>89.5</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>0-10kg</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>45.8</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>10-50kg</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>899.9</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>0-10kg</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>129.3</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>10-50kg</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>0-10kg</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>10-50kg</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -992,7 +1119,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：运费台账区间统计</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1130,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"上海",C2:C6)</f>
+        <f>SUMIFS(D2:D7,B2:B7,"华东线",C2:C7,"重货")</f>
         <v/>
       </c>
     </row>
@@ -1017,7 +1144,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1027,10 +1154,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>笔数：=COUNTIFS(B2:B7,"小李",C2:C7,"&gt;=200")；金额：=SUMIFS(C2:C7,B2:B7,"小李",C2:C7,"&gt;=200")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>DATEDIF(C2,TODAY(),"D")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1169,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
+          <t>第 3 题：第3题：重量汇总与计数</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1180,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")</f>
+        <f>SUMIF(B2:B6,"生鲜",C2:C6)；件数公式：=COUNTIF(B2:B6,"生鲜")</f>
         <v/>
       </c>
     </row>
@@ -1068,7 +1194,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
+          <t>第 4 题：第4题：成绩等级判定与除错</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1205,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(E2,A2:B5,2,0),"无记录")</f>
+        <f>IFERROR(IF(B2&gt;=60,"合格","不合格"),"待录入")</f>
         <v/>
       </c>
     </row>
@@ -1093,7 +1219,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
+          <t>第 5 题：第5题：物流报价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1230,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(INDEX(B2:B5,MATCH(E2,A2:A5,0))*F2,2)</f>
+        <f>ROUND(20*XLOOKUP(1,(A2:A7="上海")*(B2:B7="10-50kg"),C2:C7),2)</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1262,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：物流重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：运费台账区间统计</t>
         </is>
       </c>
     </row>
@@ -1148,14 +1274,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6（目的城市列），条件是 "上海"，求和区域是 C2:C6（重量列）。只要目的城市等于上海，就把对应重量相加，结果为 120+95+60=275。</t>
+          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。先指定求和区域 D2:D7（运费），再给出两个条件：线路列 B2:B7 等于「华东线」，货物类型列 C2:C7 等于「重货」。只有同时满足两个条件的行才被求和，结果为 320+450+210=980。文本条件要加英文双引号。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单笔数与金额双条件统计（COUNTIFS + SUMIFS）</t>
+          <t>第 2 题：第2题：到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1293,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法 COUNTIFS(区域1,条件1,区域2,条件2...)，本题小李且金额&gt;=200 的订单是 A01、A04、A06，共 3 笔。SUMIFS 语法为 SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2...)，求和区域放最前，结果为 300+500+220=1020。注意比较条件要写成 "&gt;=200" 字符串。</t>
+          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "D") 返回两个日期之间的整天数，第三个参数 "D" 表示按天计算。用 C2 作为开始日期、TODAY() 作为结束日期，就得到从装船到今天的在途天数。注意日期必须是真正的日期格式，不是文本。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：入职天数计算（TODAY + DATEDIF）</t>
+          <t>第 3 题：第3题：重量汇总与计数</t>
         </is>
       </c>
     </row>
@@ -1186,14 +1312,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回当前日期，无需参数，每天打开表格会自动更新。DATEDIF 语法为 DATEDIF(开始日期,结束日期,单位)，单位 "Y" 表示相差的整年数。这里开始日期是 B2 的入职日期，结束日期是 TODAY()，即可得到截至今天的入职年数。DATEDIF 是隐藏函数，需手工输入。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域) 只对满足条件的行求和，这里条件区域是品类列 B2:B6，条件是「生鲜」，求和区域是重量列 C2:C6，结果为 12.5+20+15.5=48。COUNTIF(条件区域, 条件) 统计满足条件的单元格个数，结果为 3。两个函数都是单条件统计，比 SUMIFS/COUNTIFS 更简洁。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：到港天数与误差处理（IFERROR + VLOOKUP）</t>
+          <t>第 4 题：第4题：成绩等级判定与除错</t>
         </is>
       </c>
     </row>
@@ -1205,14 +1331,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 语法为 VLOOKUP(查找值,查找区域,返回第几列,匹配方式)，第4参数用 0 表示精确匹配。这里在 A2:B5 的第一列找 E2 的运单号，找到后返回第 2 列（到港天数）。当运单号不存在时 VLOOKUP 会返回 #N/A 错误，外层用 IFERROR(值, 出错时显示内容) 把它替换成 "无记录"，让报表更整洁。</t>
+          <t>IF(条件, 真值, 假值) 根据条件返回不同结果，B2&gt;=60 成立返回「合格」，否则「不合格」。IFERROR(公式, 出错时返回值) 会把公式中的错误（如 #VALUE!）替换成指定内容。把 IF 写在 IFERROR 里面，就能在正常判定等级的同时，对异常数据给出「待录入」提示。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：货品单价查询与金额计算（INDEX + MATCH + ROUND）</t>
+          <t>第 5 题：第5题：物流报价查表匹配</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1350,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值,查找区域,0) 返回查找值在区域中的位置，MATCH("显示器",A2:A5,0) 得 3。INDEX(B2:B5,位置) 按位置取出单价区的值，得 899.9。INDEX+MATCH 不受列顺序限制，比 VLOOKUP 更灵活。最后用 ROUND(数值,2) 将 899.9*3 的结果四舍五入保留 2 位小数，得 2699.7。</t>
+          <t>XLOOKUP 支持多条件：用 (A2:A7="上海")*(B2:B7="10-50kg") 生成一个数组，只有两条件都成立的位置为 1，然后在查找值里写 1，返回 C2:C7 对应单价 7。ROUND(数值, 2) 把运费四舍五入保留两位小数，20×7=140，结果为 140。若用 VLOOKUP，需要先加辅助列把「目的地&amp;重量段」拼成一个键再查；INDEX+MATCH 也可用 MATCH 定位行号后由 INDEX 取值，思路相同。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,171 +476,136 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：运费台账区间统计</t>
+          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司有一份运费台账，记录了每笔运单的线路、货物类型和运费金额。现在需要统计「华东线」且货物类型为「重货」的运费合计，放到 F2 单元格。</t>
+          <t>要求：你是一名仓库管理员，手上有一份按日期记录的发货台账，需要快速统计出「食品」这一类商品的总发货重量（公斤）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格输入公式，统计线路为「华东线」且货物类型为「重货」的运费总和。</t>
+          <t>任务：在空白单元格（如 F1）输入公式，统计「商品类别」为「食品」的发货重量总和，结果应为 495。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>线路</t>
+          <t>商品类别</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>货物类型</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
+          <t>发货重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>重货</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>320</v>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>华南线</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>轻货</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>180</v>
+          <t>日化</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>轻货</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>260</v>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>YD004</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>重货</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>450</v>
+          <t>饮料</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>YD005</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华南线</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>重货</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>390</v>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>YD006</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>华东线</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>重货</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>210</v>
+          <t>日化</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -653,367 +618,367 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：统计指定区间的订单数量</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：货代公司需要跟踪每批货物的在途天数。表格记录了装船日期，要求计算每批货物从装船到今天已经过了多少天，结果放在 D 列。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式并向下填充到 D4，计算每批货物从装船日期到今天（TODAY）的天数。</t>
+          <t>要求：销售部有一份订单明细表，需要统计「华东」地区中「金额大于等于 500」的订单共有多少笔。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>批次号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>装船日期</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>已装船天数</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格输入公式，统计「地区」为「华东」且「金额」&gt;=500 的订单数，结果应为 2。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>大米</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>520</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>机械零件</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：重量汇总与计数</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库有一份到货明细，记录了每件货物的品类和重量。需要先统计「生鲜」品类的总重量，再统计「生鲜」品类的件数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 用公式统计品类为「生鲜」的重量总和；在 E3 用公式统计品类为「生鲜」的件数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>12.5</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>干货</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>8</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流跟单员需要根据每批货物的「到港日期」，计算从到港当天到今天已经过去了多少天，用于判断滞港情况。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>20</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设今天是 2024-04-01，在空白单元格输入公式，计算 B101 批次从到港日期到今天的已过天数，结果应为 82。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>生鲜</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>15.5</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>批次</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>B101</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>干货</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>9</v>
+          <t>2024-01-10</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>B102</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>B103</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：成绩等级判定与除错</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：培训考核表记录了每位学员的得分，需要根据得分判定等级：60 分及以上为「合格」，否则为「不合格」。同时用 IFERROR 处理可能出现的错误值。</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式并向下填充，用 IF 判断得分是否≥60，返回「合格」或「不合格」；再用 IFERROR 包裹，使出错时显示「待录入」。</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据商品编号提取并查价</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>得分</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>等级</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：商品编号格式为「前缀+数字」如 SP1001，其中后三位是商品序号。需要先从编号中取出后 3 位作为查询键，再用 VLOOKUP 在价格表中查出对应单价。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格输入公式，对编号 SP1002 取出后 3 位「002」，再据此在价格表中查出单价，结果应为 3.2。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
+          <t>SP1001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
+          <t>SP1002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>SP1003</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：物流报价查表匹配</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司有一张按目的地和重量段制定的运费单价表（元/kg）。现需要根据目的地和重量段查出单价，并计算运费（重量×单价，保留两位小数）。</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 单元格用 XLOOKUP 或多个函数组合，根据 D2 中的「目的地」和「重量段」两个条件查出单价，再用 ROUND 计算运费（重量 20kg，保留两位小数）。</t>
+          <t>要求：一份各地区季度销量表，需要先找出销量最高的数值，再通过 INDEX+MATCH 定位该数值对应的地区名称，并可结合 MAX 与 IFERROR 处理异常。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>重量段</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格输入公式，找出「二季度」销量最高的地区名称，结果应为「广州」（二季度最大值 450 对应广州）。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>0-10kg</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>8</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>一季度</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>二季度</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1022,13 +987,11 @@
           <t>北京</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>10-50kg</t>
-        </is>
+      <c r="B49" s="4" t="n">
+        <v>320</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>6</v>
+        <v>410</v>
       </c>
     </row>
     <row r="50">
@@ -1037,62 +1000,41 @@
           <t>上海</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>0-10kg</t>
-        </is>
+      <c r="B50" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>9</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>10-50kg</t>
-        </is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>360</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>7</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>0-10kg</t>
-        </is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>300</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>10</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>10-50kg</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1119,7 +1061,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：运费台账区间统计</t>
+          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1072,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(D2:D7,B2:B7,"华东线",C2:C7,"重货")</f>
+        <f>SUMIF(B2:B7,"食品",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1144,7 +1086,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：统计指定区间的订单数量</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1097,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(C2,TODAY(),"D")</f>
+        <f>COUNTIFS(B2:B7,"华东",C2:C7,"&gt;=500")</f>
         <v/>
       </c>
     </row>
@@ -1169,7 +1111,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：重量汇总与计数</t>
+          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1122,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIF(B2:B6,"生鲜",C2:C6)；件数公式：=COUNTIF(B2:B6,"生鲜")</f>
+        <f>DATEDIF(B2,TODAY(),"D")</f>
         <v/>
       </c>
     </row>
@@ -1194,7 +1136,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：成绩等级判定与除错</t>
+          <t>第 4 题：第4题：根据商品编号提取并查价</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1147,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(IF(B2&gt;=60,"合格","不合格"),"待录入")</f>
+        <f>VLOOKUP(RIGHT("SP1002",3),C2:D4,2,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1219,7 +1161,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：物流报价查表匹配</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1172,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(20*XLOOKUP(1,(A2:A7="上海")*(B2:B7="10-50kg"),C2:C7),2)</f>
+        <f>INDEX(A2:A5,MATCH(MAX(C2:C5),C2:C5,0))</f>
         <v/>
       </c>
     </row>
@@ -1262,7 +1204,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：运费台账区间统计</t>
+          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
         </is>
       </c>
     </row>
@@ -1274,14 +1216,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。先指定求和区域 D2:D7（运费），再给出两个条件：线路列 B2:B7 等于「华东线」，货物类型列 C2:C7 等于「重货」。只有同时满足两个条件的行才被求和，结果为 320+450+210=980。文本条件要加英文双引号。</t>
+          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B7（商品类别），条件是 "食品"，求和区域是 C2:C7（发货重量），即把类别为食品的重量相加：120+200+175=495。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：到港天数计算</t>
+          <t>第 2 题：第2题：统计指定区间的订单数量</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1235,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期。DATEDIF(开始日期, 结束日期, "D") 返回两个日期之间的整天数，第三个参数 "D" 表示按天计算。用 C2 作为开始日期、TODAY() 作为结束日期，就得到从装船到今天的在途天数。注意日期必须是真正的日期格式，不是文本。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。这里对地区列 B2:B7 限定 "华东"，同时对金额列 C2:C7 限定 "&gt;=500"，两个条件同时满足的订单是 A001 和 A004，共 2 笔。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：重量汇总与计数</t>
+          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1254,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域) 只对满足条件的行求和，这里条件区域是品类列 B2:B6，条件是「生鲜」，求和区域是重量列 C2:C6，结果为 12.5+20+15.5=48。COUNTIF(条件区域, 条件) 统计满足条件的单元格个数，结果为 3。两个函数都是单条件统计，比 SUMIFS/COUNTIFS 更简洁。</t>
+          <t>DATEDIF(开始日期,结束日期,"D") 返回两个日期之间的整天数；TODAY() 返回今天的日期。以 B101 的 2024-01-10 到 2024-04-01 计算，相差 82 天。注意 DATEDIF 是隐藏函数，需手动输入函数名。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：成绩等级判定与除错</t>
+          <t>第 4 题：第4题：根据商品编号提取并查价</t>
         </is>
       </c>
     </row>
@@ -1331,14 +1273,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IF(条件, 真值, 假值) 根据条件返回不同结果，B2&gt;=60 成立返回「合格」，否则「不合格」。IFERROR(公式, 出错时返回值) 会把公式中的错误（如 #VALUE!）替换成指定内容。把 IF 写在 IFERROR 里面，就能在正常判定等级的同时，对异常数据给出「待录入」提示。</t>
+          <t>RIGHT(文本,3) 从右侧截取 3 个字符，"SP1002" 得到 "002"；VLOOKUP(查找值,查找区域,返回列号,精确匹配) 在 C2:D4 的序号列中精确查找 "002"，返回第 2 列单价 3.2。FALSE 表示精确匹配，务必加上。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：物流报价查表匹配</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1292,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 支持多条件：用 (A2:A7="上海")*(B2:B7="10-50kg") 生成一个数组，只有两条件都成立的位置为 1，然后在查找值里写 1，返回 C2:C7 对应单价 7。ROUND(数值, 2) 把运费四舍五入保留两位小数，20×7=140，结果为 140。若用 VLOOKUP，需要先加辅助列把「目的地&amp;重量段」拼成一个键再查；INDEX+MATCH 也可用 MATCH 定位行号后由 INDEX 取值，思路相同。</t>
+          <t>MAX(C2:C5) 先算出二季度最大值 450；MATCH(450,C2:C5,0) 在二季度列中精确查找 450 所在的行位置，返回 3；INDEX(A2:A5,3) 取地区列第 3 个即「广州」。INDEX 负责按位置返回值，MATCH 负责找位置，二者配合可实现反向或灵活查表。若担心找不到，可外套 IFERROR(公式,"未找到")。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,565 +476,696 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIF</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：小王管理一个仓库出库台账，需要按商品名称和日期汇总出库重量，并练习单条件与多条件求和。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一名仓库管理员，手上有一份按日期记录的发货台账，需要快速统计出「食品」这一类商品的总发货重量（公斤）。</t>
+          <t>任务：在 F2 单元格统计商品名称为“苹果”的总出库重量；在 F3 单元格统计 A 仓中“苹果”的总出库重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（如 F1）输入公式，统计「商品类别」为「食品」的发货重量总和，结果应为 495。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>出库重量(kg)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>商品类别</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>发货重量(kg)</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>120</v>
+        <v>80</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>日化</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>85</v>
+        <v>150</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>150</v>
+        <v>60</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>175</v>
+        <v>110</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>日化</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单数量计数与到港天数</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计指定区间的订单数量</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司统计订单台账，需要统计某类订单数量，并计算出库日期到今天的在途天数，练习计数函数与日期函数。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 统计“上海-北京”线路的订单数量；在 G3 统计“上海-北京”线路且状态为“在途”的订单数量；在 G4 用 DATEDIF 计算 DD002 从出库日期到今天（以 TODAY 为准）的在途天数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售部有一份订单明细表，需要统计「华东」地区中「金额大于等于 500」的订单共有多少笔。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>线路</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>出库日期</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>出库重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，统计「地区」为「华东」且「金额」&gt;=500 的订单数，结果应为 2。</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DD001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DD002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>上海-广州</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>在途</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>DD003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>520</v>
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>在途</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>DD004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>800</v>
+          <t>上海-广州</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>DD005</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>300</v>
+          <t>上海-北京</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>410</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>900</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>480</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：重量最大值与四舍五入</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库对每批货物称重并记录单价，需要找出最重的一批，并计算该批重量以“斤”为单位、保留 1 位小数的结果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 用 MAX 求出最大重量；在 E3 将最大重量换算成斤（1kg=2斤）并用 ROUND 保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流跟单员需要根据每批货物的「到港日期」，计算从到港当天到今天已经过去了多少天，用于判断滞港情况。</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>钢材</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1250.5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设今天是 2024-04-01，在空白单元格输入公式，计算 B101 批次从到港日期到今天的已过天数，结果应为 82。</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>980.25</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>批次</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>水泥</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1420.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>B101</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
-        </is>
+          <t>砂石</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1100.4</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>B102</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>B103</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按订单号查客户联系方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：客服需要根据订单号在客户信息表中查询客户姓名和电话，查不到时显示“未找到”，练习查找函数与错误处理。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据商品编号提取并查价</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 输入订单号“DD1003”，在 G3 用 VLOOKUP 查出对应客户姓名；在 G4 用 VLOOKUP 查出电话，并用 IFERROR 处理查不到的情况显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品编号格式为「前缀+数字」如 SP1001，其中后三位是商品序号。需要先从编号中取出后 3 位作为查询键，再用 VLOOKUP 在价格表中查出对应单价。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>电话</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，对编号 SP1002 取出后 3 位「002」，再据此在价格表中查出单价，结果应为 3.2。</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>DD1001</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>DD1002</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>SP1001</t>
+          <t>DD1003</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>5.5</v>
+          <t>13700003333</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>SP1002</t>
+          <t>DD1004</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>002</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>3.2</v>
+          <t>13600004444</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>SP1003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事部门有一张员工信息表，需要按工号查出姓名和部门，并练习从工号字符串中截取信息，体验 INDEX+MATCH 与 XLOOKUP 两种查表方式。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>要求：一份各地区季度销量表，需要先找出销量最高的数值，再通过 INDEX+MATCH 定位该数值对应的地区名称，并可结合 MAX 与 IFERROR 处理异常。</t>
+          <t>任务：在 H2 输入工号“BJ-2019-003”，在 H3 用 INDEX+MATCH 查出姓名；在 H4 用 XLOOKUP 查出部门；在 H5 用 MID 截取工号中的年份；在 H6 用 RIGHT 取出工号最后 3 位序号。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格输入公式，找出「二季度」销量最高的地区名称，结果应为「广州」（二季度最大值 450 对应广州）。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>入职年份</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>一季度</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>二季度</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SH-2021-001</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>陈明</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>410</v>
+          <t>SH-2020-002</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>林芳</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>390</v>
+          <t>BJ-2019-003</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>周强</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>450</v>
+          <t>BJ-2022-004</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>吴敏</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1061,7 +1192,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1071,9 +1202,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <f>SUMIF(B2:B7,"食品",C2:C7)</f>
-        <v/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>F2: =SUMIF(B2:B7,"苹果",C2:C7)  F3: =SUMIFS(C2:C7,B2:B7,"苹果",D2:D7,"A仓")</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1086,7 +1218,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计指定区间的订单数量</t>
+          <t>第 2 题：第2题：订单数量计数与到港天数</t>
         </is>
       </c>
     </row>
@@ -1096,9 +1228,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIFS(B2:B7,"华东",C2:C7,"&gt;=500")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>G2: =COUNTIF(B2:B6,"上海-北京")  G3: =COUNTIFS(B2:B6,"上海-北京",C2:C6,"在途")  G4: =DATEDIF(D3,TODAY(),"D")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1111,7 +1244,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
+          <t>第 3 题：第3题：重量最大值与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1121,9 +1254,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"D")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>E2: =MAX(C2:C5)  E3: =ROUND(MAX(C2:C5)*2,1)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1136,7 +1270,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据商品编号提取并查价</t>
+          <t>第 4 题：第4题：按订单号查客户联系方式</t>
         </is>
       </c>
     </row>
@@ -1146,9 +1280,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>VLOOKUP(RIGHT("SP1002",3),C2:D4,2,FALSE)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>G3: =VLOOKUP(G2,A2:C5,2,FALSE)  G4: =IFERROR(VLOOKUP(G2,A2:C5,3,FALSE),"未找到")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1161,7 +1296,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
         </is>
       </c>
     </row>
@@ -1171,9 +1306,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>INDEX(A2:A5,MATCH(MAX(C2:C5),C2:C5,0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>H3: =INDEX(B2:B5,MATCH(H2,A2:A5,0))  H4: =XLOOKUP(H2,A2:A5,C2:C5)  H5: =MID(H2,4,4)  H6: =RIGHT(H2,3)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1204,7 +1340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按商品类别汇总发货重量</t>
+          <t>第 1 题：第1题：仓库出库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1352,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B7（商品类别），条件是 "食品"，求和区域是 C2:C7（发货重量），即把类别为食品的重量相加：120+200+175=495。</t>
+          <t>SUMIF(条件区域,条件,求和区域)用于单条件求和，F2 统计 B 列为“苹果”对应的 C 列重量之和，结果 470。SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)用于多条件求和，F3 同时要求 B 列为“苹果”且 D 列为“A仓”，结果 380。注意 SUMIFS 的求和区域写在最前面。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计指定区间的订单数量</t>
+          <t>第 2 题：第2题：订单数量计数与到港天数</t>
         </is>
       </c>
     </row>
@@ -1235,14 +1371,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(区域1,条件1,区域2,条件2,...)。这里对地区列 B2:B7 限定 "华东"，同时对金额列 C2:C7 限定 "&gt;=500"，两个条件同时满足的订单是 A001 和 A004，共 2 笔。</t>
+          <t>COUNTIF(区域,条件)统计满足单个条件的单元格个数，G2 结果为 3。COUNTIFS(区域1,条件1,区域2,条件2)统计同时满足多个条件的个数，G3 结果为 1。DATEDIF(开始日期,结束日期,"D")返回两个日期相差的整天数，TODAY()返回当天日期，所以 G4 返回 DD002 从 2024-04-10 到今天的实际天数（随时间变化）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算货物到港天数（含今天）</t>
+          <t>第 3 题：第3题：重量最大值与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1390,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,"D") 返回两个日期之间的整天数；TODAY() 返回今天的日期。以 B101 的 2024-01-10 到 2024-04-01 计算，相差 82 天。注意 DATEDIF 是隐藏函数，需手动输入函数名。</t>
+          <t>MAX(区域)返回区域中的最大值，E2 结果为 1420.75。ROUND(数值,小数位数)对数值四舍五入，第二参数为 1 表示保留 1 位小数；E3 先取最大值再乘以 2 换算成斤，最后保留 1 位小数，结果 2841.5。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据商品编号提取并查价</t>
+          <t>第 4 题：第4题：按订单号查客户联系方式</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1409,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT(文本,3) 从右侧截取 3 个字符，"SP1002" 得到 "002"；VLOOKUP(查找值,查找区域,返回列号,精确匹配) 在 C2:D4 的序号列中精确查找 "002"，返回第 2 列单价 3.2。FALSE 表示精确匹配，务必加上。</t>
+          <t>VLOOKUP(查找值,查找区域,返回列序号,精确匹配)在区域首列查找值并返回同行指定列，第 4 参数用 FALSE 表示精确匹配；G3 返回“王五”。IFERROR(公式,错误时显示的值)在公式出错（如查不到返回 #N/A）时显示指定内容，G4 正常返回“13700003333”。若把 G2 改成不存在的订单号，G4 会显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表找最高分地区</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1428,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MAX(C2:C5) 先算出二季度最大值 450；MATCH(450,C2:C5,0) 在二季度列中精确查找 450 所在的行位置，返回 3；INDEX(A2:A5,3) 取地区列第 3 个即「广州」。INDEX 负责按位置返回值，MATCH 负责找位置，二者配合可实现反向或灵活查表。若担心找不到，可外套 IFERROR(公式,"未找到")。</t>
+          <t>MATCH(查找值,区域,0)返回查找值在区域中的位置（精确匹配），H2 在 A 列排第 3 行，返回 3；INDEX(返回区域,行号)按行号取出对应值，H3 得到 B 列第 3 个值“周强”。XLOOKUP(查找值,查找区域,返回区域)直接按对应关系返回，H4 得到“技术部”。MID(文本,起始位置,字符数)从第 4 个字符起截 4 位，得到“2019”；RIGHT(文本,字符数)从右端截 3 位，得到“003”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,696 +476,660 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：小王管理一个仓库出库台账，需要按商品名称和日期汇总出库重量，并练习单条件与多条件求和。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格统计商品名称为“苹果”的总出库重量；在 F3 单元格统计 A 仓中“苹果”的总出库重量。</t>
+          <t>要求：你是销售助理，手上有一份客户订单台账。老板想快速知道「宏达物流」这一家客户累计下单了多少钱，需要用一个函数自动求和，而不是手动挑选。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>出库重量(kg)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格 E2 中输入公式，计算客户名称为「宏达物流」的所有订单金额合计，结果应为 3750。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>A仓</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>SO001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>宏达物流</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>B仓</t>
-        </is>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>SO002</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>启程贸易</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>A仓</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>SO003</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>宏达物流</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>B仓</t>
-        </is>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>SO004</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>恒安仓储</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>A仓</t>
-        </is>
+        <v>990</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>SO005</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>宏达物流</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>A仓</t>
-        </is>
+        <v>2100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO006</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>启程贸易</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：订单数量计数与到港天数</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司统计订单台账，需要统计某类订单数量，并计算出库日期到今天的在途天数，练习计数函数与日期函数。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 G2 统计“上海-北京”线路的订单数量；在 G3 统计“上海-北京”线路且状态为“在途”的订单数量；在 G4 用 DATEDIF 计算 DD002 从出库日期到今天（以 TODAY 为准）的在途天数。</t>
+          <t>要求：你是物流专员，负责跟踪进口批次的实际到港日期。台账里记录了计划到港日和实际到港日，需要先算出每批的延误天数，再统计有多少批发生了延误（延误天数大于 0），并用 TODAY 函数保证「今天」是动态自动更新的。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>线路</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>出库日期</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>出库重量(kg)</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2:D6 输入公式计算每批的延误天数（实际到港日-计划到港日），然后在 E2 用 COUNTIF 统计延误天数大于 0 的批次数；并在 F2 用 TODAY 显示当天日期。答案给出 D2 与 E2 的公式。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DD001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>320</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>计划到港日</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>实际到港日</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DD002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>上海-广州</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>在途</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-10</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>150</v>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>45203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DD003</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>在途</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>200</v>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>45205</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>45205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>DD004</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>上海-广州</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>90</v>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>45210</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>45212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>DD005</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>上海-北京</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>410</v>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>45215</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>45214</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>45220</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>45226</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：重量最大值与四舍五入</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库对每批货物称重并记录单价，需要找出最重的一批，并计算该批重量以“斤”为单位、保留 1 位小数的结果。</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 用 MAX 求出最大重量；在 E3 将最大重量换算成斤（1kg=2斤）并用 ROUND 保留 1 位小数。</t>
+          <t>要求：仓库主管要统计「华东仓」中「已出库」状态的货物总重量（单位 kg），重量常带多位小数，报表要求保留 2 位小数。请用多条件求和函数一次完成，再用 ROUND 处理结果。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>批次号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F2 输入公式，统计仓库为「华东仓」且状态为「已出库」的重量合计，并将结果四舍五入保留 2 位小数。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>钢材</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1250.5</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>YT001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>木材</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>980.25</v>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>已出库</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>123.456</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>YT002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>水泥</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1420.75</v>
+          <t>华南仓</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>已出库</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>88.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>YT003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>砂石</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1100.4</v>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>已出库</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>200.789</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YT004</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>待出库</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>YT005</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>华南仓</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>待出库</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>66.66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YT006</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>已出库</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>10.005</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按订单号查客户联系方式</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服需要根据订单号在客户信息表中查询客户姓名和电话，查不到时显示“未找到”，练习查找函数与错误处理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 输入订单号“DD1003”，在 G3 用 VLOOKUP 查出对应客户姓名；在 G4 用 VLOOKUP 查出电话，并用 IFERROR 处理查不到的情况显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>客户姓名</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>电话</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>DD1001</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：质检部门有一份抽检记录，记录了每件产品的重量。质检员要求：统计重量在 100 到 500 克之间（含边界）的合格件数，并找出所有记录中最重的那一件是多少克。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>DD1002</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 用 COUNTIFS 统计重量在 100 到 500 之间（含 100 和 500）的记录条数；在 E3 用 MAX 求最大重量。答案给出 E2 与 E3 的公式。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>DD1003</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>记录号</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>重量g</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>DD1004</t>
+          <t>Q01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>13600004444</t>
-        </is>
+          <t>A型</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Q02</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>A型</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Q03</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>B型</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Q04</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>B型</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Q05</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>A型</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Q06</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>B型</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：人事部门有一张员工信息表，需要按工号查出姓名和部门，并练习从工号字符串中截取信息，体验 INDEX+MATCH 与 XLOOKUP 两种查表方式。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 H2 输入工号“BJ-2019-003”，在 H3 用 INDEX+MATCH 查出姓名；在 H4 用 XLOOKUP 查出部门；在 H5 用 MID 截取工号中的年份；在 H6 用 RIGHT 取出工号最后 3 位序号。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事部有一份员工档案，包含工号、姓名和入职日期（日期为序列号）。现在拿到一个工号「E003」，需要自动查出该员工姓名，并算出他截至今天已经入职满多少整年（用于计算年假）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F1 输入工号 E003，在 F2 用 XLOOKUP（或 VLOOKUP）根据 F1 查出姓名；在 F3 用 DATEDIF 计算该员工从入职到今天满多少整年。答案给出 F2 与 F3 的公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>工号</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>入职年份</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>SH-2021-001</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>陈明</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>SH-2020-002</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>林芳</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>BJ-2019-003</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>周强</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>BJ-2022-004</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>吴敏</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>43831</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1192,7 +1156,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1202,10 +1166,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>F2: =SUMIF(B2:B7,"苹果",C2:C7)  F3: =SUMIFS(C2:C7,B2:B7,"苹果",D2:D7,"A仓")</t>
-        </is>
+      <c r="B2" s="2">
+        <f>SUMIF(B2:B7,"宏达物流",C2:C7)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1218,7 +1181,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数与到港天数</t>
+          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
         </is>
       </c>
     </row>
@@ -1228,10 +1191,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>G2: =COUNTIF(B2:B6,"上海-北京")  G3: =COUNTIFS(B2:B6,"上海-北京",C2:C6,"在途")  G4: =DATEDIF(D3,TODAY(),"D")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>C2-B2 ；=COUNTIF(D2:D6,"&gt;0") ；=TODAY()</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1244,7 +1206,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：重量最大值与四舍五入</t>
+          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1254,10 +1216,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>E2: =MAX(C2:C5)  E3: =ROUND(MAX(C2:C5)*2,1)</t>
-        </is>
+      <c r="B10" s="2">
+        <f>ROUND(SUMIFS(D2:D7,B2:B7,"华东仓",C2:C7,"已出库"),2)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1270,7 +1231,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按订单号查客户联系方式</t>
+          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1241,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>G3: =VLOOKUP(G2,A2:C5,2,FALSE)  G4: =IFERROR(VLOOKUP(G2,A2:C5,3,FALSE),"未找到")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>COUNTIFS(C2:C7,"&gt;=100",C2:C7,"&lt;=500") ；=MAX(C2:C7)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1296,7 +1256,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
+          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1306,10 +1266,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>H3: =INDEX(B2:B5,MATCH(H2,A2:A5,0))  H4: =XLOOKUP(H2,A2:A5,C2:C5)  H5: =MID(H2,4,4)  H6: =RIGHT(H2,3)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>XLOOKUP(F1,A2:A5,B2:B5) ；=DATEDIF(XLOOKUP(F1,A2:A5,C2:C5),TODAY(),"Y")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1340,7 +1299,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库出库重量汇总</t>
+          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1352,14 +1311,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域,条件,求和区域)用于单条件求和，F2 统计 B 列为“苹果”对应的 C 列重量之和，结果 470。SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2)用于多条件求和，F3 同时要求 B 列为“苹果”且 D 列为“A仓”，结果 380。注意 SUMIFS 的求和区域写在最前面。</t>
+          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。本题条件区域是 B2:B7（客户名称列），条件是文本"宏达物流"，求和区域是 C2:C7（订单金额列）。函数会逐行判断客户名称是否等于「宏达物流」，相等则把对应金额相加：1200+450+2100=3750。注意文本条件要加英文双引号。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数与到港天数</t>
+          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
         </is>
       </c>
     </row>
@@ -1371,14 +1330,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(区域,条件)统计满足单个条件的单元格个数，G2 结果为 3。COUNTIFS(区域1,条件1,区域2,条件2)统计同时满足多个条件的个数，G3 结果为 1。DATEDIF(开始日期,结束日期,"D")返回两个日期相差的整天数，TODAY()返回当天日期，所以 G4 返回 DD002 从 2024-04-10 到今天的实际天数（随时间变化）。</t>
+          <t>D2 用 =C2-B2 得到日期差（Excel 日期本质是序列号，相减即天数）。COUNTIF(区域, 条件) 语法为 COUNTIF(D2:D6, "&gt;0")，统计大于 0 的单元格个数，即延误批次数。TODAY() 无参数，返回今天的日期且每次打开自动更新，常用于计算「逾期天数=TODAY()-计划日」。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：重量最大值与四舍五入</t>
+          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1390,14 +1349,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MAX(区域)返回区域中的最大值，E2 结果为 1420.75。ROUND(数值,小数位数)对数值四舍五入，第二参数为 1 表示保留 1 位小数；E3 先取最大值再乘以 2 换算成斤，最后保留 1 位小数，结果 2841.5。</t>
+          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)，本题求和区域是 D2:D7，条件1 为 B2:B7="华东仓"，条件2 为 C2:C7="已出库"，得到 123.456+200.789+10.005=334.25。ROUND(数值, 小数位数) 将结果保留 2 位小数，语法为 ROUND(数值,2)。若只想显示两位可改单元格格式，但 ROUND 会真正改变数值。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按订单号查客户联系方式</t>
+          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
         </is>
       </c>
     </row>
@@ -1409,14 +1368,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值,查找区域,返回列序号,精确匹配)在区域首列查找值并返回同行指定列，第 4 参数用 FALSE 表示精确匹配；G3 返回“王五”。IFERROR(公式,错误时显示的值)在公式出错（如查不到返回 #N/A）时显示指定内容，G4 正常返回“13700003333”。若把 G2 改成不存在的订单号，G4 会显示“未找到”。</t>
+          <t>COUNTIFS 可对同一区域设置多个条件，本题 C2:C7 同时满足 "&gt;=100" 和 "&lt;=500"，即 120、480、500、300 共 4 条（符合条件返回 4）。MAX(区域) 返回区域中最大数值，即 650。注意比较运算符要写在英文双引号内。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查询与 XLOOKUP 查询</t>
+          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1387,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值,区域,0)返回查找值在区域中的位置（精确匹配），H2 在 A 列排第 3 行，返回 3；INDEX(返回区域,行号)按行号取出对应值，H3 得到 B 列第 3 个值“周强”。XLOOKUP(查找值,查找区域,返回区域)直接按对应关系返回，H4 得到“技术部”。MID(文本,起始位置,字符数)从第 4 个字符起截 4 位，得到“2019”；RIGHT(文本,字符数)从右端截 3 位，得到“003”。</t>
+          <t>XLOOKUP(查找值, 查找区域, 返回区域) 在 A2:A5 中找到 E003，返回 B2:B5 对应姓名「王强」；若用旧函数写作 =VLOOKUP(F1,A2:C5,2,FALSE)。DATEDIF(开始日期, 结束日期, "Y") 返回两日期之间的整年数，本题开始日期用 XLOOKUP 取到入职日期，结束日期为 TODAY()，"Y" 表示整年，即入职至今满多少年。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,28 +476,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
+          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是销售助理，手上有一份客户订单台账。老板想快速知道「宏达物流」这一家客户累计下单了多少钱，需要用一个函数自动求和，而不是手动挑选。</t>
+          <t>要求：你是一家小物流公司的财务，需要统计「华东」区域已签收订单的运费总额，用于月度对账。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格 E2 中输入公式，计算客户名称为「宏达物流」的所有订单金额合计，结果应为 3750。</t>
+          <t>任务：请在 H2 单元格输入公式，计算「区域」为华东且「状态」为已签收的运费合计。</t>
         </is>
       </c>
     </row>
@@ -509,103 +509,138 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>区域</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SO001</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>宏达物流</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1200</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SO002</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>启程贸易</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>800</v>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SO003</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>宏达物流</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>450</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SO004</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>恒安仓储</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>990</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SO005</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>宏达物流</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2100</v>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SO006</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>启程贸易</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>300</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -618,274 +653,239 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
+          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流专员，负责跟踪进口批次的实际到港日期。台账里记录了计划到港日和实际到港日，需要先算出每批的延误天数，再统计有多少批发生了延误（延误天数大于 0），并用 TODAY 函数保证「今天」是动态自动更新的。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2:D6 输入公式计算每批的延误天数（实际到港日-计划到港日），然后在 E2 用 COUNTIF 统计延误天数大于 0 的批次数；并在 F2 用 TODAY 显示当天日期。答案给出 D2 与 E2 的公式。</t>
+          <t>要求：仓库主管想知道「华南」区域中状态为「已签收」的订单有多少笔，方便考核该区域时效。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>批次号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>计划到港日</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>实际到港日</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 单元格输入公式，统计区域为华南且状态为已签收的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>45200</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>45203</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>45205</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>45205</v>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>B03</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>45210</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>45212</v>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>B04</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>45215</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>45214</v>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>B05</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>45220</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>45226</v>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库主管要统计「华东仓」中「已出库」状态的货物总重量（单位 kg），重量常带多位小数，报表要求保留 2 位小数。请用多条件求和函数一次完成，再用 ROUND 处理结果。</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 输入公式，统计仓库为「华东仓」且状态为「已出库」的重量合计，并将结果四舍五入保留 2 位小数。</t>
+          <t>要求：物流公司规定单件货物重量超过30kg需走「超重件」通道。请根据重量列判断每单类型，并用 IFERROR 让空重量单元格显示“待补录”而不是报错。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C 列对应的 D2:D6 单元格输入公式，重量大于30返回“超重件”，否则返回“普通件”；若重量为空或无法计算则返回“待补录”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>运单号</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>重量kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>YT001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>已出库</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>123.456</v>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>货物重量</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>YT002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>华南仓</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>已出库</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>88.2</v>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>YT003</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>已出库</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>200.789</v>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>YT004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>待出库</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>55.5</v>
-      </c>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>YT005</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>华南仓</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>待出库</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>66.66</v>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>YT006</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>华东仓</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>已出库</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>10.005</v>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -898,238 +898,251 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
+          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>要求：质检部门有一份抽检记录，记录了每件产品的重量。质检员要求：统计重量在 100 到 500 克之间（含边界）的合格件数，并找出所有记录中最重的那一件是多少克。</t>
+          <t>要求：货运代理需要监控到港时长。已知每票货的到港日期，请计算从到港日到今天已过多少天，并判断是否超过7天。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 用 COUNTIFS 统计重量在 100 到 500 之间（含 100 和 500）的记录条数；在 E3 用 MAX 求最大重量。答案给出 E2 与 E3 的公式。</t>
+          <t>任务：请在 D2 单元格输入公式计算到港至今的天数，并向下填充到 D4；再用 IF 在 E2 判断：超过7天显示“超期”，否则显示“正常”。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>记录号</t>
+          <t>提单号</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>到港日期</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>重量g</t>
+          <t>货物</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Q01</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A型</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>95</v>
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>机械配件</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Q02</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A型</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>120</v>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>纺织品</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Q03</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>B型</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>480</v>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Q04</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>B型</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Q05</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>A型</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>300</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Q06</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>B型</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>650</v>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：报价表按目的地列出了首重价格。请根据报价表，用查找函数自动填入每个订单的运费单价，要求兼容不同 Excel 版本（新版本用 XLOOKUP，老版本用 VLOOKUP 或 INDEX+MATCH）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在订单表的 D2:D5 单元格输入公式，根据 B2 的目的地在下方报价表（A6:B10，A列目的地、B列单价）中查出单价。请给出 XLOOKUP、VLOOKUP、INDEX+MATCH 三种写法。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>要求：人事部有一份员工档案，包含工号、姓名和入职日期（日期为序列号）。现在拿到一个工号「E003」，需要自动查出该员工姓名，并算出他截至今天已经入职满多少整年（用于计算年假）。</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F1 输入工号 E003，在 F2 用 XLOOKUP（或 VLOOKUP）根据 F1 查出姓名；在 F3 用 DATEDIF 计算该员工从入职到今天满多少整年。答案给出 F2 与 F3 的公式。</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>工号</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
+          <t>E004</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>43831</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>目的地</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>44197</v>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>44562</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>44927</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1156,7 +1169,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
+          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1180,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B7,"宏达物流",C2:C7)</f>
+        <f>SUMIFS(D2:D7,B2:B7,"华东",C2:C7,"已签收")</f>
         <v/>
       </c>
     </row>
@@ -1181,7 +1194,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
+          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1205,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>C2-B2 ；=COUNTIF(D2:D6,"&gt;0") ；=TODAY()</f>
+        <f>COUNTIFS(B2:B6,"华南",C2:C6,"已签收")</f>
         <v/>
       </c>
     </row>
@@ -1206,7 +1219,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
+          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1230,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>ROUND(SUMIFS(D2:D7,B2:B7,"华东仓",C2:C7,"已出库"),2)</f>
+        <f>IFERROR(IF(B2&gt;30,"超重件","普通件"),"待补录")</f>
         <v/>
       </c>
     </row>
@@ -1231,7 +1244,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
+          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1241,9 +1254,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>COUNTIFS(C2:C7,"&gt;=100",C2:C7,"&lt;=500") ；=MAX(C2:C7)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>天数：=DATEDIF(B2,TODAY(),"D")；判断：=IF(D2&gt;7,"超期","正常")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1256,7 +1270,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
+          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
         </is>
       </c>
     </row>
@@ -1266,9 +1280,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>XLOOKUP(F1,A2:A5,B2:B5) ；=DATEDIF(XLOOKUP(F1,A2:A5,C2:C5),TODAY(),"Y")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>XLOOKUP：=XLOOKUP(B2,$A$7:$A$10,$B$7:$B$10)；VLOOKUP：=VLOOKUP(B2,$A$7:$B$10,2,FALSE)；INDEX+MATCH：=INDEX($B$7:$B$10,MATCH(B2,$A$7:$A$10,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1299,7 +1314,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定客户的订单总金额（SUMIF）</t>
+          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1326,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。本题条件区域是 B2:B7（客户名称列），条件是文本"宏达物流"，求和区域是 C2:C7（订单金额列）。函数会逐行判断客户名称是否等于「宏达物流」，相等则把对应金额相加：1200+450+2100=3750。注意文本条件要加英文双引号。</t>
+          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题求和区域是 D2:D7（运费），第一个条件是区域列 B2:B7 等于“华东”，第二个条件是状态列 C2:C7 等于“已签收”。文本条件要加英文双引号。结果为 120+200+90=410。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港延误的批次数量（COUNTIF + TODAY）</t>
+          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
         </is>
       </c>
     </row>
@@ -1330,14 +1345,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D2 用 =C2-B2 得到日期差（Excel 日期本质是序列号，相减即天数）。COUNTIF(区域, 条件) 语法为 COUNTIF(D2:D6, "&gt;0")，统计大于 0 的单元格个数，即延误批次数。TODAY() 无参数，返回今天的日期且每次打开自动更新，常用于计算「逾期天数=TODAY()-计划日」。</t>
+          <t>COUNTIFS 语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)，用于多条件计数。本题统计 B2:B6 中等于“华南”且 C2:C6 中等于“已签收”的行数。符合条件的订单为 B001、B004，共 2 笔。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件汇总出库重量并做四舍五入（SUMIFS + ROUND）</t>
+          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
         </is>
       </c>
     </row>
@@ -1349,14 +1364,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)，本题求和区域是 D2:D7，条件1 为 B2:B7="华东仓"，条件2 为 C2:C7="已出库"，得到 123.456+200.789+10.005=334.25。ROUND(数值, 小数位数) 将结果保留 2 位小数，语法为 ROUND(数值,2)。若只想显示两位可改单元格格式，但 ROUND 会真正改变数值。</t>
+          <t>IF 语法为 IF(判断条件, 条件成立时的值, 不成立时的值)。本题 B2&gt;30 成立返回“超重件”，否则返回“普通件”。外层 IFERROR(值, 出错时显示的内容) 用于捕获错误，例如空单元格参与比较或后续扩展时出现异常，就显示“待补录”。向下填充到 D6 即可。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计区间数量并取出最大值（COUNTIFS + MAX）</t>
+          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
         </is>
       </c>
     </row>
@@ -1368,14 +1383,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 可对同一区域设置多个条件，本题 C2:C7 同时满足 "&gt;=100" 和 "&lt;=500"，即 120、480、500、300 共 4 条（符合条件返回 4）。MAX(区域) 返回区域中最大数值，即 650。注意比较运算符要写在英文双引号内。</t>
+          <t>TODAY() 返回今天的日期且会自动更新。DATEDIF(开始日期, 结束日期, "D") 返回两日期相差的天数，这里开始日期是 B2，结束日期用 TODAY()。得到天数后，用 IF(D2&gt;7,"超期","正常") 做超期判断。注意日期要按 Excel 可识别的日期格式录入。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按编号查表并计算入职年限（XLOOKUP/VLOOKUP + DATEDIF）</t>
+          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1402,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找区域, 返回区域) 在 A2:A5 中找到 E003，返回 B2:B5 对应姓名「王强」；若用旧函数写作 =VLOOKUP(F1,A2:C5,2,FALSE)。DATEDIF(开始日期, 结束日期, "Y") 返回两日期之间的整年数，本题开始日期用 XLOOKUP 取到入职日期，结束日期为 TODAY()，"Y" 表示整年，即入职至今满多少年。</t>
+          <t>XLOOKUP(查找值, 查找数组, 返回数组) 直接在目的地列找 B2，返回对应单价列，无需数列号。VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 中第2列是单价，FALSE 表示精确匹配，且查找值必须在区域首列。INDEX(返回区域, 行号) 配合 MATCH(查找值, 查找区域, 0)（0 为精确匹配）可先定位行号再取单价，适合列顺序被打乱的情况。报价表区域要加 $ 绝对引用以便向下填充。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,35 +476,35 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
+          <t>第 1 题：第1题：按部门汇总销售额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小物流公司的财务，需要统计「华东」区域已签收订单的运费总额，用于月度对账。</t>
+          <t>要求：你是一家公司的财务助理，需要从销售台账中统计“华东区”的总销售额，用于月度汇报。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 H2 单元格输入公式，计算「区域」为华东且「状态」为已签收的运费合计。</t>
+          <t>任务：在 F2 单元格输入公式，计算区域为“华东区”的销售额合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -514,635 +514,488 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>120</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>150</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>200</v>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>2024-01-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>60</v>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流专员需要计算每票货物从“发运日期”到“到港日期”的到港天数，并将结果保留到整数（四舍五入），用于计算仓储费用。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，计算 SF001 的发运到到港天数，并用 ROUND 保留 0 位小数，结果为 17。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库主管想知道「华南」区域中状态为「已签收」的订单有多少笔，方便考核该区域时效。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 单元格输入公式，统计区域为华南且状态为已签收的订单笔数。</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SF001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SF002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>SF003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>12</v>
+          <t>2024-03-01</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>15</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>20</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件统计订单数量</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>B005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>5</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：电商运营需要统计“已完成”且金额大于等于 500 元的订单数量，用于评估高价值订单的完成情况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F2 单元格输入公式，统计状态为“已完成”且金额大于等于 500 的订单数量，结果为 2。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司规定单件货物重量超过30kg需走「超重件」通道。请根据重量列判断每单类型，并用 IFERROR 让空重量单元格显示“待补录”而不是报错。</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>680</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 C 列对应的 D2:D6 单元格输入公式，重量大于30返回“超重件”，否则返回“普通件”；若重量为空或无法计算则返回“待补录”。</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>货物重量</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>待发货</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>25</v>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>42</v>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>30</v>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>55</v>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库管理员需要根据输入的“产品名称”查找到对应的库存数量。如果产品不存在，则显示“未找到”，避免出现错误值影响报表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，根据 E1 中输入的产品名称（例如“扳手”）查找库存数量；如果找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>库存数量</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：货运代理需要监控到港时长。已知每票货的到港日期，请计算从到港日到今天已过多少天，并判断是否超过7天。</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>螺丝刀</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D2 单元格输入公式计算到港至今的天数，并向下填充到 D4；再用 IF 在 E2 判断：超过7天显示“超期”，否则显示“正常”。</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>提单号</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>电工胶带</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>机械配件</t>
-        </is>
+          <t>卷尺</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>纺织品</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售经理需要根据“月份”和“产品”两个条件，从二维销售表中查找对应的销售额。要求使用 INDEX 和 MATCH 组合实现，比 VLOOKUP 更灵活（可向左查找）。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 单元格输入公式，根据 G1 中的月份（如“2月”）和 H1 中的产品（如“产品B”）查找销售额，结果为 1600。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：报价表按目的地列出了首重价格。请根据报价表，用查找函数自动填入每个订单的运费单价，要求兼容不同 Excel 版本（新版本用 XLOOKUP，老版本用 VLOOKUP 或 INDEX+MATCH）。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>产品A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>产品B</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>产品C</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在订单表的 D2:D5 单元格输入公式，根据 B2 的目的地在下方报价表（A6:B10，A列目的地、B列单价）中查出单价。请给出 XLOOKUP、VLOOKUP、INDEX+MATCH 三种写法。</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>1400</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3</v>
+        <v>1700</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1169,7 +1022,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
+          <t>第 1 题：第1题：按部门汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1033,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(D2:D7,B2:B7,"华东",C2:C7,"已签收")</f>
+        <f>SUMIF(B2:B6,"华东区",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1194,7 +1047,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
+          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B6,"华南",C2:C6,"已签收")</f>
+        <f>ROUND(DATEDIF(B2,C2,"d"),0)</f>
         <v/>
       </c>
     </row>
@@ -1219,7 +1072,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
+          <t>第 3 题：第3题：多条件统计订单数量</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1083,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(IF(B2&gt;30,"超重件","普通件"),"待补录")</f>
+        <f>COUNTIFS(B2:B6,"已完成",C2:C6,"&gt;=500")</f>
         <v/>
       </c>
     </row>
@@ -1244,7 +1097,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
+          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
         </is>
       </c>
     </row>
@@ -1254,10 +1107,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>天数：=DATEDIF(B2,TODAY(),"D")；判断：=IF(D2&gt;7,"超期","正常")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(VLOOKUP(E1,A2:B5,2,FALSE),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1270,7 +1122,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1132,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>XLOOKUP：=XLOOKUP(B2,$A$7:$A$10,$B$7:$B$10)；VLOOKUP：=VLOOKUP(B2,$A$7:$B$10,2,FALSE)；INDEX+MATCH：=INDEX($B$7:$B$10,MATCH(B2,$A$7:$A$10,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>INDEX(B2:D4,MATCH(G1,A2:A4,0),MATCH(H1,B1:D1,0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1314,7 +1165,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用SUMIFS按条件汇总运费</t>
+          <t>第 1 题：第1题：按部门汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1177,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。本题求和区域是 D2:D7（运费），第一个条件是区域列 B2:B7 等于“华东”，第二个条件是状态列 C2:C7 等于“已签收”。文本条件要加英文双引号。结果为 120+200+90=410。</t>
+          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6（区域列），条件是文本“华东区”，求和区域是 C2:C6（销售额列），公式会把所有华东区对应的销售额相加得到 4480。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用COUNTIFS统计多条件订单数</t>
+          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1345,14 +1196,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)，用于多条件计数。本题统计 B2:B6 中等于“华南”且 C2:C6 中等于“已签收”的行数。符合条件的订单为 B001、B004，共 2 笔。</t>
+          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数；ROUND(数值, 0) 将数值四舍五入到整数。这里 DATEDIF 得到 17 天，ROUND 后仍为 17。实际业务中可下拉填充计算其他运单。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用IF和IFERROR判断重量是否超限</t>
+          <t>第 3 题：第3题：多条件统计订单数量</t>
         </is>
       </c>
     </row>
@@ -1364,14 +1215,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IF 语法为 IF(判断条件, 条件成立时的值, 不成立时的值)。本题 B2&gt;30 成立返回“超重件”，否则返回“普通件”。外层 IFERROR(值, 出错时显示的内容) 用于捕获错误，例如空单元格参与比较或后续扩展时出现异常，就显示“待补录”。向下填充到 D6 即可。</t>
+          <t>COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...) 用于多条件计数。这里第一个条件是状态列等于“已完成”，第二个条件是金额列大于等于 500，两个条件同时满足才计数，结果有 A001 和 A004 两单。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用DATEDIF计算到港天数并用TODAY判断是否超期</t>
+          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
         </is>
       </c>
     </row>
@@ -1383,14 +1234,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期且会自动更新。DATEDIF(开始日期, 结束日期, "D") 返回两日期相差的天数，这里开始日期是 B2，结束日期用 TODAY()。得到天数后，用 IF(D2&gt;7,"超期","正常") 做超期判断。注意日期要按 Excel 可识别的日期格式录入。</t>
+          <t>VLOOKUP(查找值, 查找区域, 返回列号, FALSE) 在 A2:B5 第一列中精确查找 E1 的值，并返回第 2 列（库存数量）。IFERROR(公式, 错误时显示值) 用于捕获 #N/A 等错误，产品不存在时返回“未找到”。注意查找值 E1 需单独输入。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用XLOOKUP/VLOOKUP配合INDEX+MATCH查运费单价</t>
+          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1253,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找数组, 返回数组) 直接在目的地列找 B2，返回对应单价列，无需数列号。VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 中第2列是单价，FALSE 表示精确匹配，且查找值必须在区域首列。INDEX(返回区域, 行号) 配合 MATCH(查找值, 查找区域, 0)（0 为精确匹配）可先定位行号再取单价，适合列顺序被打乱的情况。报价表区域要加 $ 绝对引用以便向下填充。</t>
+          <t>INDEX(数据区域, 行号, 列号) 返回区域中指定行列交叉处的值；MATCH(查找值, 查找区域, 0) 返回精确匹配的位置。第一个 MATCH 在 A2:A4 中找月份所在行，第二个 MATCH 在 B1:D1 中找产品所在列，两者组合即可定位销售额。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总销售额</t>
+          <t>第 1 题：第1题：按部门汇总报销金额</t>
         </is>
       </c>
     </row>
@@ -490,43 +490,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家公司的财务助理，需要从销售台账中统计“华东区”的总销售额，用于月度汇报。</t>
+          <t>要求：财务助理小王在做月度报销台账，需要按部门统计报销总额，先练习单条件求和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格输入公式，计算区域为“华东区”的销售额合计。</t>
+          <t>任务：数据放在 A1:C7，请在 F2 单元格输入公式，计算【销售部】的报销金额合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>报销人</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -536,42 +536,42 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>行政部</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2300</v>
+        <v>950</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>技术部</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>华北区</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -581,421 +581,534 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流专员需要计算每票货物从“发运日期”到“到港日期”的到港天数，并将结果保留到整数（四舍五入），用于计算仓储费用。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，计算 SF001 的发运到到港天数，并用 ROUND 保留 0 位小数，结果为 17。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：行政专员小李在做考勤台账，需要统计某人迟到次数，并根据次数判断是否达到提醒标准。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SF001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：数据放在 A1:C7，请在 E2 单元格输入公式，统计【张三】的迟到次数；再在 E3 单元格用 IF 判断：次数大于等于 3 返回"需提醒"，否则返回"正常"。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SF002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-22</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>考勤状态</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SF003</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>2024-03-01</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件统计订单数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：电商运营需要统计“已完成”且金额大于等于 500 元的订单数量，用于评估高价值订单的完成情况。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，统计状态为“已完成”且金额大于等于 500 的订单数量，结果为 2。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>680</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>320</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司仓管员需要按仓库汇总到货重量，并把查不到的仓库显示为"无记录"而不是错误值。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>待发货</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>900</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：数据放在 A1:C7，请在 E2:E3 分别输入仓库名"上海仓"和"成都仓"，在 F2 输入一个公式，按 E 列仓库名汇总重量，若该仓库不存在则显示"无记录"。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>520</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>上海仓</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>已取消</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>780</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>210.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库管理员需要根据输入的“产品名称”查找到对应的库存数量。如果产品不存在，则显示“未找到”，避免出现错误值影响报表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，根据 E1 中输入的产品名称（例如“扳手”）查找库存数量；如果找不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>库存数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>螺丝刀</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>80</v>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>电工胶带</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>320</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：订单编号包含固定格式信息，运单需要从编号中截取客户代码和序号，并计算起运日到今天的间隔天数。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>卷尺</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>60</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：数据放在 A1:E4，请在 C2 用 MID 提取订单编号前两位的客户代码；在 D2 用 RIGHT 提取订单编号末尾 5 位的序号；在 E2 用 DATEDIF 计算从起运日期到今天的间隔天数。</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>起运日期</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>客户代码</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>到港天数</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>SH-2024-00123</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>BJ-2024-00456</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>GZ-2024-00789</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售经理需要根据“月份”和“产品”两个条件，从二维销售表中查找对应的销售额。要求使用 INDEX 和 MATCH 组合实现，比 VLOOKUP 更灵活（可向左查找）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 单元格输入公式，根据 G1 中的月份（如“2月”）和 H1 中的产品（如“产品B”）查找销售额，结果为 1600。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>产品B</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>产品C</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>900</v>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>1000</v>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流报价员需要根据省份到运价表里查对应首重价格，传统 VLOOKUP 要求查找列在最左，这里用 INDEX+MATCH 实现任意方向查找。</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>1100</v>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：数据放在 A1:C6，请在 E2 输入要查询的省份"江苏"，在 F2 用 INDEX+MATCH 返回该省份的【首重价格】，并用 ROUND 把结果保留 1 位小数。</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>省份</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>首重价格</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>续重价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1022,7 +1135,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总销售额</t>
+          <t>第 1 题：第1题：按部门汇总报销金额</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B6,"华东区",C2:C6)</f>
+        <f>SUMIF(A2:A7,"销售部",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1047,7 +1160,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
+          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1171,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>ROUND(DATEDIF(B2,C2,"d"),0)</f>
+        <f>IF(COUNTIFS(A2:A7,"张三",C2:C7,"迟到")&gt;=3,"需提醒","正常")</f>
         <v/>
       </c>
     </row>
@@ -1072,7 +1185,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计订单数量</t>
+          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1196,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(B2:B6,"已完成",C2:C6,"&gt;=500")</f>
+        <f>IFERROR(SUMIFS(C$2:C$7,A$2:A$7,E2),"无记录")</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1210,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
+          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1107,9 +1220,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(E1,A2:B5,2,FALSE),"未找到")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2:=MID(A2,1,2)  D2:=RIGHT(A2,5)  E2:=DATEDIF(B2,TODAY(),"D")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1122,7 +1236,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1247,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(B2:D4,MATCH(G1,A2:A4,0),MATCH(H1,B1:D1,0))</f>
+        <f>ROUND(INDEX(B2:B6,MATCH(E2,A2:A6,0)),1)</f>
         <v/>
       </c>
     </row>
@@ -1165,7 +1279,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总销售额</t>
+          <t>第 1 题：第1题：按部门汇总报销金额</t>
         </is>
       </c>
     </row>
@@ -1177,14 +1291,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 B2:B6（区域列），条件是文本“华东区”，求和区域是 C2:C6（销售额列），公式会把所有华东区对应的销售额相加得到 4480。</t>
+          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是部门列 A2:A7，条件是文本"销售部"（需加英文双引号），求和区域是金额列 C2:C7，结果为 1200+950+600=2750。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到港天数并四舍五入</t>
+          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1310,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数；ROUND(数值, 0) 将数值四舍五入到整数。这里 DATEDIF 得到 17 天，ROUND 后仍为 17。实际业务中可下拉填充计算其他运单。</t>
+          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里同时限定姓名为"张三"且状态为"迟到"，得到 3 次；外层 IF 判断 COUNTIFS 的结果是否 &gt;=3，成立返回"需提醒"，否则返回"正常"。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计订单数量</t>
+          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1329,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...) 用于多条件计数。这里第一个条件是状态列等于“已完成”，第二个条件是金额列大于等于 500，两个条件同时满足才计数，结果有 A001 和 A004 两单。</t>
+          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1...)，只有一个条件时用法与 SUMIF 类似。这里求和区域 C2:C7，条件区域 A2:A7，条件是 E2 的仓库名。外层 IFERROR 包裹公式（语法 IFERROR(值, 出错时返回值)），当结果为错误时返回"无记录"。注意把求和/条件区域用 $ 锁定，向下填充公式时才不会错位。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按产品查找库存并处理错误</t>
+          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1348,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 查找区域, 返回列号, FALSE) 在 A2:B5 第一列中精确查找 E1 的值，并返回第 2 列（库存数量）。IFERROR(公式, 错误时显示值) 用于捕获 #N/A 等错误，产品不存在时返回“未找到”。注意查找值 E1 需单独输入。</t>
+          <t>MID(文本, 起始位置, 字符数) 从文本中间截取字符，MID(A2,1,2) 取前两位客户代码；RIGHT(文本, 字符数) 从右端截取，RIGHT(A2,5) 取末尾 5 位序号；DATEDIF(开始日期, 结束日期, "D") 计算两个日期相差的天数，用 TODAY() 返回当天日期，"D" 表示按天计算。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 双向查表</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1367,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX(数据区域, 行号, 列号) 返回区域中指定行列交叉处的值；MATCH(查找值, 查找区域, 0) 返回精确匹配的位置。第一个 MATCH 在 A2:A4 中找月份所在行，第二个 MATCH 在 B1:D1 中找产品所在列，两者组合即可定位销售额。</t>
+          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的相对位置，MATCH(E2,A2:A6,0) 找到"江苏"在第 3 行；INDEX(返回区域, 行号) 按位置取值，INDEX(B2:B6,3) 取价格列第 3 个值即 11。外层 ROUND(数值, 位数) 将结果四舍五入到 1 位小数。INDEX+MATCH 不要求查找列在最左，比 VLOOKUP 更灵活。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总报销金额</t>
+          <t>第 1 题：第1题：按条件汇总重量</t>
         </is>
       </c>
     </row>
@@ -490,625 +490,573 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：财务助理小王在做月度报销台账，需要按部门统计报销总额，先练习单条件求和。</t>
+          <t>要求：物流仓库有一张货物台账，记录了每个批次的货物名称和重量（单位：kg）。现在需要统计‘纸箱’这一货物的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：数据放在 A1:C7，请在 F2 单元格输入公式，计算【销售部】的报销金额合计。</t>
+          <t>任务：请在单元格 D2 输入公式，计算‘纸箱’的总重量，结果应显示为 40。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>货物名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>报销人</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1200</v>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>行政部</t>
+          <t>木箱</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>800</v>
+          <t>30</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>950</v>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>技术部</t>
+          <t>编织袋</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1500</v>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>纸箱</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>600</v>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>行政部</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计符合条件的订单数</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：电商订单表记录了每笔订单的销售区域和订单金额。现在需要统计‘华东’区域中订单金额大于 100 的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：行政专员小李在做考勤台账，需要统计某人迟到次数，并根据次数判断是否达到提醒标准。</t>
+          <t>任务：请在单元格 E2 输入公式，统计华东区域且订单金额大于 100 的订单数量，结果应显示为 2。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：数据放在 A1:C7，请在 E2 单元格输入公式，统计【张三】的迟到次数；再在 E3 单元格用 IF 判断：次数大于等于 3 返回"需提醒"，否则返回"正常"。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>销售区域</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>考勤状态</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流跟踪表记录了每批货物的发货日期和到港日期。部分货物尚未到港，到港日期为空。需要计算已到港货物的到港天数（到港日期减发货日期），尚未到港的显示“在途”。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 D2 输入公式并向下填充到 D5，计算每批货物的到港天数；若到港日期为空则显示“在途”。B001 结果应为 7，B003 结果应为“在途”。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司仓管员需要按仓库汇总到货重量，并把查不到的仓库显示为"无记录"而不是错误值。</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>货物批次</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：数据放在 A1:C7，请在 E2:E3 分别输入仓库名"上海仓"和"成都仓"，在 F2 输入一个公式，按 E 列仓库名汇总重量，若该仓库不存在则显示"无记录"。</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>上海仓</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>120.5</v>
-      </c>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>北京仓</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>300</v>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>88.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>150</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>210.8</v>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按编号查货物名称与重量</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>95</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库有一张货物信息表，包含编号、名称和重量。现在需要根据给定的编号，查出对应的货物名称。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 E2 输入公式，根据 E1 中的编号“P03”查出对应的货物名称，结果应显示为“垫片”。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>货物名称</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>要求：订单编号包含固定格式信息，运单需要从编号中截取客户代码和序号，并计算起运日到今天的间隔天数。</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>螺丝</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：数据放在 A1:E4，请在 C2 用 MID 提取订单编号前两位的客户代码；在 D2 用 RIGHT 提取订单编号末尾 5 位的序号；在 E2 用 DATEDIF 计算从起运日期到今天的间隔天数。</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>螺母</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>起运日期</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>客户代码</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>到港天数</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>垫片</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>SH-2024-00123</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
+          <t>弹簧</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>BJ-2024-00456</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>GZ-2024-00789</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：双向查找并四舍五入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：一张月度销售表，行是产品，列是月份。现在需要根据指定的产品和月份，查出对应的销售额，并保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 F2 输入公式，根据 F1 中的产品“产品B”和 G1 中的月份“2月”，查出对应销售额并四舍五入保留 1 位小数，结果应显示为 5678.9。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流报价员需要根据省份到运价表里查对应首重价格，传统 VLOOKUP 要求查找列在最左，这里用 INDEX+MATCH 实现任意方向查找。</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>3月</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：数据放在 A1:C6，请在 E2 输入要查询的省份"江苏"，在 F2 用 INDEX+MATCH 返回该省份的【首重价格】，并用 ROUND 把结果保留 1 位小数。</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>产品A</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>1234.567</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2345.678</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>3456.789</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>省份</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>首重价格</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>续重价格</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>产品B</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>4567.891</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>5678.912</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>6789.123</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>3</v>
+          <t>产品C</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>7890.123</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>8901.234</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>9012.345</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1135,7 +1083,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总报销金额</t>
+          <t>第 1 题：第1题：按条件汇总重量</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1094,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"销售部",C2:C7)</f>
+        <f>SUMIF(A2:A6,"纸箱",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1108,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
+          <t>第 2 题：第2题：统计符合条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1119,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IF(COUNTIFS(A2:A7,"张三",C2:C7,"迟到")&gt;=3,"需提醒","正常")</f>
+        <f>COUNTIFS(B2:B6,"华东",C2:C6,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1133,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1144,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(SUMIFS(C$2:C$7,A$2:A$7,E2),"无记录")</f>
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"在途")</f>
         <v/>
       </c>
     </row>
@@ -1210,7 +1158,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
+          <t>第 4 题：第4题：按编号查货物名称与重量</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1168,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2:=MID(A2,1,2)  D2:=RIGHT(A2,5)  E2:=DATEDIF(B2,TODAY(),"D")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>VLOOKUP(E1,A2:C5,2,FALSE)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1236,7 +1183,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
+          <t>第 5 题：第5题：双向查找并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1194,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(INDEX(B2:B6,MATCH(E2,A2:A6,0)),1)</f>
+        <f>ROUND(INDEX(B2:D4,MATCH(F1,A2:A4,0),MATCH(G1,B1:D1,0)),1)</f>
         <v/>
       </c>
     </row>
@@ -1279,7 +1226,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按部门汇总报销金额</t>
+          <t>第 1 题：第1题：按条件汇总重量</t>
         </is>
       </c>
     </row>
@@ -1291,14 +1238,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是部门列 A2:A7，条件是文本"销售部"（需加英文双引号），求和区域是金额列 C2:C7，结果为 1200+950+600=2750。</t>
+          <t>SUMIF 用于对满足单个条件的单元格求和。语法为 =SUMIF(条件区域, 条件, 求和区域)。本题条件区域是 A2:A6（货物名称），条件是“纸箱”，求和区域是 B2:B6（重量），因此把三个“纸箱”对应的重量 12+8+20 加总得到 40。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计迟到次数并做简单判断</t>
+          <t>第 2 题：第2题：统计符合条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1257,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于多条件计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。这里同时限定姓名为"张三"且状态为"迟到"，得到 3 次；外层 IF 判断 COUNTIFS 的结果是否 &gt;=3，成立返回"需提醒"，否则返回"正常"。</t>
+          <t>COUNTIFS 用于统计同时满足多个条件的单元格个数。语法为 =COUNTIFS(区域1, 条件1, 区域2, 条件2, ...)。本题第一个条件是区域 B2:B6 等于“华东”，第二个条件是区域 C2:C6 大于 100，两个条件同时满足的有 A001 和 A003 两笔订单，所以结果为 2。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按仓库汇总重量并处理错误</t>
+          <t>第 3 题：第3题：计算到港天数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1329,14 +1276,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1...)，只有一个条件时用法与 SUMIF 类似。这里求和区域 C2:C7，条件区域 A2:A7，条件是 E2 的仓库名。外层 IFERROR 包裹公式（语法 IFERROR(值, 出错时返回值)），当结果为错误时返回"无记录"。注意把求和/条件区域用 $ 锁定，向下填充公式时才不会错位。</t>
+          <t>DATEDIF 用于计算两个日期之间的差值，语法为 =DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。当到港日期为空时，DATEDIF 会返回错误值，外层用 IFERROR 捕获错误并显示“在途”。语法为 =IFERROR(原公式, 出错时显示的内容)。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取订单编号中的信息并计算到港天数</t>
+          <t>第 4 题：第4题：按编号查货物名称与重量</t>
         </is>
       </c>
     </row>
@@ -1348,14 +1295,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID(文本, 起始位置, 字符数) 从文本中间截取字符，MID(A2,1,2) 取前两位客户代码；RIGHT(文本, 字符数) 从右端截取，RIGHT(A2,5) 取末尾 5 位序号；DATEDIF(开始日期, 结束日期, "D") 计算两个日期相差的天数，用 TODAY() 返回当天日期，"D" 表示按天计算。</t>
+          <t>VLOOKUP 用于在表格首列查找值，并返回同一行指定列的内容。语法为 =VLOOKUP(查找值, 查找区域, 返回第几列, 是否精确匹配)。本题查找值是 E1 中的“P03”，查找区域是 A2:C5，货物名称在区域中的第 2 列，FALSE 表示精确匹配，所以返回“垫片”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 INDEX+MATCH 查表匹配运价</t>
+          <t>第 5 题：第5题：双向查找并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1314,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(查找值, 查找区域, 0) 返回查找值在区域中的相对位置，MATCH(E2,A2:A6,0) 找到"江苏"在第 3 行；INDEX(返回区域, 行号) 按位置取值，INDEX(B2:B6,3) 取价格列第 3 个值即 11。外层 ROUND(数值, 位数) 将结果四舍五入到 1 位小数。INDEX+MATCH 不要求查找列在最左，比 VLOOKUP 更灵活。</t>
+          <t>INDEX 返回指定行和列交叉处的值，语法为 =INDEX(数据区域, 行号, 列号)。MATCH 用于查找值在区域中的位置，语法为 =MATCH(查找值, 区域, 0)，0 表示精确匹配。本题先用 MATCH 分别求出“产品B”在 A2:A4 中的行号和“2月”在 B1:D1 中的列号，再用 INDEX 在 B2:D4 中取出交叉值 5678.912，最后用 ROUND(数值, 1) 四舍五入保留 1 位小数，得到 5678.9。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,107 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：物流仓库有一张货物台账，记录了每个批次的货物名称和重量（单位：kg）。现在需要统计‘纸箱’这一货物的总重量。</t>
+          <t>要求：某物流仓库记录了几批货物的仓库名称和重量（单位：kg）。现在需要单独统计『A仓』的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 D2 输入公式，计算‘纸箱’的总重量，结果应显示为 40。</t>
+          <t>任务：在 F2 单元格输入公式，计算『A仓』所有货物的重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>重量(kg)</t>
+          <t>货物</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>A仓</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>纸箱</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>木箱</t>
+          <t>B仓</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
+          <t>塑料件</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
+          <t>A仓</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
+          <t>五金件</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>编织袋</t>
+          <t>C仓</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
+          <t>A仓</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
+          <t>塑料件</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -583,130 +603,100 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合条件的订单数</t>
+          <t>第 2 题：第2题：迟到次数统计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：电商订单表记录了每笔订单的销售区域和订单金额。现在需要统计‘华东’区域中订单金额大于 100 的订单数量。</t>
+          <t>要求：一份员工考勤台账记录了姓名和是否迟到（迟到/正常）。需要统计迟到的总人次。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E2 输入公式，统计华东区域且订单金额大于 100 的订单数量，结果应显示为 2。</t>
+          <t>任务：在 D2 单元格输入公式，统计“迟到”出现的次数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>订单编号</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>销售区域</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>订单金额</t>
+          <t>考勤状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>迟到</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>迟到</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>孙七</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>迟到</t>
         </is>
       </c>
     </row>
@@ -720,343 +710,344 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：多条件统计订单</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流跟踪表记录了每批货物的发货日期和到港日期。部分货物尚未到港，到港日期为空。需要计算已到港货物的到港天数（到港日期减发货日期），尚未到港的显示“在途”。</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 D2 输入公式并向下填充到 D5，计算每批货物的到港天数；若到港日期为空则显示“在途”。B001 结果应为 7，B003 结果应为“在途”。</t>
+          <t>要求：一份销售台账记录了销售员、产品和数量。需要统计『销售员为“小李”且产品为“键盘”』的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>货物批次</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，统计销售员为“小李”且产品为“键盘”的订单笔数。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-12</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>小王</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
-        </is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>小李</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>小张</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按编号查货物名称与重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库有一张货物信息表，包含编号、名称和重量。现在需要根据给定的编号，查出对应的货物名称。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：多条件重量汇总</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在单元格 E2 输入公式，根据 E1 中的编号“P03”查出对应的货物名称，结果应显示为“垫片”。</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：一份到货台账记录了仓库、货物和重量。需要统计『B仓』中『塑料件』的总重量。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>螺丝</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 单元格输入公式，计算仓库为“B仓”且货物为“塑料件”的重量合计。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>螺母</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>货物</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>A仓</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>垫片</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>B仓</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>弹簧</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>塑料件</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>A仓</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>五金件</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>塑料件</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>B仓</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：双向查找并四舍五入</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：一张月度销售表，行是产品，列是月份。现在需要根据指定的产品和月份，查出对应的销售额，并保留 1 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在单元格 F2 输入公式，根据 F1 中的产品“产品B”和 G1 中的月份“2月”，查出对应销售额并四舍五入保留 1 位小数，结果应显示为 5678.9。</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>3月</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：到港天数与误差处理</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>1234.567</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>2345.678</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>3456.789</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>要求：一份到港台账记录了船名、到港日期和预计到港日期。需要计算实际到港与预计到港之间的天数差；如果日期缺失导致出错，则显示“日期缺失”。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>产品B</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>4567.891</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>5678.912</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>6789.123</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式并向下填充到 D4，计算实际到港日期减去预计到港日期的天数；若出错则显示“日期缺失”。</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>产品C</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>7890.123</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>8901.234</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>9012.345</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>船名</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>实际到港日期</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>远洋1号</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>远洋2号</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>远洋3号</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1083,7 +1074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1085,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"纸箱",B2:B6)</f>
+        <f>SUMIF(A2:A6,"A仓",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1108,7 +1099,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合条件的订单数</t>
+          <t>第 2 题：第2题：迟到次数统计</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1110,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B6,"华东",C2:C6,"&gt;100")</f>
+        <f>COUNTIF(B2:B6,"迟到")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1124,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：多条件统计订单</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1135,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"在途")</f>
+        <f>COUNTIFS(A2:A6,"小李",B2:B6,"键盘")</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1149,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按编号查货物名称与重量</t>
+          <t>第 4 题：第4题：多条件重量汇总</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1160,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(E1,A2:C5,2,FALSE)</f>
+        <f>SUMIFS(C2:C6,A2:A6,"B仓",B2:B6,"塑料件")</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1174,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：双向查找并四舍五入</t>
+          <t>第 5 题：第5题：到港天数与误差处理</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1185,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(INDEX(B2:D4,MATCH(F1,A2:A4,0),MATCH(G1,B1:D1,0)),1)</f>
+        <f>IFERROR(DATEDIF(B2,C2,"d"),"日期缺失")</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1238,14 +1229,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于对满足单个条件的单元格求和。语法为 =SUMIF(条件区域, 条件, 求和区域)。本题条件区域是 A2:A6（货物名称），条件是“纸箱”，求和区域是 B2:B6（重量），因此把三个“纸箱”对应的重量 12+8+20 加总得到 40。</t>
+          <t>SUMIF 的语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是仓库列 A2:A6，条件是“A仓”，求和区域是重量列 C2:C6。函数会把 A 列等于“A仓”的对应 C 列重量相加，得到 120+230+45=395。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计符合条件的订单数</t>
+          <t>第 2 题：第2题：迟到次数统计</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1248,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 用于统计同时满足多个条件的单元格个数。语法为 =COUNTIFS(区域1, 条件1, 区域2, 条件2, ...)。本题第一个条件是区域 B2:B6 等于“华东”，第二个条件是区域 C2:C6 大于 100，两个条件同时满足的有 A001 和 A003 两笔订单，所以结果为 2。</t>
+          <t>COUNTIF 的语法是 COUNTIF(区域, 条件)，用于统计满足条件的单元格个数。这里区域是 B2:B6，条件是“迟到”，结果为 3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数并处理错误</t>
+          <t>第 3 题：第3题：多条件统计订单</t>
         </is>
       </c>
     </row>
@@ -1276,14 +1267,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 用于计算两个日期之间的差值，语法为 =DATEDIF(开始日期, 结束日期, 单位)，单位“d”表示天数。当到港日期为空时，DATEDIF 会返回错误值，外层用 IFERROR 捕获错误并显示“在途”。语法为 =IFERROR(原公式, 出错时显示的内容)。</t>
+          <t>COUNTIFS 的语法是 COUNTIFS(区域1, 条件1, 区域2, 条件2, ...)，只有同时满足所有条件的行才计数。这里第 1、4 行满足，结果为 2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按编号查货物名称与重量</t>
+          <t>第 4 题：第4题：多条件重量汇总</t>
         </is>
       </c>
     </row>
@@ -1295,14 +1286,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 用于在表格首列查找值，并返回同一行指定列的内容。语法为 =VLOOKUP(查找值, 查找区域, 返回第几列, 是否精确匹配)。本题查找值是 E1 中的“P03”，查找区域是 A2:C5，货物名称在区域中的第 2 列，FALSE 表示精确匹配，所以返回“垫片”。</t>
+          <t>SUMIFS 的语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。注意求和区域放在第一个参数。这里把 C2:C6 中同时满足 A 列为“B仓”、B 列为“塑料件”的重量相加，得到 85+40=125。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：双向查找并四舍五入</t>
+          <t>第 5 题：第5题：到港天数与误差处理</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1305,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX 返回指定行和列交叉处的值，语法为 =INDEX(数据区域, 行号, 列号)。MATCH 用于查找值在区域中的位置，语法为 =MATCH(查找值, 区域, 0)，0 表示精确匹配。本题先用 MATCH 分别求出“产品B”在 A2:A4 中的行号和“2月”在 B1:D1 中的列号，再用 INDEX 在 B2:D4 中取出交叉值 5678.912，最后用 ROUND(数值, 1) 四舍五入保留 1 位小数，得到 5678.9。</t>
+          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。D2 中 B2=2024-01-10、C2=2024-01-12，得到 2；D3 得到 0。D4 中实际日期为空，DATEDIF 会报错，外层 IFERROR 捕获错误并返回“日期缺失”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,38 +490,38 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：某物流仓库记录了几批货物的仓库名称和重量（单位：kg）。现在需要单独统计『A仓』的总重量。</t>
+          <t>要求：你是仓库管理员，收到一张到货台账，记录了每批货物的供应商和重量。老板想知道「华东供应商」的总到货重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 F2 单元格输入公式，计算『A仓』所有货物的重量合计。</t>
+          <t>任务：在单元格 E2 中计算「华东供应商」的重量合计，返回一个数值。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>货物</t>
+          <t>货物名称</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>华东供应商</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -536,12 +536,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>B仓</t>
+          <t>华南供应商</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>塑料件</t>
+          <t>木箱</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -551,22 +551,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>华东供应商</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>五金件</t>
+          <t>托盘</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>C仓</t>
+          <t>华北供应商</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -581,16 +581,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>华东供应商</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>塑料件</t>
+          <t>木箱</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -603,100 +603,130 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：迟到次数统计</t>
+          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIF</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：一份员工考勤台账记录了姓名和是否迟到（迟到/正常）。需要统计迟到的总人次。</t>
+          <t>要求：物流部有一张发货记录表，记录每单的线路和状态。主管想知道「上海线」中状态为「已签收」的订单有多少单。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，统计“迟到”出现的次数。</t>
+          <t>任务：在单元格 E2 中统计「线路=上海线 且 状态=已签收」的订单数量，返回一个整数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>考勤状态</t>
+          <t>线路</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>上海线</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>北京线</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>上海线</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>上海线</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>孙七</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>上海线</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
         </is>
       </c>
     </row>
@@ -710,121 +740,121 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计订单</t>
+          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：一份销售台账记录了销售员、产品和数量。需要统计『销售员为“小李”且产品为“键盘”』的订单笔数。</t>
+          <t>要求：销售台账记录了各地区、各月份的销售额。财务需要汇总「华南地区」在「1月」的销售额合计。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E2 单元格输入公式，统计销售员为“小李”且产品为“键盘”的订单笔数。</t>
+          <t>任务：在单元格 E2 中计算「地区=华南 且 月份=1月」的销售额合计，返回一个数值。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>月份</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>小王</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>小张</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="35">
@@ -837,217 +867,154 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件重量汇总</t>
+          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：进口货物台账中记录了每批货的到港日期。业务员想实时查看从到港当天到今天已经过了多少天。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>要求：一份到货台账记录了仓库、货物和重量。需要统计『B仓』中『塑料件』的总重量。</t>
+          <t>任务：在单元格 D2 中输入公式，计算 G001 这批货从到港到今天的天数（结果随当天日期自动变化），返回一个整数。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 单元格输入公式，计算仓库为“B仓”且货物为“塑料件”的重量合计。</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>A仓</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>120</v>
+          <t>2024-02-15</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>B仓</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>85</v>
+          <t>2024-03-01</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>A仓</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>五金件</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>B仓</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>塑料件</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>40</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>B仓</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>60</v>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张商品价格表和一张销售明细表。需要根据商品名称查出单价，计算「数量×单价」的金额并保留2位小数；若查不到商品（例如「台灯」不在价格表里）则显示「未找到」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在价格表之外的商品明细中（明细数据：商品「笔记本」数量 3、「台灯」数量 2），对「笔记本」这行在单元格 D8 计算金额并四舍五入保留2位小数；对「台灯」这行用同样思路让查不到时显示「未找到」。请写出 D8 中针对「笔记本」的通用公式（假设商品名在 B8、数量在 C8）。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：到港天数与误差处理</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>要求：一份到港台账记录了船名、到港日期和预计到港日期。需要计算实际到港与预计到港之间的天数差；如果日期缺失导致出错，则显示“日期缺失”。</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>铅笔</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式并向下填充到 D4，计算实际到港日期减去预计到港日期的天数；若出错则显示“日期缺失”。</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>船名</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>实际到港日期</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>远洋1号</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-12</t>
-        </is>
+          <t>订书机</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>远洋2号</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>远洋3号</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1074,7 +1041,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1052,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"A仓",C2:C6)</f>
+        <f>SUMIF(A2:A6,"华东供应商",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1066,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：迟到次数统计</t>
+          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1077,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"迟到")</f>
+        <f>COUNTIFS(B2:B6,"上海线",C2:C6,"已签收")</f>
         <v/>
       </c>
     </row>
@@ -1124,7 +1091,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计订单</t>
+          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1102,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(A2:A6,"小李",B2:B6,"键盘")</f>
+        <f>SUMIFS(C2:C6,A2:A6,"华南",B2:B6,"1月")</f>
         <v/>
       </c>
     </row>
@@ -1149,7 +1116,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件重量汇总</t>
+          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1127,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>SUMIFS(C2:C6,A2:A6,"B仓",B2:B6,"塑料件")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1174,7 +1141,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：到港天数与误差处理</t>
+          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1152,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(DATEDIF(B2,C2,"d"),"日期缺失")</f>
+        <f>IFERROR(ROUND(XLOOKUP(B8,A2:A5,B2:B5),2),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1217,7 +1184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1196,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 的语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是仓库列 A2:A6，条件是“A仓”，求和区域是重量列 C2:C6。函数会把 A 列等于“A仓”的对应 C 列重量相加，得到 120+230+45=395。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域) 用于按单一条件求和。A2:A6 存放供应商名称，条件为「华东供应商」，对满足条件的行在 C2:C6 中求和：120+200+150=470。条件区域和求和区域行数必须一致。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：迟到次数统计</t>
+          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1248,14 +1215,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 的语法是 COUNTIF(区域, 条件)，用于统计满足条件的单元格个数。这里区域是 B2:B6，条件是“迟到”，结果为 3。</t>
+          <t>COUNTIFS(区域1, 条件1, 区域2, 条件2, ...) 用于多条件计数。B2:B6 判断是否「上海线」，C2:C6 判断是否「已签收」，两个条件同时成立才计数。满足的行是 A001、A004、A005，共 3 单。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计订单</t>
+          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1234,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 的语法是 COUNTIFS(区域1, 条件1, 区域2, 条件2, ...)，只有同时满足所有条件的行才计数。这里第 1、4 行满足，结果为 2。</t>
+          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...) 注意求和区域放在第一个参数，这与 SUMIF 不同。对 A2:A6 为「华南」且 B2:B6 为「1月」的行，在 C2:C6 求和：5200+3800=9000。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件重量汇总</t>
+          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
         </is>
       </c>
     </row>
@@ -1286,14 +1253,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 的语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。注意求和区域放在第一个参数。这里把 C2:C6 中同时满足 A 列为“B仓”、B 列为“塑料件”的重量相加，得到 85+40=125。</t>
+          <t>TODAY() 返回今天的日期；DATEDIF(开始日期, 结束日期, "d") 返回两日期相差的天数，"d" 表示按天。B2 是到港日期，TODAY() 是当前日期，公式会随日期自动更新。注意样例中的日期是文本，实际使用时应为真正的日期格式。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：到港天数与误差处理</t>
+          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1272,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数。D2 中 B2=2024-01-10、C2=2024-01-12，得到 2；D3 得到 0。D4 中实际日期为空，DATEDIF 会报错，外层 IFERROR 捕获错误并返回“日期缺失”。</t>
+          <t>XLOOKUP(查找值, 查找区域, 返回区域) 在 A2:A5 中找 B8 的商品名，返回 B2:B5 对应单价；ROUND(数值,2) 保留2位小数；IFERROR(公式, "未找到") 在查不到时报错时改为显示「未找到」。对「笔记本」：单价8×数量3=24.00（若 C8 参与则 =IFERROR(ROUND(XLOOKUP(B8,A2:A5,B2:B5)*C8,2),"未找到")）。若用 VLOOKUP 则写作 =IFERROR(ROUND(VLOOKUP(B8,A2:B5,2,FALSE)*C8,2),"未找到")，其中 FALSE 表示精确匹配。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某客户的订单总金额</t>
         </is>
       </c>
     </row>
@@ -490,107 +490,77 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，收到一张到货台账，记录了每批货物的供应商和重量。老板想知道「华东供应商」的总到货重量。</t>
+          <t>要求：你是一家小店的店主，手头有一张订单台账，记录了每个客户各自的订单金额。现在老板想知道「王芳」这个客户一共贡献了多少金额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 E2 中计算「华东供应商」的重量合计，返回一个数值。</t>
+          <t>任务：请在 D2 单元格输入公式，计算客户为「王芳」的订单金额合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>客户</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东供应商</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华南供应商</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>85</v>
+          <t>李明</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华东供应商</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>200</v>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华北供应商</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>60</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>华东供应商</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>150</v>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="11">
@@ -603,418 +573,443 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计快递单数与最大重量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流仓库有一张到货明细表，记录了每票货物的目的城市和重量（kg）。需要统计发往「上海」的票数，并找出所有货物中最重的一件是多少 kg。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：物流部有一张发货记录表，记录每单的线路和状态。主管想知道「上海线」中状态为「已签收」的订单有多少单。</t>
+          <t>任务：请在 E2 输入公式统计目的城市为「上海」的票数；在 E3 输入公式求所有重量的最大值。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 E2 中统计「线路=上海线 且 状态=已签收」的订单数量，返回一个整数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>目的城市</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>线路</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SF001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>SF002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>上海线</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>SF003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>北京线</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>SF004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>上海线</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>SF005</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>上海线</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>上海线</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件汇总与到港天数</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：船务台账记录了每票货物的到港日期、目的港和费用。需要汇总「上海港」在 2024 年产生的费用，并计算某票货物从到港到今天的到港天数。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 F2 用 SUMIFS 汇总目的港为「上海港」且到港日期在 2024 年的费用；在 F3 用 DATEDIF 计算 A001 从 2024-01-10 到今天的天数。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售台账记录了各地区、各月份的销售额。财务需要汇总「华南地区」在「1月」的销售额合计。</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>单号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>目的港</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>费用</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 E2 中计算「地区=华南 且 月份=1月」的销售额合计，返回一个数值。</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>宁波港</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>5200</v>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>4300</v>
+          <t>上海港</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>3800</v>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>2900</v>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：有一张发货明细（含重量）和一张运费单价表（按重量区间）。需要统计重量在 10kg 到 20kg 之间的票数，并根据某票货物重量从单价表查出对应运费单价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 用 COUNTIFS 统计重量在 10 到 20 之间的票数；在 D3 用 VLOOKUP 查出重量 18kg 对应的运费单价（近似匹配，假设单价表在 G2:H4：0→5、10→4、20→3）。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>单号</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>重量kg</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：进口货物台账中记录了每批货的到港日期。业务员想实时查看从到港当天到今天已经过了多少天。</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 D2 中输入公式，计算 G001 这批货从到港到今天的天数（结果随当天日期自动变化），返回一个整数。</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>G001</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>G002</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>G003</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：有一张货物信息表，包含单号、品名、重量。需要根据单号「C003」查出对应的品名，并用 IFERROR 让查不到时显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张商品价格表和一张销售明细表。需要根据商品名称查出单价，计算「数量×单价」的金额并保留2位小数；若查不到商品（例如「台灯」不在价格表里）则显示「未找到」。</t>
+          <t>任务：请在 E2 输入公式，根据单号「C003」返回品名；再用 IFERROR 包装，使查不到时显示「未找到」。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在价格表之外的商品明细中（明细数据：商品「笔记本」数量 3、「台灯」数量 2），对「笔记本」这行在单元格 D8 计算金额并四舍五入保留2位小数；对「台灯」这行用同样思路让查不到时显示「未找到」。请写出 D8 中针对「笔记本」的通用公式（假设商品名在 B8、数量在 C8）。</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>单号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>铅笔</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>1.5</v>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>8</v>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>12.5</v>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1041,7 +1036,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某客户的订单总金额</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1047,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"华东供应商",C2:C6)</f>
+        <f>SUMIF(A2:A6,"王芳",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1066,7 +1061,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计快递单数与最大重量</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1072,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B6,"上海线",C2:C6,"已签收")</f>
+        <f>COUNTIF(B2:B6,"上海") 和 =MAX(C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1086,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
+          <t>第 3 题：第3题：多条件汇总与到港天数</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1097,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(C2:C6,A2:A6,"华南",B2:B6,"1月")</f>
+        <f>SUMIFS(D2:D5,B2:B5,"上海港",C2:C5,"&gt;=2024-01-01",C2:C5,"&lt;=2024-12-31") 和 =DATEDIF(C2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1111,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
+          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1122,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>COUNTIFS(B2:B6,"&gt;=10",B2:B6,"&lt;=20") 和 =VLOOKUP(18,G2:H4,2,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -1141,7 +1136,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
+          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1147,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(ROUND(XLOOKUP(B8,A2:A5,B2:B5),2),"未找到")</f>
+        <f>IFERROR(XLOOKUP("C003",A2:A5,B2:B5),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1184,7 +1179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：按条件汇总重量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某客户的订单总金额</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1191,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域) 用于按单一条件求和。A2:A6 存放供应商名称，条件为「华东供应商」，对满足条件的行在 C2:C6 中求和：120+200+150=470。条件区域和求和区域行数必须一致。</t>
+          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6（客户列），条件是 "王芳"，求和区域是 B2:B6（金额列）。结果为 1200+350+650=2200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件计数（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计快递单数与最大重量</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1210,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS(区域1, 条件1, 区域2, 条件2, ...) 用于多条件计数。B2:B6 判断是否「上海线」，C2:C6 判断是否「已签收」，两个条件同时成立才计数。满足的行是 A001、A004、A005，共 3 单。</t>
+          <t>COUNTIF 按条件计数，语法 COUNTIF(区域, 条件)，统计上海出现的次数得 3。MAX 返回区域最大值，MAX(C2:C6) 得 15.2。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件求和（SUMIFS）</t>
+          <t>第 3 题：第3题：多条件汇总与到港天数</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1229,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...) 注意求和区域放在第一个参数，这与 SUMIF 不同。对 A2:A6 为「华南」且 B2:B6 为「1月」的行，在 C2:C6 求和：5200+3800=9000。</t>
+          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)，可叠加多个条件，这里求上海港且在 2024 年区间内，得 5000+4500=9500。DATEDIF(开始日期, 结束日期, "d") 返回相差天数，用 TODAY() 作结束日期即从到港日到今天的天数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数（DATEDIF + TODAY）</t>
+          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1248,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期；DATEDIF(开始日期, 结束日期, "d") 返回两日期相差的天数，"d" 表示按天。B2 是到港日期，TODAY() 是当前日期，公式会随日期自动更新。注意样例中的日期是文本，实际使用时应为真正的日期格式。</t>
+          <t>COUNTIFS 支持多条件计数，统计重量同时 &gt;=10 且 &lt;=20 的票数得 3。VLOOKUP(查找值, 表格, 列号, TRUE) 用近似匹配，在第1列升序中找不超过 18 的最大值（10），返回第2列得 4。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查表取单价并计算金额（XLOOKUP/VLOOKUP + ROUND + IFERROR）</t>
+          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1267,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找区域, 返回区域) 在 A2:A5 中找 B8 的商品名，返回 B2:B5 对应单价；ROUND(数值,2) 保留2位小数；IFERROR(公式, "未找到") 在查不到时报错时改为显示「未找到」。对「笔记本」：单价8×数量3=24.00（若 C8 参与则 =IFERROR(ROUND(XLOOKUP(B8,A2:A5,B2:B5)*C8,2),"未找到")）。若用 VLOOKUP 则写作 =IFERROR(ROUND(VLOOKUP(B8,A2:B5,2,FALSE)*C8,2),"未找到")，其中 FALSE 表示精确匹配。</t>
+          <t>XLOOKUP(查找值, 查找数组, 返回数组) 直接返回对应结果，比 VLOOKUP 更灵活；这里在 A 列找 C003，返回 B 列对应值「橙子」。IFERROR(表达式, 出错时值) 在查找失败时显示「未找到」，避免 #N/A 报错。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户的订单总金额</t>
+          <t>第 1 题：第1题：统计指定仓库的出库总量</t>
         </is>
       </c>
     </row>
@@ -490,197 +490,206 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的店主，手头有一张订单台账，记录了每个客户各自的订单金额。现在老板想知道「王芳」这个客户一共贡献了多少金额。</t>
+          <t>要求：某电商仓库有一份商品出库台账，记录了每个商品所属的仓库和出库件数。现在需要快速统计「华东仓」的总出库件数，方便做仓储绩效汇总。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 D2 单元格输入公式，计算客户为「王芳」的订单金额合计。</t>
+          <t>任务：请在单元格 E2 中输入公式，计算「所属仓库」为「华东仓」的出库件数总和，结果应为 380。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>客户</t>
+          <t>商品名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>所属仓库</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>出库件数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200</v>
+          <t>运动鞋A</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李明</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>800</v>
+          <t>运动鞋B</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>华北仓</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>350</v>
+          <t>背包A</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>500</v>
+          <t>背包B</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>华南仓</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>650</v>
+          <t>帽子A</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>帽子B</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>华北仓</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计快递单数与最大重量</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流仓库有一张到货明细表，记录了每票货物的目的城市和重量（kg）。需要统计发往「上海」的票数，并找出所有货物中最重的一件是多少 kg。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计到港天数并设置异常提示</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 E2 输入公式统计目的城市为「上海」的票数；在 E3 输入公式求所有重量的最大值。</t>
+          <t>要求：物流部门有一份货物到港记录，包含「到港日期」。需要计算每批货物从到港到今天已经过去了多少天，用于监控滞留时间。若日期为空或无法计算，则显示「待确认」，避免出现错误值。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>目的城市</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>重量kg</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 C2 输入公式，计算 G001 从到港日期到今天的天数；若无法计算则显示「待确认」。然后将公式下拉到 C5。（假设今天是 2024-03-15，G001 结果应为 70。）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SF001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>12.5</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SF002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>8</v>
+          <t>2024-01-05</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SF003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>15.2</v>
+          <t>2024-02-10</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SF004</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>9.800000000000001</v>
-      </c>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SF005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>6.4</v>
+          <t>2024-03-01</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -693,319 +702,316 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件汇总与到港天数</t>
+          <t>第 3 题：第3题：按重量区间统计并求和</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>要求：船务台账记录了每票货物的到港日期、目的港和费用。需要汇总「上海港」在 2024 年产生的费用，并计算某票货物从到港到今天的到港天数。</t>
+          <t>要求：快递网点有一份包裹重量明细，需要统计两个指标：①重量大于等于 5 公斤且小于 10 公斤的包裹数量；②「北京」地区这些中等重量包裹的总重量。用于安排配送车辆。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 F2 用 SUMIFS 汇总目的港为「上海港」且到港日期在 2024 年的费用；在 F3 用 DATEDIF 计算 A001 从 2024-01-10 到今天的天数。</t>
+          <t>任务：请在单元格 E2 输入公式统计重量 &gt;=5 且 &lt;10 公斤的包裹数量（结果应为 3）；在单元格 E3 输入公式统计「北京」地区重量 &gt;=5 且 &lt;10 公斤的包裹总重量（结果应为 21.3）。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>单号</t>
+          <t>包裹单号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>目的港</t>
+          <t>目的地区</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>费用</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>P1001</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>5000</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>P1002</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>宁波港</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>3000</v>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>P1003</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>4500</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>P1004</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>上海港</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>2000</v>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>P1005</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>P1006</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：有一张发货明细（含重量）和一张运费单价表（按重量区间）。需要统计重量在 10kg 到 20kg 之间的票数，并根据某票货物重量从单价表查出对应运费单价。</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D2 用 COUNTIFS 统计重量在 10 到 20 之间的票数；在 D3 用 VLOOKUP 查出重量 18kg 对应的运费单价（近似匹配，假设单价表在 G2:H4：0→5、10→4、20→3）。</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据编号查表获取商品价格（VLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>重量kg</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售订单表只记录了商品编号，价格存放在另一张价格表中。需要用编号到价格表里查对应单价，填回订单表；如果编号在价格表里查不到，就显示「无报价」，方便人工跟进。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>5</v>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：价格表为：A101 对应 19.9，B205 对应 49.5（假设在 G2:H3 区域，G 列为编号、H 列为价格）。请在 C2 输入公式，根据 B 列左侧的编号（A 列）查单价，查不到显示「无报价」，并下拉到 C5。A101 结果应为 19.9，C999 结果应为「无报价」。</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>12</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>订单数量</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>A101</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>B205</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>B005</t>
+          <t>A101</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>C999</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：有一张货物信息表，包含单号、品名、重量。需要根据单号「C003」查出对应的品名，并用 IFERROR 让查不到时显示「未找到」。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查表找库存（XLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 E2 输入公式，根据单号「C003」返回品名；再用 IFERROR 包装，使查不到时显示「未找到」。</t>
+          <t>要求：仓库库存是一个二维表：行是商品，列是仓库。现在要从表中精确取出「蓝牙耳机」在「广州仓」的库存数量。要求用 INDEX+MATCH 组合实现，并给出 XLOOKUP 的替代写法，体会不同查表方式的思路。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在单元格 F2 输入公式，查找「蓝牙耳机」在「广州仓」的库存（结果应为 25）。可分别尝试 INDEX+MATCH 与 XLOOKUP 两种写法。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>30</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>广州仓</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
+          <t>蓝牙耳机</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="C50" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
+          <t>充电器</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>葡萄</t>
-        </is>
+          <t>数据线</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="53">
@@ -1036,7 +1042,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户的订单总金额</t>
+          <t>第 1 题：第1题：统计指定仓库的出库总量</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1053,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"王芳",B2:B6)</f>
+        <f>SUMIF(B2:B7,"华东仓",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1067,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计快递单数与最大重量</t>
+          <t>第 2 题：第2题：统计到港天数并设置异常提示</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1078,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"上海") 和 =MAX(C2:C6)</f>
+        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待确认")</f>
         <v/>
       </c>
     </row>
@@ -1086,7 +1092,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件汇总与到港天数</t>
+          <t>第 3 题：第3题：按重量区间统计并求和</t>
         </is>
       </c>
     </row>
@@ -1096,9 +1102,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>SUMIFS(D2:D5,B2:B5,"上海港",C2:C5,"&gt;=2024-01-01",C2:C5,"&lt;=2024-12-31") 和 =DATEDIF(C2,TODAY(),"d")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>E2: =COUNTIFS(C2:C7,"&gt;=5",C2:C7,"&lt;10")；E3: =SUMIFS(C2:C7,B2:B7,"北京",C2:C7,"&gt;=5",C2:C7,"&lt;10")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1111,7 +1118,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
+          <t>第 4 题：第4题：根据编号查表获取商品价格（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1129,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(B2:B6,"&gt;=10",B2:B6,"&lt;=20") 和 =VLOOKUP(18,G2:H4,2,TRUE)</f>
+        <f>IFERROR(VLOOKUP(A2,$G$2:$H$3,2,FALSE),"无报价")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1143,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查表找库存（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1154,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP("C003",A2:A5,B2:B5),"未找到")</f>
+        <f>INDEX(B2:D4,MATCH("蓝牙耳机",A2:A4,0),MATCH("广州仓",B1:D1,0))  或  =XLOOKUP("蓝牙耳机",A2:A4,XLOOKUP("广州仓",B1:D1,B2:D4))</f>
         <v/>
       </c>
     </row>
@@ -1179,7 +1186,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某客户的订单总金额</t>
+          <t>第 1 题：第1题：统计指定仓库的出库总量</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1198,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按单个条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6（客户列），条件是 "王芳"，求和区域是 B2:B6（金额列）。结果为 1200+350+650=2200。</t>
+          <t>SUMIF 用于单条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题条件区域是 B2:B7 的仓库列，条件是文本「华东仓」（要加英文双引号），求和区域是 C2:C7 的出库件数列。函数会逐行判断仓库是否等于「华东仓」，只把符合条件的 120+200+60=380 相加。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计快递单数与最大重量</t>
+          <t>第 2 题：第2题：统计到港天数并设置异常提示</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1217,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 按条件计数，语法 COUNTIF(区域, 条件)，统计上海出现的次数得 3。MAX 返回区域最大值，MAX(C2:C6) 得 15.2。</t>
+          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间相差的天数，"d" 表示按天计算。TODAY() 返回当前日期，所以 DATEDIF(B2,TODAY(),"d") 就是从到港日到今天的间隔天数。IFERROR(表达式, "待确认") 在表达式出错时（例如日期为空）返回「待确认」，防止工作表出现 #NUM! 或 #VALUE! 错误。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件汇总与到港天数</t>
+          <t>第 3 题：第3题：按重量区间统计并求和</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1236,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)，可叠加多个条件，这里求上海港且在 2024 年区间内，得 5000+4500=9500。DATEDIF(开始日期, 结束日期, "d") 返回相差天数，用 TODAY() 作结束日期即从到港日到今天的天数。</t>
+          <t>COUNTIFS(区域1, 条件1, 区域2, 条件2, ...) 按多个条件计数；SUMIFS(求和区域, 条件区域1, 条件1, ...) 按多个条件求和。区间条件要写成带比较符的文本，如 "&gt;=5"、"&lt;10"。E2 只有重量一个区域的两个条件，得 6.5、9.8、5.0 共 3 个。E3 增加「目的地区=北京」条件，同样三个包裹重量相加 6.5+9.8+5.0=21.3。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按重量筛选并用 VLOOKUP 查运费</t>
+          <t>第 4 题：第4题：根据编号查表获取商品价格（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1248,14 +1255,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 支持多条件计数，统计重量同时 &gt;=10 且 &lt;=20 的票数得 3。VLOOKUP(查找值, 表格, 列号, TRUE) 用近似匹配，在第1列升序中找不超过 18 的最大值（10），返回第2列得 4。</t>
+          <t>VLOOKUP(查找值, 查找区域, 返回第几列, 是否精确匹配) 在查找区域第一列中找查找值，找到后返回同行指定列的值。这里查找值是 A2 的编号，区域 $G$2:$H$3 用绝对引用固定，返回第 2 列价格，FALSE 表示精确匹配。编号 C999 找不到会返回 #N/A，IFERROR 把它替换成「无报价」。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：INDEX+MATCH 精确查表并处理错误</t>
+          <t>第 5 题：第5题：用 INDEX+MATCH 双向查表找库存（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1274,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找数组, 返回数组) 直接返回对应结果，比 VLOOKUP 更灵活；这里在 A 列找 C003，返回 B 列对应值「橙子」。IFERROR(表达式, 出错时值) 在查找失败时显示「未找到」，避免 #N/A 报错。</t>
+          <t>INDEX(数据区域, 行号, 列号) 按行列位置取值。MATCH(查找值, 区域, 0) 返回查找值在区域中的相对位置，0 表示精确匹配。第一个 MATCH 找「蓝牙耳机」在 A2:A4 中是第 1 行，第二个 MATCH 找「广州仓」在 B1:D1 中是第 3 列，INDEX 取 B2:D4 第 1 行第 3 列即 25。XLOOKUP 思路是：先在内层用 XLOOKUP 按列标题「广州仓」从 B1:D1 找到整列数据 B2:D4 中对应的那列，再由外层 XLOOKUP 按「蓝牙耳机」在该列中取到 25。</t>
         </is>
       </c>
     </row>
